--- a/data/systems.xlsx
+++ b/data/systems.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -819,8 +819,6 @@
           <t>LORA (missile) — Wikipedia</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -928,8 +926,6 @@
           <t>NAVDEX 2019: MBDA unveils the Self-Protection Integrated Mistral Module (SPIMM) for surface ship — EDR Magazine</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1037,8 +1033,6 @@
           <t>The Cube — EDGE Defence Ltd</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1136,10 +1130,6 @@
           <t>C-DOME: Maritime Application of the Combat-Proven Iron Dome — Rafael</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1247,8 +1237,6 @@
           <t>U.S. Navy Brings Offensive Capability To LCS With Mk 70 PDS — Naval News</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1346,10 +1334,6 @@
           <t>HUNTER 10 Long-Range Multi Role Loitering Munition — EDGE Group</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1457,8 +1441,6 @@
           <t>China's truck drone launcher hides airpower in civilian traffic — Asia Times</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1566,8 +1548,6 @@
           <t>Patria NEMO Container — 120 mm mortar system (product sheet)</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1675,8 +1655,6 @@
           <t>Naval Strike Missile (NSM) Coastal Defence System — Kongsberg</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1784,8 +1762,6 @@
           <t>U.S. Navy And Army Mk 70 PDS Stretch Their Wings — Naval News</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1893,8 +1869,6 @@
           <t>North Korea Debuts Rocket Launchers That Appear As Civilian Trucks — The War Zone</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1992,10 +1966,6 @@
           <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2103,8 +2073,6 @@
           <t>Iran's Modern Q-Ship: A Threat from New Quarters — RUSI</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2212,8 +2180,6 @@
           <t>Shipping Container Launcher Packing 126 Kamikaze Drones — UAS Vision</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2311,10 +2277,6 @@
           <t>Mysterious Guided Rocket Launcher Disguised In A Shipping Container At Fort Bragg Identified — The War Zone</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2412,10 +2374,6 @@
           <t>CWS-A — Invariant Corp.</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2523,8 +2481,6 @@
           <t>Babcock and Frankenburg will build a containerized launch system for anti-drone missiles — Resilience Media</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2622,10 +2578,6 @@
           <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2723,10 +2675,6 @@
           <t>Operation Spiderweb — Wikipedia</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2834,8 +2782,6 @@
           <t>Locust — AeroVironment</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2943,8 +2889,6 @@
           <t>Chinese Cargo Ship Packed Full Of Modular Missile Launchers Emerges — The War Zone</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3042,10 +2986,6 @@
           <t>Turkey just unveiled a 19.8-ton drone submarine built to launch FPV drone swarms, anti-ship missiles, torpedoes and mines while submerged — Autonocion.com</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3143,10 +3083,6 @@
           <t>Containerized Variant Of Navy's Drone-Swatting HELIOS Laser Being Pushed By Congress — The War Zone</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3254,8 +3190,6 @@
           <t>Hellfire Missile Launcher Tucked Inside A Container Rolled Out By Lockheed — The War Zone</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3353,10 +3287,6 @@
           <t>Hanwha Unveils Striker MUSV Family at Eurosatory 2026 — Naval News</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3464,8 +3394,3928 @@
           <t>Containerised Missile Launcher makes its debut at Eurosatory — Rheinmetall</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>csdcs</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CSDCS Container-Type Sea Defense Combat System</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CSDCS, containerized coastal defense system, China's Club-K</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CASIC (China Aerospace Science and Industry Corp)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2022-11-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>November 2022</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Unveiled at Airshow China (Zhuhai)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Missile launcher</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>A self-contained combat system built into a 20/40-ft container (~13m x 2.3m x 2.5m) with operator station, power and a quadruple launcher firing YJ-12E supersonic or YJ-18E subsonic anti-ship cruise missiles from ships, trucks or trains; China's openly-marketed Club-K analogue with broader missile compatibility.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Distinct from the Zhong Da 79 arsenal-ship entry already in the list; this is the standalone containerized launcher product.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>https://www.globaltimes.cn/page/202211/1279349.shtml</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>China debuts container-type missile launch system - Global Times</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>https://en.defence-ua.com/news/in_2022_china_unveiled_its_copy_of_russias_club_k_missile_system_now_it_threatens_us_navy-14827.html</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>China unveiled its copy of Russia's Club-K - Defense Express</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>https://www.vermilionchina.com/p/36-chinas-container-launched-cruise</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>China's Container-launched Cruise Missiles - Vermilion China</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>yj-18c</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>YJ-18C Container-Launched Cruise Missile</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>YJ-18C, container-launched YJ-18 land-attack variant</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CASC (China Aerospace Science and Technology Corp)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>March 2019</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>US intelligence-sourced reporting of container-launched variant</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Covert strike</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Concealed cargo</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Reported land-attack variant of the YJ-18 cruise missile (&gt;1,000 km, low-RCS) designed to fire from launchers built to look like standard ISO shipping containers on merchant-ship decks or trucks; conceptually a Chinese Club-K.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Traces to a single 2019 US-intel report; missile never officially shown separately from the container concept.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>https://freebeacon.com/national-security/china-building-long-range-cruise-missile-launched-from-ship-container/</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>China Building Cruise Missile Launched from Ship Container - Free Beacon</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/archives/archives-naval-defense/naval-defense-2019/china-is-building-long-range-cruise-missiles-launched-from-ship-containers</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>China building long-range cruise missiles from ship containers - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>https://www.scmp.com/news/china/military/article/3341929/will-new-chinas-yj-18c-missile-be-logistics-killer-us-navy</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Will China's YJ-18C missile be a logistics killer - SCMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ivan-papanin-kalibr-k</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Project 23550 Ivan Papanin Kalibr-K Container Module</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ivan Papanin containerized Kalibr, Project 23550 combat icebreaker</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Admiralty Shipyards / Morinformsystem-Agat lineage</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>October 2021</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Naval News detailed the containerized-bay design; lead ship commissioned Sept 2025</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Naval arsenal</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Modular deck launcher</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Purpose-built Arctic combat icebreaker/patrol ship with an open stern flex-bay designed to accept containerized Kalibr-K cruise-missile or Kh-35 anti-ship modules (up to 8 missiles); Russia's first near-operational Club-K-style warship fit.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Missile module reportedly not yet installed at commissioning (only the 76mm gun fitted); deck pre-wired for retrofit.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2021/10/russia-arctic-patrol-ship-cruise-missiles/</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Russia's Arctic Patrol Ships to Feature Cruise Missiles - Naval News</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/navy-news/2024/russian-navys-new-ivan-papanin-project-23550-combat-icebreaker-begins-sea-trials-with-kalibr-missiles</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ivan Papanin begins sea trials with Kalibr - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cm-300la</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Iran CM-300LA Land-Attack Container Launcher</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CM-300LA, Container Missile-300 Land Attack</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Iranian defence industry (AIO/Shahid Bagheri lineage)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>September 2025</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Shown at PARTNER 2025 exhibition (Belgrade)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Covert strike</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>A three-round canister built to mimic a standard 20-ft ISO container on a civilian-style 6x6 truck, firing a subsonic (~300 km) sea-skimming land-attack cruise missile; onboard power, auto-leveling and shoot-and-scoot salvo capability.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Reported by three trade outlets from the same unveiling; no TWZ/Naval News/Janes coverage yet.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/iran-presents-cm-300la-land-attack-container-launcher-firing-three-cruise-missiles-in-minutes</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Iran Presents CM-300LA Land-Attack Container Launcher - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>https://milivox.media/iran-cm300la-cruise-missile-container-launcher/</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Iran Unveils CM-300LA Containerized Cruise Missile Launcher - Milivox</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>shahed-136-container-launcher</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Iran Shahed-136 Tilting Container Drone Launcher</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Shahed-136 catapult-container system, Great Prophet 17 launcher</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HESA / IRGC Aerospace Force</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2021-12-24</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>December 2021</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Unveiled during Great Prophet 17 exercise</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Loitering munition</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>A tilting truck-mounted container-like box holding up to five Shahed-136 loitering munitions, each rocket-boosted into flight; container form factor allows palletizing onto rail cars, ships or other vehicles.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Well corroborated; distinct from later no-container pickup-truck launch method.</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>https://iranprimer.usip.org/blog/2021/dec/28/irgc-tests-ballistic-missiles-drones-war-game</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>IRGC Tests Ballistic Missiles, Drones in War Game - USIP</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>https://militarnyi.com/en/news/shahed-loitering-munition-received-the-capability-to-be-launched-from-a-vehicle/</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Shahed launched from a vehicle - Militarnyi</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>shahid-roudaki</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Iran Shahid Roudaki Twin Container Anti-Ship Launchers</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Shahid Roudaki forward-base ship container launchers, Qader/Ghadir deck launchers</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IRGC Navy (converted from merchant Galaxy F)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2020-11-19</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>November 2020</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Commissioning ceremony reveal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Naval arsenal</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Modular deck launcher</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Four twin box/container-style launchers (eight Qader/Ghadir anti-ship cruise missiles) bolted to the forward deck of a converted forward-base ship, alongside road-mobile radar.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>H.I. Sutton flagged some displayed equipment may have been staged for the ceremony rather than integrated.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>https://www.hisutton.com/Iranian-IRGC-Forward-Base-Shahid-Roudaki.html</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Iranian IRGC Forward Base Shahid Roudaki - Covert Shores</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>https://news.usni.org/2020/11/19/video-iran-inducts-new-special-operations-ship</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Iran Inducts New Special Operations Ship - USNI</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>hezbollah-container-launcher</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hezbollah Container-Concealed Launcher Trucks</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Hezbollah closed-container hydraulic launcher, Paveh-351 container truck</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Hezbollah (Iranian-supplied)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2022-11-01</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Documented doctrine; Nov 2022 Israeli strike on a Paveh container truck</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Covert / disguised</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Concealed cargo</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Hezbollah mounts Iranian-supplied rockets/cruise missiles on civilian trucks within closed containers that open hydraulically to erect and fire, dispersed in populated areas for survivability.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Described launch method/doctrine (Alma Research) rather than one photographed named system; secondary confirmation thinner.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>https://israel-alma.org/hezbollahs-heavy-rocket-array-medium-range-up-to-200-km-and-its-ballistic-missile-array-constitute-strategic-capabilities-of-the-organization/</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Hezbollah's heavy rocket array - Alma Research</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>https://israel-alma.org/iranian-paveh-cruise-missile-351-supplied-to-lebanese-hezbollah/</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Iranian Paveh Cruise Missile supplied to Hezbollah - Alma Research</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>hwasal-2-container</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>North Korea Hwasal-2 Container Cruise-Missile Launcher</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hwasal-2 angled container launcher, Amnok-class corvette cruise-missile box</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>North Korean state defence industry</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>North Korea (DPRK)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>August 2023</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Naval version revealed on Amnok-class corvette; ground debut Oct 2021</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Strike missile</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Nuclear-capable land-attack cruise missile (~1,500-2,000 km) launched from an angled, box-like container rather than a VLS; seen in a 5-tube road-mobile launcher and an 8-tube aft-deck fit on the Amnok-class corvette.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Ambiguity over whether 'container' means a true ISO box or an inclined canister bank.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Hwasal-2</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Hwasal-2 - Wikipedia</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2023/08/north-korea-new-cruise-missile-amnok-class-corvette/</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>North Korea reveals cruise missile-armed corvette - Naval News</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>dprk-harop-launcher</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>North Korea Harop-Type Loitering Munition Container Launcher</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>DPRK Harop-clone container launcher, six-cell suicide-drone box</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>North Korean state defence industry</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>North Korea (DPRK)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>October 2025</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Displayed at Pyongyang parade (80th WPK anniversary)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Loitering munition</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>A 6x6 armored truck carrying two rows of three container-style launch cells for Harop-style kamikaze drones, marking a shift from 2024's bare-airframe reveal to fieldable launch hardware.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Single-source detailed reporting; technical detail relies on analyst inference.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/north-korea-rolls-out-harop-type-loitering-munition-launcher-in-pyongyang-parade</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>North Korea rolls out Harop-type loitering munition launcher - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>https://militarnyi.com/en/news/north-korea-presents-launcher-for-copies-of-israeli-harop-kamikaze-drones/</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>North Korea Presents Launcher for Harop Copies - Militarnyi</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>thor-hpm</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>THOR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Tactical High-power Operational Responder</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Air Force Research Laboratory (AFRL)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Development and swarm-defeat testing at Kirtland AFB</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>High-power microwave counter-swarm weapon stored in a standard 20-ft ISO container, C-130 transportable, set up in hours for airbase point defense against drone swarms.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Follow-on is Mjolnir (Leidos).</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/thor-microwave-anti-drone-system-downs-swarms-in-test</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>THOR Microwave Anti-Drone System Downs Swarms - TWZ</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>https://www.airandspaceforces.com/air-forces-thor-drone-swarm-demo/</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>THOR Hammers Drone Swarm - Air &amp; Space Forces Magazine</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/THOR_(weapon)</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>THOR (weapon) - Wikipedia</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>mjolnir-hpm</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Mjolnir</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>THOR follow-on high-power microwave</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Leidos / Air Force Research Laboratory</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2021-03-01</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Development contract award</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Next-generation high-power microwave counter-swarm weapon derived from THOR, packaged in a transportable ISO container.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Container form-factor inherited from THOR.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://afresearchlab.com/technology/directed-energy/</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>AFRL Directed Energy</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>https://www.leidos.com/insights/leidos-awarded-contract-develop-next-generation-high-power-microwave-weapon</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leidos next-gen HPM weapon - Leidos</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>epirus-leonidas</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Epirus Leonidas (IFPC-HPM)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Leonidas, IFPC-HPM, Indirect Fire Protection Capability-High Power Microwave</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Epirus Inc.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>January 2023</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>US Army selection ($66.1M); prototypes delivered 2023-2024</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Solid-state GaN high-power microwave system that disables drone swarms; the base/IFPC-HPM unit fits inside a standard 20-ft container. Live-fire demo Aug 2025 downed 61 drones.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Only the base/IFPC-HPM version is containerized; Mobile/Pod/Expeditionary variants are not.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://breakingdefense.com/2025/02/high-power-microwave-force-field-knocks-drone-swarms-from-sky/</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>HPM force field knocks drone swarms from sky - Breaking Defense</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>https://www.defensedaily.com/ifpc-hpm-prototype-deliveries-complete-epirus-eyes-engineering-tests-ahead-of-potential-deployment/army/</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>IFPC-HPM Prototype Deliveries Complete - Defense Daily</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>liteye-c-auds</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Liteye C-AUDS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C-AUDS, Containerized Anti-UAS Defense System</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Liteye Systems (integrating UK AUDS tech)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2018-09-05</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>September 2018</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>USAF follow-on contract; production units delivered Dec 2018</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Air defense / C-UAS</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Integrates AUDS radar (Blighter), EO/IR tracker (Chess Dynamics) and RF-jamming effector (optional kinetic add-on) into a self-contained 20-ft ISO container for base and critical-infrastructure defense.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Base AUDS is vehicle/trailer-mounted; only the C-AUDS repackaging is a true container.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://equipment.adsinc.com/</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Liteye C-AUDS product page - ADS</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>https://www.unmannedairspace.info/</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Blighter to supply C-UAS radar to Liteye - Unmanned Airspace</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dzyne-blitzbox</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DZYNE BlitzBox</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BlitzBox, Blitz drone container launcher</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DZYNE Technologies</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Unveiled at SOF Week</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Loitering munition</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Concealed cargo</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>An ordinary-looking shipping container hiding a launch system for DZYNE's Blitz Group-1 expendable swarming drones; a 10-ft container holds 16 drones on 4 rail launchers, a 40-ft container up to 100.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>TWZ direct interview with DZYNE program manager.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>BlitzBox Packs 100 Weaponized Drones Into A Container - TWZ</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>https://www.slashgear.com/</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>A Container Full Of 100 Deadly Drones - SlashGear</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>dragonfire</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>DragonFire</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DragonFire laser directed-energy weapon</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>MBDA UK / Leonardo UK / QinetiQ / Dstl</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2024-01-19</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>January 2024</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>First UK high-power live firing vs aerial targets (Hebrides Range)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>50kW-class laser weapon whose land-trial unit is described as roughly the size of a TEU shipping container; £316m production contract (Nov 2025) to arm Royal Navy Type 45 destroyers by 2027.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Shipboard-fitted version's exact housing less certain than the land-test container configuration.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://www.naval-technology.com/news/dragonfire-uk-royal-navy-to-get-ships-with-laser-beams-by-2027/</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>DragonFire: Royal Navy laser by 2027 - Naval Technology</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>https://breakingdefense.com/2024/01/in-first-uk-test-fires-13-per-strike-dragonfire-laser-weapon-against-aerial-targets/</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>UK test fires DragonFire laser - Breaking Defense</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>rheinmetall-mbda-lwd</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Rheinmetall/MBDA Laser Weapon Demonstrator</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LWD, 20kW naval laser demonstrator</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Rheinmetall + MBDA Deutschland</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>October 2022</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Installed on frigate Sachsen; sea trials 2022-2023</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>20kW-scalable laser demonstrator with turret and support equipment housed in a standard 20-ft container, craned onto the frigate Sachsen for a year of at-sea firing trials against drones and small boats.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>In-service target ~2029.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2025/10/rheinmetall-and-mbda-german-laser-weapon-system-close-to-market-readiness/</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>German laser weapon close to market readiness - Naval News</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>https://www.edrmagazine.eu/mbda-deutschland-provided-new-details-on-the-laser-weapon-demonstrator</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>MBDA Laser Weapon Demonstrator details - EDR Magazine</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>iron-beam</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Iron Beam</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Magen Or, Light Shield, Iron Beam 450</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Rafael Advanced Defense Systems (Elbit laser source)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>December 2025</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>First operational unit delivered to IDF</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>100kW-class laser (ten fused 10kW fiber lasers) with a dome turret; beam-generation and cooling equipment described as housed in two 40-ft container-like modules, generally stationary but relocatable.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>The 'two 40-ft container modules' phrasing recurs in secondary sources but primary ISO-container wording not verified.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Iron_Beam</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Iron Beam - Wikipedia</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/rafael-delivers-israels-first-operational-iron-beam-laser-shield-to-revolutionize-air-defense-era</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Rafael Delivers First Operational Iron Beam - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>silent-hunter</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Silent Hunter</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Shen Nu, Silent Hunter laser air-defence</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Poly Technologies</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2017-02-01</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>February 2017</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Unveiled at IDEX 2017; Saudi operational use vs Houthi drones</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>30-100kW-class anti-drone fiber laser; the mobile version is described as installed in a container towed by a 6x6 truck. Exported to the UAE/Saudi Arabia.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Some sources describe it as separate truck-sized power and equipment units rather than a clear ISO box.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Silent_Hunter_(laser_weapon)</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Silent Hunter (laser weapon) - Wikipedia</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>https://armyrecognition.com/news/army-news/army-news-2024/dsa-2024-chinese-company-poly-technologies-showcases-silent-hunter-laser-defense-system</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Poly Technologies showcases Silent Hunter - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cheongwang-skylight</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cheongwang (Skylight) Laser</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cheongwang, Skylight, Block-I laser air-defense</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Hanwha Aerospace with ADD</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>December 2024</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Initial operational fielding (Seoul area and frontline)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>World's first laser weapon to reach operational military deployment; a 20kW fiber laser fully housed in a container-sized unit (~9m x 3m x 3m) with integrated radar mast, for point air-defense against small drones over Seoul.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Army Recognition explicitly calls it container-sized.</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>https://armyrecognition.com/news/army-news/army-news-2024/south-korea-commissions-cheongwang-its-most-modern-laser-system-to-counter-aerial-threats</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>South Korea Commissions Cheongwang Laser - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/south-korea-deploys-skylight-laser-weapon-to-protect-seoul-capital-and-frontline-areas-from-north-korean-drones</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>South Korea deploys Skylight laser - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>kawasaki-hel</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Kawasaki 100kW Laser C-UAS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>KHI Electric-Drive High-Power Laser System</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Kawasaki Heavy Industries (KHI)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>December 2025</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Installed aboard JMSDF test ship JS Asuka</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>100kW-class laser (ten fused 10kW fiber lasers) for counter-UAS, packaged into two 40-ft ISO container modules with a domed turret, installed on JS Asuka's deck for maritime trials.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Prototype delivered to Japan MoD Feb 2023.</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2025/12/high-energy-laser-system-spotted-aboard-jmsdf-test-ship/</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>High-Energy Laser Aboard JMSDF Test Ship - Naval News</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/industry/dsei-japan-2023-kawasaki-heavy-industries-unveils-high-energy-laser-c-uas</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>KHI unveils high-energy laser C-UAS - Janes</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>edge-skyshield</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EDGE SKYSHIELD</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SKYSHIELD, SKYSHIELD-TM C-UAS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SIGN4L (EDGE Group)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2023-02-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>February 2023</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Unveiled at IDEX 2023</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Air defense / C-UAS</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>A multi-layered C-UAS solution (3D radar, EO/IR, RF direction-finders, jammers) networked into a unified C2 system, housed in a shock-proof, sealed container/cabinet for fixed or rapidly-deployable use; UAE MoD contract announced ~2024.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Sources describe a compact shock-proof container/cabinet rather than confirmed full ISO dimensions.</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>IDEX 2023: EDGE launches SKYSHIELD C-UAS - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>https://www.sign4l.ae/</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SKYSHIELD Counter-UAS - SIGN4L</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>knds-drone-container</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>KNDS Containerized Drone Launcher</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>KNDS drone launch container, Helsing HX-2 / Tytan TI-1 METIS container</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>KNDS (France/Germany) with Helsing and Tytan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>France / Germany</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Demonstrator unveiled at Eurosatory 2026</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Loitering munition</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>A self-contained 20-ft ISO container with independent power, environmental control and networking, housing dozens to 100+ effectors combining Helsing HX-2 strike drones and Tytan TI-1 METIS hard-kill interceptor drones; pitched as a response to Ukraine's Operation Spiderweb.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Mock-up demonstrator/concept, not yet fielded; dual strike + interceptor role.</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>KNDS unveils containerized drone launcher concept - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>https://www.euro-sd.com/</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>KNDS showcases C-UAV capabilities at Eurosatory 2026 - ESD</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>destinus-hornet-b1</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Destinus Hornet Block 1 Containerized Interceptor</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hornet B1, Destinus containerized interceptor drone launcher</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Destinus</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Switzerland (tested by Spain)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Test-fired aboard frigate Santa Maria and in land container config</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Air defense / C-UAS</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Canister-launched hard-kill interceptor drone engaging subsonic UAVs/swarms, fired from a modular containerized launch unit demonstrated on both a ship's deck and a land container configuration.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Clearest verified containerized interceptor-drone launcher found.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Spanish Navy Tests Hornet Block 1 from Santa Maria Frigate - Naval News</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>https://thedefensepost.com/</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Spanish Army Tests Destinus Hornet B1 in Container Launch Config - The Defense Post</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>roketsan-kara-atmaca</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Roketsan Kara Atmaca Container Launcher</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Kara Atmaca, ATMACA-UM Container Launch System</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Roketsan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>July 2025</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Unveiled at IDEF 2025 (Istanbul)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Covert strike</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>A launcher disguised as an ordinary 20/40-ft commercial container, firing up to six Kara Atmaca land-attack/anti-ship cruise missiles (~250-280 km, 220kg warhead), movable by truck, rail or civilian cargo vessel.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Roketsan states it is fully operational; multiple independent outlets confirm the container form factor.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/tuerkiye-debuts-kara-atmaca-container-launcher-at-idef-2025-for-covert-and-mobile-land-based-strike-roles</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Turkiye Debuts Kara Atmaca Container Launcher at IDEF 2025 - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>https://interestingengineering.com/military/shipping-containers-into-surprise-missile-launchers</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Turkey turns cargo container into missile-in-a-box - Interesting Engineering</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>roketsan-eren</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Roketsan EREN Containerized Loitering Munition Launcher</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EREN Container Launch System, Roketsan EREN ground launcher</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Roketsan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>July 2025</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Unveiled at IDEF 2025 (Istanbul)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Loitering munition</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>A truck-mounted launcher disguised as a civilian freight container, concealing up to 12 EREN jet-powered dual-role (anti-air/anti-ground) loitering munitions (35kg, &gt;100 km); serial production planned for 2026.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Multiple independent outlets confirm the container disguise and IDEF 2025 debut.</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/defense-news-army-2025/roketsan-debuts-containerized-eren-loitering-munition-launcher-at-idef-2025-for-covert-deep-strikes</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Roketsan Debuts Containerized EREN Launcher at IDEF 2025 - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>https://united24media.com/latest-news/inspired-by-ukraines-operation-spiderweb-turkey-unveils-hidden-drone-launcher-for-deep-strikes-10361</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Turkey Unveils Hidden Drone Launcher for Deep Strikes - United24</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>elbit-skystriker-container</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Elbit SkyStriker Containerized Launcher</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SkyStriker container launch configuration</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Elbit Systems</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2022-06-15</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Container launch configuration publicized (approximate)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Loitering munition</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Electrically powered canister-launched loitering munition (up to 100 km, 10kg warhead); Elbit markets a container launch configuration packing 6 SkyStriker rounds per container for land or naval deployment.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Container figure from Elbit product literature rather than a dedicated show unveiling; reveal date approximate.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://www.elbitsystems.com/sites/default/files/2025-02/skystriker.pdf</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Elbit SkyStriker datasheet</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>https://www.battlepolicy.com/skystriker/</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SkyStriker Israel's electric loitering munition - Battle Policy</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>elbit-trigon</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Elbit TRIGON Sea-to-Shore Weapon System</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TRIGON naval rocket and missile launcher</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Elbit Systems</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Earliest trade-press coverage (approximate)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Naval arsenal</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Modular deck launcher</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>A fixed-elevation deck-mounted launcher carrying two pods of four EXTRA guided rockets (150 km) each, installable permanently or as an add-on mission module above or below deck on small-to-medium naval craft.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Elbit describes it as a bolt-on deck mission module rather than an explicit ISO container; container claim less firmly documented.</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>https://elbitsystems.com/product/trigon/</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>TRIGON Sea-to-Shore Weapon System - Elbit</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>https://www.asianmilitaryreview.com/2017/06/imi-systems-solutions-extend-modern-naval-capabilities/</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>IMI Systems naval solutions - Asian Military Review</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>northrop-ares</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Northrop Grumman AReS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AReS, Advanced Reactive Strike, containerized ground-launched AARGM-ER</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Northrop Grumman</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>January 2025</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Unveiled at Surface Navy Association Symposium</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Strike missile</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>A 20/40-ft ISO container concealing a four-cell vertical launcher for ground-launched AARGM-ER anti-radiation missiles (~150 km), aimed at rapidly deployable suppression of enemy radar and air-defense sites.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Northrop and Hanwha signed an MOA (Apr 2026) to co-develop an AReS rocket booster.</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/new-northrop-grumman-ares-missile-launcher-enables-fast-deployment-against-enemy-radar</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>New Northrop Grumman AReS missile launcher - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>https://www.fw-mag.com/shownews/351/sna-2025-sees-northrop-grumman-push-ares-a-containerized-ground-launched-aargm-er</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SNA 2025: Northrop Grumman push AReS - FW-MAG</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ruta-block-3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Rheinmetall Destinus Ruta Block 3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ruta Block 3, RUTA Block III deep-strike cruise missile</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Rheinmetall Destinus Strike Systems</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Germany / Switzerland-Spain</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>June 2026</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Unveiled at Eurosatory 2026</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Strike missile</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>A strategic deep-strike cruise missile (&gt;2,000 km, 250 kg warhead) launched exclusively from standard ISO shipping containers on vehicle (Rheinmetall HX truck) or maritime platforms, reaching firing readiness in ~2 minutes.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Flight testing not scheduled until 2027; 100% European value chain targeted.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>https://defence-industry.eu/rheinmetall-destinus-strike-systems-outlines-european-cruise-missile-priorities-with-ruta-block-3-and-initial-production/</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Rheinmetall Destinus Ruta Block 3 priorities - Defence Industry Europe</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>https://www.army-technology.com/news/rheinmetall-destinus-cruise-missile/</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Rheinmetall, Destinus 2,000km cruise missile - Army Technology</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cm-401</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CM-401 Containerized Deck Launcher</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CM-401 anti-ship ballistic missile, CASIC CM-401 deck launcher</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CASIC (China Aerospace Science &amp; Industry Corp)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2018-11-06</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>November 2018</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Unveiled at Zhuhai Airshow China 2018</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Missile launcher</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Supersonic (Mach 4-6) anti-ship ballistic missile offered in a container-form deck launcher for surface ships (as well as an 8x8 truck TEL); pitched from 2025 for export coastal-defence use.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Rebranded in army livery for coastal-defence export at IndoDefence 2025.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/24699/china-reveals-short-range-anti-ship-ballistic-missile-designed-to-dodge-enemy-defenses</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>China Reveals Short-Range Anti-Ship Ballistic Missile - TWZ</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>https://armyrecognition.com/news/army-news/2025/indodefence-2025-china-promotes-cm-401-anti-ship-missile-as-coastal-defense-for-foreign-customers</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>IndoDefence 2025: China promotes CM-401 as coastal defense - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>saab-rbs15-cdms</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Saab Coastal Defence Missile System (RBS15 CDMS)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Saab CDMS, RBS15 containerized coastal launcher</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Saab</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>September 2025</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Publicly unveiled; on order for Swedish Armed Forces</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Artillery / coastal</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>A truck-carried launcher matching the footprint of a 20-ft ISO container, holding four RBS15 Mk3/Mk4 anti-ship missiles (&gt;300 km) with a shoot-and-scoot relocation under 120 seconds.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>RBS15 fielded across Sweden, Finland, Germany, Poland, Bulgaria, Croatia.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://www.saab.com/newsroom/stories/2025/september/a-powerful-new-deterrent-to-seaborne-threats</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>A powerful new deterrent to seaborne threats - Saab</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/navy-news/2025/saabs-new-coastal-defense-system-built-on-rbs15-missile-targets-growing-maritime-threats</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Saab's New Coastal Defense System - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>iris-t-slm-container</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Diehl IRIS-T SLM Containerized Fire Unit</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IRIS-T SLM, IRIS-T SL container launcher/radar/TOC</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Diehl Defence</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>First fire unit delivered to German Armed Forces</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Air defense / C-UAS</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>IRIS-T SLM fire units (launcher, TRML-4D radar and IBMS tactical operations centre) are each built on standardised 20-ft ISO container frames for road/rail/sea/air transport; unmanned launchers reach readiness in 10 minutes.</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Widely fielded to Ukraine and the Bundeswehr; container-frame design confirmed by multiple sources.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://defence-industry.eu/diehl-defence-delivers-first-unit-of-iris-t-slm-system-to-german-armed-forces/</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Diehl delivers first IRIS-T SLM unit to German Armed Forces - Defence Industry Europe</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/diehl-defence-delivers-first-iris-t-slm-air-defense-system-to-german-army</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Diehl delivers first IRIS-T SLM to German Army - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>boeing-clws</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Boeing Compact Laser Weapon System (containerized)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CLWS, Boeing containerized laser weapon</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>June 2024</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Demonstrated in containerized config at Canada's IDEaS C-UAS Sandbox</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Directed energy</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>A fixed containerized configuration of Boeing's 5kW-class Compact Laser Weapon System, paired with radar cueing to detect, track and defeat FPV drones, mortar rounds and a five-UAS swarm at 200m-2.5km in Canadian trials.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Tested alongside a Polaris RZR-mounted CLWS unit; hosted by DRDC at CFB Suffield.</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://www.boeing.com/features/2024/06/boeings-compact-lasers-shine-at-counter-drone-competition</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Boeing's compact lasers at counter-drone competition - Boeing</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>https://www.unmannedairspace.info/counter-uas-systems-and-policies/boeings-compact-laser-weapon-system-features-in-canadas-ideas-c-uas-trials/</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Boeing CLWS in Canada's IDEaS C-UAS trials - Unmanned Airspace</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>navypods-strike</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Royal Navy NavyPODS (Strike POD)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PODS, Persistent Operational Deployment System, Strike POD</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>G3 Systems / QinetiQ for Royal Navy</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>September 2021</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Concept unveiled at DSEI 2021</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Modular system</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>A 20-ft ISO container-footprint modular payload system for RN vessels; the Strike POD variant hosts launchers for armed UAVs or loitering munitions plus a mission-planning area, part of an 18+ POD family.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Armed Strike POD remains a low-TRL demonstrator; G3 Systems selected as preferred supplier Nov 2025.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://www.navylookout.com/thinking-inside-the-box-the-royal-navys-containerised-capability-concept/</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Royal Navy's containerised capability concept - Navy Lookout</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2025/11/g3-systems-selected-as-the-preferred-supplier-to-upgrade-navypods-capability/</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>G3 Systems preferred supplier for NavyPODS - Naval News</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>elbit-seagull-usv</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Elbit Seagull USV</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Seagull MCM/ASW USV, Seagull Mk3</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Elbit Systems</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>February 2025</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>4th-gen Seagull showcased at NAVDEX 2025</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Autonomous vehicle</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>A 12m multi-mission unmanned surface vessel (MCM/ASW/EW) that ships and deploys from a standard 40-ft ISO container; the planned 20m Mk3 adds deck space for a standardised 20-ft ISO container payload.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>100% success in Royal Navy WISEX mine-hunting trials.</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>https://www.elbitsystems.com/unmanned/maritime/unmanned-surface-vessel/seagull-usv</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Seagull USV - Elbit Systems</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/sea/navdex-2025-elbit-system-showcases-fourth-generation-seagull-usv</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>NAVDEX 2025: 4th-gen Seagull USV - Janes</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>blacksea-chaser-usv</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BlackSea Technologies Chaser USV</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Chaser, GARC Block II</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BlackSea Technologies</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>April 2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Unveiled at Sea-Air-Space 2026</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Autonomous vehicle</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>A modular unmanned surface vessel engineered to fit inside and deploy from a standard 20-ft ISO container per a US Navy transportability requirement; carries JAGM launchers and EO/radar sensors.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Built on ~5,000 operational hours of the earlier GARC design; unveiled alongside the larger Comet USV.</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2026/05/video-new-comet-and-chaser-usv-by-blacksea-technologies/</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>New Comet and Chaser USV by BlackSea Technologies - Naval News</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>https://www.blacksea.tech/chaser</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Chaser - BlackSea Technologies</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>speartooth-luuv</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>C2 Robotics Speartooth LUUV</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Speartooth, C2 Robotics long-range LUUV</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>C2 Robotics</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>First unit delivered to US Navy</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Autonomous vehicle</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>A long-range (2,000 km), 2,000m-depth large uncrewed undersea vehicle purpose-built to ship inside and deploy from a standard container via ramp or austere coastal infrastructure, without dedicated submarine support; ISR, mine warfare and strike delivery.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Follows a 2025 NUWC Newport order for three long-range LUUVs.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/navy-news/2026/us-navy-receives-first-australian-speartooth-luuv-drone-for-autonomous-underwater-strikes</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>US Navy receives first Australian Speartooth LUUV - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>https://www.navaltoday.com/2026/05/05/australian-firm-commissions-first-us-export-luuv/</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Australian firm commissions first US export LUUV - Naval Today</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>xv-excalibur</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>XV Excalibur XLUUV</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Project Cetus XLUUV, Excalibur</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MSubs Ltd / UK Submarine Delivery Agency</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>December 2025</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Handed over to Royal Navy</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Autonomous vehicle</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>A 12m, ~19-25 tonne extra-large uncrewed underwater vehicle technology testbed, sized to be transported worldwide inside a standard 40-ft shipping container; controlled submerged from a remote centre in Australia during Talisman Sabre 2025.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Culmination of Project Cetus; payload bay can carry mines, smaller UUVs, sensors.</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2026/01/autonomous-submarine-xv-excalibur-handed-to-royal-navy/</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Autonomous submarine XV Excalibur handed to Royal Navy - Naval News</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>https://www.naval-technology.com/news/royal-navy-name-project-cetus-xluuv-excalibur/</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Royal Navy name Project Cetus XLUUV Excalibur - Naval Technology</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>bluewhale-uuv</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>IAI/tkMS BlueWhale UUV</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BlueWhale AUV/XLUUV</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Israel Aerospace Industries / thyssenkrupp Marine Systems</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Israel / Germany</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>February 2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Delivered to German Navy at Eckernforde</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Autonomous vehicle</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>A 10.9m, 5.5-tonne autonomous underwater vehicle for ASW support, minehunting and covert ISR, engineered to be transported inside a standard 40-ft shipping container for deployment by land, air or sea; 10-30 day endurance to 300m depth.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Delivered under Germany's Kurs Marine 2035+ program after a 2-week German Navy trial.</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>https://www.tkmsgroup.com/news/article/autonomous-underwater-vehicle-bluewhale-handed-over-to-german-navy-delivery-by-tkms-and-israel-aerospace-industries-as-part-of-the-kurs-marine-2035-program</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>BlueWhale AUV handed over to German Navy - TKMS Group</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/navy-news/2026/germanys-new-bluewhale-autonomous-underwater-vehicle-is-transforming-baltic-maritime-surveillance</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Germany's BlueWhale AUV - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>anduril-slb-500m</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Anduril Surface-Launched Barracuda-500M</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SLB-500M, Surface-Launched Barracuda</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Anduril Industries</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Production agreement announcement</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Strike missile</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>A surface-launched Barracuda-500M variant paired with a standard 20-ft ISO launcher that can carry up to 16 rounds, for dispersed land and maritime strike; announced under the US Low-Cost Containerized Munitions effort.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>From ChatGPT deep-research set; corroborated by Anduril and Naval News.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>https://www.anduril.com/news/anduril-department-of-war-sign-production-agreement-for-surface-launched-barracuda-500m</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Anduril-DoW Production Agreement for SLB-500M - Anduril</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2026/05/massive-u-s-missile-order-may-expand-american-anti-ship-arsenal/</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Massive US Missile Order May Expand Anti-Ship Arsenal - Naval News</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>iai-diamond</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>IAI DIAMOND Distributed Warfare System</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DIAMOND, Distributed Warfare Solution</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Israel Aerospace Industries</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Official unveiling</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Modular system</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Modular deck launcher</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>A distributed-warfare architecture using container-footprint payload modules for ships and other platforms, able to host loitering munitions, Blue Spear, LORA, Barak MX and counter-UAS payloads in reconfigurable packages.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>From ChatGPT deep-research set. Architecture/family rather than a fixed single-munition launcher.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>https://www.iai.co.il/press/iai-unveils-diamond</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>IAI Unveils DIAMOND: New Distributed Warfare Solution - IAI</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>https://www.iai.co.il/product/diamond</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>DIAMOND - IAI</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>vampire-casket</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>L3Harris VAMPIRE CASKET</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>VAMPIRE CASKET, Containerized VAMPIRE counter-drone</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>L3Harris Technologies</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>October 2025</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Shown in L3Harris roadmap imagery</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Air defense / C-UAS</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Container form-factor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>A standard-container mounting of L3Harris's VAMPIRE counter-drone system, combining its sensor-and-launcher architecture with kinetic effectors including laser-guided 70mm rockets.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>From ChatGPT deep-research set. Depicted as a proposed family variant; dimensions/procurement/fielding limited.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/air/entire-family-of-vampire-counter-drone-systems-unveiled</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Entire Family Of VAMPIRE Counter-Drone Systems Unveiled - TWZ</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/systems.xlsx
+++ b/data/systems.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="systems" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="systems" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3461,10 +3461,26 @@
           <t>Distinct from the Zhong Da 79 arsenal-ship entry already in the list; this is the standalone containerized launcher product.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>images/csdcs.jpg</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Fan Wei / Global Times</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://www.globaltimes.cn/page/202211/1279349.shtml</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>https://www.globaltimes.cn/page/202211/1279349.shtml</t>
@@ -3562,10 +3578,26 @@
           <t>Traces to a single 2019 US-intel report; missile never officially shown separately from the container concept.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>images/yj-18c.jpg</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>CCTV News via Global Times</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://www.globaltimes.cn/page/202509/1342523.shtml</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>https://freebeacon.com/national-security/china-building-long-range-cruise-missile-launched-from-ship-container/</t>
@@ -3663,10 +3695,26 @@
           <t>Missile module reportedly not yet installed at commissioning (only the 76mm gun fitted); deck pre-wired for retrofit.</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>images/ivan-papanin-kalibr-k.jpg</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Alekc2m / Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:%D0%9B%D0%B5%D0%B4%D0%BE%D0%BA%D0%BE%D0%BB_%22%D0%98%D0%B2%D0%B0%D0%BD_%D0%9F%D0%B0%D0%BD%D0%B0%D0%BD%D0%B8%D0%BD%22_01.jpg</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>https://www.navalnews.com/naval-news/2021/10/russia-arctic-patrol-ship-cruise-missiles/</t>
@@ -3687,8 +3735,6 @@
           <t>Ivan Papanin begins sea trials with Kalibr - Army Recognition</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3756,10 +3802,26 @@
           <t>Reported by three trade outlets from the same unveiling; no TWZ/Naval News/Janes coverage yet.</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>images/cm-300la.jpg</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Army Recognition</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/iran-presents-cm-300la-land-attack-container-launcher-firing-three-cruise-missiles-in-minutes</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/news/army-news/2025/iran-presents-cm-300la-land-attack-container-launcher-firing-three-cruise-missiles-in-minutes</t>
@@ -3780,8 +3842,6 @@
           <t>Iran Unveils CM-300LA Containerized Cruise Missile Launcher - Milivox</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3849,10 +3909,26 @@
           <t>Well corroborated; distinct from later no-container pickup-truck launch method.</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>images/shahed-136-container-launcher.jpg</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Amin Ahouei / Tasnim News Agency, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sacred_Defence_Week_parade,_2023,_in_Tehran_(113).jpg</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>https://iranprimer.usip.org/blog/2021/dec/28/irgc-tests-ballistic-missiles-drones-war-game</t>
@@ -3873,8 +3949,6 @@
           <t>Shahed launched from a vehicle - Militarnyi</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3942,10 +4016,26 @@
           <t>H.I. Sutton flagged some displayed equipment may have been staged for the ceremony rather than integrated.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>images/shahid-roudaki.jpg</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Tasnim News Agency, via Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:IRIS_Shahid_Roudaki.jpg</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>https://www.hisutton.com/Iranian-IRGC-Forward-Base-Shahid-Roudaki.html</t>
@@ -3966,8 +4056,6 @@
           <t>Iran Inducts New Special Operations Ship - USNI</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4035,10 +4123,6 @@
           <t>Described launch method/doctrine (Alma Research) rather than one photographed named system; secondary confirmation thinner.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>https://israel-alma.org/hezbollahs-heavy-rocket-array-medium-range-up-to-200-km-and-its-ballistic-missile-array-constitute-strategic-capabilities-of-the-organization/</t>
@@ -4059,8 +4143,6 @@
           <t>Iranian Paveh Cruise Missile supplied to Hezbollah - Alma Research</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4128,10 +4210,26 @@
           <t>Ambiguity over whether 'container' means a true ISO box or an inclined canister bank.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>images/hwasal-2-container.jpg</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>KCNA via Army Recognition</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/north-korea-announces-successful-test-of-strategic-cruise-missile-hwasal-2</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Hwasal-2</t>
@@ -4152,8 +4250,6 @@
           <t>North Korea reveals cruise missile-armed corvette - Naval News</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4221,10 +4317,26 @@
           <t>Single-source detailed reporting; technical detail relies on analyst inference.</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>images/dprk-harop-launcher.jpg</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>KCNA via Army Recognition</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/north-korea-rolls-out-harop-type-loitering-munition-launcher-in-pyongyang-parade</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/news/army-news/2025/north-korea-rolls-out-harop-type-loitering-munition-launcher-in-pyongyang-parade</t>
@@ -4245,8 +4357,6 @@
           <t>North Korea Presents Launcher for Harop Copies - Militarnyi</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4314,10 +4424,26 @@
           <t>Follow-on is Mjolnir (Leidos).</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>images/thor-hpm.jpg</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>AFRL Directed Energy Directorate</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>public-domain-gov</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>https://afresearchlab.com/counter-swarm-high-power-weapon/</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>https://www.twz.com/thor-microwave-anti-drone-system-downs-swarms-in-test</t>
@@ -4415,10 +4541,6 @@
           <t>Container form-factor inherited from THOR.</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>https://afresearchlab.com/technology/directed-energy/</t>
@@ -4439,8 +4561,6 @@
           <t>Leidos next-gen HPM weapon - Leidos</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4508,10 +4628,26 @@
           <t>Only the base/IFPC-HPM version is containerized; Mobile/Pod/Expeditionary variants are not.</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>images/epirus-leonidas.jpg</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Epirus, Inc.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://www.epirusinc.com/press-releases/epirus-general-dynamics-land-systems-unveil-integrated-counter-electronics-system-stryker-leonidas</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>https://breakingdefense.com/2025/02/high-power-microwave-force-field-knocks-drone-swarms-from-sky/</t>
@@ -4532,8 +4668,6 @@
           <t>IFPC-HPM Prototype Deliveries Complete - Defense Daily</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4601,10 +4735,26 @@
           <t>Base AUDS is vehicle/trailer-mounted; only the C-AUDS repackaging is a true container.</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>images/liteye-c-auds.jpg</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Liteye Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2020/07/16/2063226/0/en/Liteye-C-AUDS-Chosen-to-Defend-Critical-Infrastructure-by-the-US-Government.html</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>https://equipment.adsinc.com/</t>
@@ -4625,8 +4775,6 @@
           <t>Blighter to supply C-UAS radar to Liteye - Unmanned Airspace</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4694,10 +4842,26 @@
           <t>TWZ direct interview with DZYNE program manager.</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>images/dzyne-blitzbox.jpg</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>DZYNE Technologies (via The War Zone)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/news-features/blitzbox-packs-100-weaponized-drones-into-an-unassuming-container</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>https://www.twz.com/</t>
@@ -4718,8 +4882,6 @@
           <t>A Container Full Of 100 Deadly Drones - SlashGear</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4787,10 +4949,26 @@
           <t>Shipboard-fitted version's exact housing less certain than the land-test container configuration.</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>images/dragonfire.jpg</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>UK Ministry of Defence / Crown Copyright (OGL v3.0)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Dragonfire_laser_system_test_firing.webp</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>https://www.naval-technology.com/news/dragonfire-uk-royal-navy-to-get-ships-with-laser-beams-by-2027/</t>
@@ -4811,8 +4989,6 @@
           <t>UK test fires DragonFire laser - Breaking Defense</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4880,10 +5056,26 @@
           <t>In-service target ~2029.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>images/rheinmetall-mbda-lwd.jpg</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Rheinmetall (via Naval News)</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2025/10/rheinmetall-and-mbda-german-laser-weapon-system-close-to-market-readiness/</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>https://www.navalnews.com/naval-news/2025/10/rheinmetall-and-mbda-german-laser-weapon-system-close-to-market-readiness/</t>
@@ -4904,8 +5096,6 @@
           <t>MBDA Laser Weapon Demonstrator details - EDR Magazine</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4973,10 +5163,26 @@
           <t>The 'two 40-ft container modules' phrasing recurs in secondary sources but primary ISO-container wording not verified.</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>images/iron-beam.jpg</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Rafael Advanced Defense Systems (via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Iron_beam_01.jpg</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Iron_Beam</t>
@@ -4997,8 +5203,6 @@
           <t>Rafael Delivers First Operational Iron Beam - Army Recognition</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5066,10 +5270,26 @@
           <t>Some sources describe it as separate truck-sized power and equipment units rather than a clear ISO box.</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>images/silent-hunter.jpg</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Army Recognition</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/dsa-2024-chinese-company-poly-technologies-showcases-silent-hunter-laser-defense-system</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Silent_Hunter_(laser_weapon)</t>
@@ -5090,8 +5310,6 @@
           <t>Poly Technologies showcases Silent Hunter - Army Recognition</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5159,10 +5377,26 @@
           <t>Army Recognition explicitly calls it container-sized.</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>images/cheongwang-skylight.jpg</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Army Recognition</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/south-korea-commissions-cheongwang-its-most-modern-laser-system-to-counter-aerial-threats</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>https://armyrecognition.com/news/army-news/army-news-2024/south-korea-commissions-cheongwang-its-most-modern-laser-system-to-counter-aerial-threats</t>
@@ -5183,8 +5417,6 @@
           <t>South Korea deploys Skylight laser - Army Recognition</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5252,10 +5484,26 @@
           <t>Prototype delivered to Japan MoD Feb 2023.</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>images/kawasaki-hel.jpg</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Koji Miyake / Shephard Media</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://www.shephardmedia.com/news/landwarfareintl/kawasaki-develops-c-uas-laser-system-for-japanese-military/</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
           <t>https://www.navalnews.com/naval-news/2025/12/high-energy-laser-system-spotted-aboard-jmsdf-test-ship/</t>
@@ -5276,8 +5524,6 @@
           <t>KHI unveils high-energy laser C-UAS - Janes</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5345,10 +5591,26 @@
           <t>Sources describe a compact shock-proof container/cabinet rather than confirmed full ISO dimensions.</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>images/edge-skyshield.jpg</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>EDGE Group (via The Defense Post)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://thedefensepost.com/2023/02/22/edge-skyshield-counter-drone/</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/</t>
@@ -5369,8 +5631,6 @@
           <t>SKYSHIELD Counter-UAS - SIGN4L</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5438,10 +5698,26 @@
           <t>Mock-up demonstrator/concept, not yet fielded; dual strike + interceptor role.</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>images/knds-drone-container.jpg</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>KNDS Group</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>https://knds.com/en/press-releases/bolstering-mission-solution-portfolio-knds-showcases-first-drone-launch-container-prototype-at-eurosatory-2026-1</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/</t>
@@ -5462,8 +5738,6 @@
           <t>KNDS showcases C-UAV capabilities at Eurosatory 2026 - ESD</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5531,10 +5805,26 @@
           <t>Clearest verified containerized interceptor-drone launcher found.</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>images/destinus-hornet-b1.jpg</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Artvill / Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Destinus_Hornet_au_Salon_du_Bourget_2025_1.jpg</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>https://www.navalnews.com/</t>
@@ -5555,8 +5845,6 @@
           <t>Spanish Army Tests Destinus Hornet B1 in Container Launch Config - The Defense Post</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5624,10 +5912,26 @@
           <t>Roketsan states it is fully operational; multiple independent outlets confirm the container form factor.</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>images/roketsan-kara-atmaca.jpg</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Army Recognition Group</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/tuerkiye-debuts-kara-atmaca-container-launcher-at-idef-2025-for-covert-and-mobile-land-based-strike-roles</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/news/army-news/2025/tuerkiye-debuts-kara-atmaca-container-launcher-at-idef-2025-for-covert-and-mobile-land-based-strike-roles</t>
@@ -5648,8 +5952,6 @@
           <t>Turkey turns cargo container into missile-in-a-box - Interesting Engineering</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5717,10 +6019,26 @@
           <t>Multiple independent outlets confirm the container disguise and IDEF 2025 debut.</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>images/roketsan-eren.jpg</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Army Recognition Group</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://armyrecognition.com/news/army-news/2025/roketsan-debuts-containerized-eren-loitering-munition-launcher-at-idef-2025-for-covert-deep-strikes</t>
+        </is>
+      </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/archives/archives-land-defense/defense-news-army-2025/roketsan-debuts-containerized-eren-loitering-munition-launcher-at-idef-2025-for-covert-deep-strikes</t>
@@ -5741,8 +6059,6 @@
           <t>Turkey Unveils Hidden Drone Launcher for Deep Strikes - United24</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5810,10 +6126,26 @@
           <t>Container figure from Elbit product literature rather than a dedicated show unveiling; reveal date approximate.</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>images/elbit-skystriker-container.jpg</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Boevaya mashina / Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Elbit_Systems_SkyStriker_SIAF-2022.jpg</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>https://www.elbitsystems.com/sites/default/files/2025-02/skystriker.pdf</t>
@@ -5834,8 +6166,6 @@
           <t>SkyStriker Israel's electric loitering munition - Battle Policy</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5903,10 +6233,26 @@
           <t>Elbit describes it as a bolt-on deck mission module rather than an explicit ISO container; container claim less firmly documented.</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>images/elbit-trigon.jpg</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Elbit Systems</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://elbitsystems.com/product/trigon/</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr">
         <is>
           <t>https://elbitsystems.com/product/trigon/</t>
@@ -5927,8 +6273,6 @@
           <t>IMI Systems naval solutions - Asian Military Review</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5996,10 +6340,26 @@
           <t>Northrop and Hanwha signed an MOA (Apr 2026) to co-develop an AReS rocket booster.</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>images/northrop-ares.jpg</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Army Recognition Group</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2025/new-northrop-grumman-ares-missile-launcher-enables-fast-deployment-against-enemy-radar</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/news/army-news/2025/new-northrop-grumman-ares-missile-launcher-enables-fast-deployment-against-enemy-radar</t>
@@ -6020,8 +6380,6 @@
           <t>SNA 2025: Northrop Grumman push AReS - FW-MAG</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6089,10 +6447,26 @@
           <t>Flight testing not scheduled until 2027; 100% European value chain targeted.</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>images/ruta-block-3.jpg</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Destinus (via Defence Industry Europe)</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://defence-industry.eu/destinus-and-rheinmetall-advance-ruta-block-3-programme-for-european-long-range-strike-production/</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
           <t>https://defence-industry.eu/rheinmetall-destinus-strike-systems-outlines-european-cruise-missile-priorities-with-ruta-block-3-and-initial-production/</t>
@@ -6113,8 +6487,6 @@
           <t>Rheinmetall, Destinus 2,000km cruise missile - Army Technology</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6182,10 +6554,26 @@
           <t>Rebranded in army livery for coastal-defence export at IndoDefence 2025.</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>images/cm-401.jpg</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Army Recognition</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/army-news/2018/airshow-china-2018-casic-unveils-new-cm-401-anti-ship-missile</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr">
         <is>
           <t>https://www.twz.com/24699/china-reveals-short-range-anti-ship-ballistic-missile-designed-to-dodge-enemy-defenses</t>
@@ -6206,8 +6594,6 @@
           <t>IndoDefence 2025: China promotes CM-401 as coastal defense - Army Recognition</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6275,10 +6661,26 @@
           <t>RBS15 fielded across Sweden, Finland, Germany, Poland, Bulgaria, Croatia.</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>images/saab-rbs15-cdms.jpg</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Army Recognition Group</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://www.armyrecognition.com/news/navy-news/2025/saabs-new-coastal-defense-system-built-on-rbs15-missile-targets-growing-maritime-threats</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
           <t>https://www.saab.com/newsroom/stories/2025/september/a-powerful-new-deterrent-to-seaborne-threats</t>
@@ -6299,8 +6701,6 @@
           <t>Saab's New Coastal Defense System - Army Recognition</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6368,10 +6768,26 @@
           <t>Widely fielded to Ukraine and the Bundeswehr; container-frame design confirmed by multiple sources.</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>images/iris-t-slm-container.jpg</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Boevaya mashina / Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:IRIS-T_SLM_launcher_at_ILA-2024.JPG</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr">
         <is>
           <t>https://defence-industry.eu/diehl-defence-delivers-first-unit-of-iris-t-slm-system-to-german-armed-forces/</t>
@@ -6392,8 +6808,6 @@
           <t>Diehl delivers first IRIS-T SLM to German Army - Army Recognition</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6461,10 +6875,26 @@
           <t>Tested alongside a Polaris RZR-mounted CLWS unit; hosted by DRDC at CFB Suffield.</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>images/boeing-clws.jpg</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://www.boeing.com/features/2024/10/boeing-compact-lasers-down-group-3-drones-for-first-time</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr">
         <is>
           <t>https://www.boeing.com/features/2024/06/boeings-compact-lasers-shine-at-counter-drone-competition</t>
@@ -6485,8 +6915,6 @@
           <t>Boeing CLWS in Canada's IDEaS C-UAS trials - Unmanned Airspace</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6554,10 +6982,26 @@
           <t>Armed Strike POD remains a low-TRL demonstrator; G3 Systems selected as preferred supplier Nov 2025.</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>images/navypods-strike.jpg</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>FDS/Simon Bradley, via Naval News</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2026/05/royal-navy-achieves-milestone-with-first-sea-trials-of-navypods/</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr">
         <is>
           <t>https://www.navylookout.com/thinking-inside-the-box-the-royal-navys-containerised-capability-concept/</t>
@@ -6578,8 +7022,6 @@
           <t>G3 Systems preferred supplier for NavyPODS - Naval News</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6647,10 +7089,26 @@
           <t>100% success in Royal Navy WISEX mine-hunting trials.</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>images/elbit-seagull-usv.jpg</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Elbit Systems</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://www.elbitsystems.com/unmanned/maritime/unmanned-surface-vessel/seagull-usv</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr">
         <is>
           <t>https://www.elbitsystems.com/unmanned/maritime/unmanned-surface-vessel/seagull-usv</t>
@@ -6671,8 +7129,6 @@
           <t>NAVDEX 2025: 4th-gen Seagull USV - Janes</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6740,10 +7196,26 @@
           <t>Built on ~5,000 operational hours of the earlier GARC design; unveiled alongside the larger Comet USV.</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>images/blacksea-chaser-usv.jpg</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>BlackSea Technologies</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://www.blacksea.tech/chaser</t>
+        </is>
+      </c>
       <c r="R64" t="inlineStr">
         <is>
           <t>https://www.navalnews.com/naval-news/2026/05/video-new-comet-and-chaser-usv-by-blacksea-technologies/</t>
@@ -6764,8 +7236,6 @@
           <t>Chaser - BlackSea Technologies</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6833,10 +7303,26 @@
           <t>Follows a 2025 NUWC Newport order for three long-range LUUVs.</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>images/speartooth-luuv.jpg</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>C2 Robotics Pty Ltd</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>https://c2robotics.com.au/products/speartooth/</t>
+        </is>
+      </c>
       <c r="R65" t="inlineStr">
         <is>
           <t>https://www.armyrecognition.com/news/navy-news/2026/us-navy-receives-first-australian-speartooth-luuv-drone-for-autonomous-underwater-strikes</t>
@@ -6857,8 +7343,6 @@
           <t>Australian firm commissions first US export LUUV - Naval Today</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6926,10 +7410,26 @@
           <t>Culmination of Project Cetus; payload bay can carry mines, smaller UUVs, sensors.</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>images/xv-excalibur.jpg</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Royal Navy / UK MOD (OGL v3.0)</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Cetus-at-an-angle-front.jpg</t>
+        </is>
+      </c>
       <c r="R66" t="inlineStr">
         <is>
           <t>https://www.navalnews.com/naval-news/2026/01/autonomous-submarine-xv-excalibur-handed-to-royal-navy/</t>
@@ -6950,8 +7450,6 @@
           <t>Royal Navy name Project Cetus XLUUV Excalibur - Naval Technology</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7019,10 +7517,26 @@
           <t>Delivered under Germany's Kurs Marine 2035+ program after a 2-week German Navy trial.</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>images/bluewhale-uuv.jpg</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Swadim / Wikimedia Commons (CC0)</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:BlueWhale.jpg</t>
+        </is>
+      </c>
       <c r="R67" t="inlineStr">
         <is>
           <t>https://www.tkmsgroup.com/news/article/autonomous-underwater-vehicle-bluewhale-handed-over-to-german-navy-delivery-by-tkms-and-israel-aerospace-industries-as-part-of-the-kurs-marine-2035-program</t>
@@ -7043,8 +7557,6 @@
           <t>Germany's BlueWhale AUV - Army Recognition</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7112,10 +7624,26 @@
           <t>From ChatGPT deep-research set; corroborated by Anduril and Naval News.</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>images/anduril-slb-500m.jpg</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Anduril Industries, via The Defense Post</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>https://thedefensepost.com/2026/05/14/anduril-us-barracuda-500m-production/</t>
+        </is>
+      </c>
       <c r="R68" t="inlineStr">
         <is>
           <t>https://www.anduril.com/news/anduril-department-of-war-sign-production-agreement-for-surface-launched-barracuda-500m</t>
@@ -7136,8 +7664,6 @@
           <t>Massive US Missile Order May Expand Anti-Ship Arsenal - Naval News</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7205,10 +7731,26 @@
           <t>From ChatGPT deep-research set. Architecture/family rather than a fixed single-munition launcher.</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>images/iai-diamond.jpg</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>IAI (Israel Aerospace Industries), via Naval News</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://www.navalnews.com/naval-news/2026/05/iai-unveils-diamond-new-distributed-warfare-solution-that-expands-the-power-of-modern-frigates/</t>
+        </is>
+      </c>
       <c r="R69" t="inlineStr">
         <is>
           <t>https://www.iai.co.il/press/iai-unveils-diamond</t>
@@ -7229,8 +7771,6 @@
           <t>DIAMOND - IAI</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7298,10 +7838,26 @@
           <t>From ChatGPT deep-research set. Depicted as a proposed family variant; dimensions/procurement/fielding limited.</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>images/vampire-casket.jpg</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>L3Harris (via The War Zone)</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/air/entire-family-of-vampire-counter-drone-systems-unveiled</t>
+        </is>
+      </c>
       <c r="R70" t="inlineStr">
         <is>
           <t>https://www.twz.com/air/entire-family-of-vampire-counter-drone-systems-unveiled</t>
@@ -7312,10 +7868,6 @@
           <t>Entire Family Of VAMPIRE Counter-Drone Systems Unveiled - TWZ</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/systems.xlsx
+++ b/data/systems.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -480,117 +480,117 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>aka</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>builder</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sortDate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>dateLabel</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>dateBasis</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>concealment</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>photo_file</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>photo_credit</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>photo_license</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>photo_source</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>source1_url</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>source1_title</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>source2_url</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>source2_title</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>source3_url</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>source3_title</t>
         </is>
@@ -599,57 +599,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>club-k</t>
+          <t>destinus-hornet-b1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Club-K Container Missile System</t>
+          <t>Destinus Hornet Block 1 Containerized Interceptor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Klab-K; 3M-54/Kh-35UE containerised launcher</t>
+          <t>Hornet B1, Destinus containerized interceptor drone launcher</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Concern Morinformsystem-Agat (missiles by Novator Design Bureau)</t>
+          <t>Destinus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Switzerland (tested by Spain)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2010-04-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Unveiled 2010 (DSA Malaysia); live Kh-35UE test 22 Aug 2012</t>
+          <t>Test-fired aboard frigate Santa Maria and in land container config</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Strike missile</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Concealed cargo</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The archetype: a standard 20-ft or 40-ft ISO shipping container that conceals four cruise missiles from the Kalibr family (3M-54/3M-14) or Kh-35UE anti-ship missiles, letting any truck, rail car, or cargo ship become a covert missile battery disguised as ordinary freight. Marketed for export by Concern Morinformsystem-Agat, it triggered international alarm over the blurring of civilian and military shipping. A live-fire test of the Kh-35UE variant was reported on 22 August 2012.</t>
+          <t>Canister-launched hard-kill interceptor drone engaging subsonic UAVs/swarms, fired from a modular containerized launch unit demonstrated on both a ship's deck and a land container configuration.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Missiles designed by Novator; container system marketed by Morinformsystem-Agat. Widely regarded as the concept that launched the containerised-weapons debate.</t>
+          <t>Clearest verified containerized interceptor-drone launcher found.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>images/club-k.jpg</t>
+          <t>images/destinus-hornet-b1.jpg</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Wikimedia Commons</t>
+          <t>Artvill / Wikimedia Commons</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -679,79 +679,69 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Club-K.jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:Destinus_Hornet_au_Salon_du_Bourget_2025_1.jpg</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Club-K_container_missile_system</t>
+          <t>https://www.navalnews.com/</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Club-K container missile system — Wikipedia</t>
+          <t>Spanish Navy Tests Hornet Block 1 from Santa Maria Frigate - Naval News</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>https://navyrecognition.com/index.php?id=592&amp;option=com_content&amp;view=article</t>
+          <t>https://thedefensepost.com/</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Club-K Container Missile System — Navy Recognition</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
+          <t>Spanish Army Tests Destinus Hornet B1 in Container Launch Config - The Defense Post</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>iai-lora</t>
+          <t>ruta-block-3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IAI LORA Containerised Ballistic Missile</t>
+          <t>Rheinmetall Destinus Ruta Block 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Long-Range Artillery (LORA) naval / ship-deck launch</t>
+          <t>Ruta Block 3, RUTA Block III deep-strike cruise missile</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Israel Aerospace Industries (IAI)</t>
+          <t>Rheinmetall Destinus Strike Systems</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Germany / Switzerland-Spain</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2017-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>June 2017</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>First ship-deck launch 20 Jun 2017; repeat Mediterranean test June 2020</t>
+          <t>Unveiled at Eurosatory 2026</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -761,109 +751,109 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>IAI test-launched its LORA quasi-ballistic missile from a container-dimensioned launcher placed on the deck of a civilian-type cargo ship on 20 June 2017, then repeated the feat in 2020 by striking two floating targets at roughly 90 km and 400 km. Because the sealed launch canister conforms to standard shipping-container dimensions, the system can be hidden among ordinary deck cargo. It demonstrated that a precision ballistic strike could be mounted from an unremarkable merchant hull.</t>
+          <t>A strategic deep-strike cruise missile (&gt;2,000 km, 250 kg warhead) launched exclusively from standard ISO shipping containers on vehicle (Rheinmetall HX truck) or maritime platforms, reaching firing readiness in ~2 minutes.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2017/2020 trials used the LORA launcher set on a deck and remote-fired; missiles ship in sealed ISO-conformant canisters.</t>
+          <t>Flight testing not scheduled until 2027; 100% European value chain targeted.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>images/iai-lora.jpg</t>
+          <t>images/ruta-block-3.jpg</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Wikimedia Commons (Paris Air Show)</t>
+          <t>Destinus (via Defence Industry Europe)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:LORA_missile.JPG</t>
+          <t>https://defence-industry.eu/destinus-and-rheinmetall-advance-ruta-block-3-programme-for-european-long-range-strike-production/</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>https://www.twz.com/11723/israel-just-launched-a-containerized-ballistic-missile-from-the-deck-of-a-ship</t>
+          <t>https://defence-industry.eu/rheinmetall-destinus-strike-systems-outlines-european-cruise-missile-priorities-with-ruta-block-3-and-initial-production/</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Israel Just Launched A Containerized Ballistic Missile From The Deck Of A Ship — The War Zone</t>
+          <t>Rheinmetall Destinus Ruta Block 3 priorities - Defence Industry Europe</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/LORA_(missile)</t>
+          <t>https://www.army-technology.com/news/rheinmetall-destinus-cruise-missile/</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>LORA (missile) — Wikipedia</t>
+          <t>Rheinmetall, Destinus 2,000km cruise missile - Army Technology</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mbda-spimm</t>
+          <t>knds-drone-container</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MBDA SPIMM / DEFENDAIR</t>
+          <t>KNDS Containerized Drone Launcher</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Self-Protection Integrated Mistral Module</t>
+          <t>KNDS drone launch container, Helsing HX-2 / Tytan TI-1 METIS container</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MBDA</t>
+          <t>KNDS (France/Germany) with Helsing and Tytan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Europe (France-led consortium)</t>
+          <t>France / Germany</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2019-02-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>February 2019</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Unveiled at NAVDEX 2019</t>
+          <t>Demonstrator unveiled at Eurosatory 2026</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Loitering munition</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -873,7 +863,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MBDA's Self-Protection Integrated Mistral Module (SPIMM), unveiled at NAVDEX 2019, packs a SIMBAD-RC automated turret with two ready-to-fire Mistral 3 infrared-guided surface-to-air missiles into an all-in-one 10-ft, 7-ton container, topped with an HGH Spynel 360-degree infrared panoramic sensor and housing a two-operator control station. Needing only a tie-in to the host ship's main power, it gives unarmed auxiliary ships or landing craft immediate point-defense against aircraft, drones, and fast inshore attack craft. MBDA is separately developing DEFENDAIR, a maintenance-free containerized counter-UAS missile system optimized against agile drone swarms.</t>
+          <t>A self-contained 20-ft ISO container with independent power, environmental control and networking, housing dozens to 100+ effectors combining Helsing HX-2 strike drones and Tytan TI-1 METIS hard-kill interceptor drones; pitched as a response to Ukraine's Operation Spiderweb.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -883,17 +873,17 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>DEFENDAIR is a related but distinct, less-mature MBDA program folded into this entry.</t>
+          <t>Mock-up demonstrator/concept, not yet fielded; dual strike + interceptor role.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>images/mbda-spimm.jpg</t>
+          <t>images/knds-drone-container.jpg</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>MBDA Systems</t>
+          <t>KNDS Group</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -903,84 +893,84 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://www.twz.com/26599/this-containerized-missile-launcher-could-give-almost-any-ship-short-range-air-defenses</t>
+          <t>https://knds.com/en/press-releases/bolstering-mission-solution-portfolio-knds-showcases-first-drone-launch-container-prototype-at-eurosatory-2026-1</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>https://www.twz.com/26599/this-containerized-missile-launcher-could-give-almost-any-ship-short-range-air-defenses</t>
+          <t>https://www.armyrecognition.com/</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>This Containerized Missile Launcher Could Give Almost Any Ship Short-Range Air Defenses — The War Zone</t>
+          <t>KNDS unveils containerized drone launcher concept - Army Recognition</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>https://www.edrmagazine.eu/navdex-2019-mbda-unveils-the-self-protection-integrated-mistral-module-spimm-for-surface-ship</t>
+          <t>https://www.euro-sd.com/</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>NAVDEX 2019: MBDA unveils the Self-Protection Integrated Mistral Module (SPIMM) for surface ship — EDR Magazine</t>
+          <t>KNDS showcases C-UAV capabilities at Eurosatory 2026 - ESD</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sh-defence-cube</t>
+          <t>rheinmetall-cml-fv014</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SH Defence CUBE System</t>
+          <t>Rheinmetall Containerized Missile Launcher (CML) / FV-014</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>The Cube</t>
+          <t>CML; FV-014 loitering munition launcher</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SH Defence</t>
+          <t>Rheinmetall</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>15 June 2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Product/brochure introduction</t>
+          <t>World premiere at Eurosatory 2026</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Modular system</t>
+          <t>Loitering munition</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Denmark's SH Defence built the CUBE System, a maritime modularity ecosystem using 20-ft and 40-ft container dimensions fully compliant with NATO STANAG and DNV GL ST-0378, letting a naval vessel switch between mission profiles — anti-surface warfare, mine-laying, search and rescue — in under four hours. The catalog includes specialized modules such as UAV side-launch-and-recovery systems, top-launch UAV swarm modules, towed-array ASW sonars, and modular missile launchers, moved between a ship's internal mission bay and flight deck via automated 'Skidding Systems' and twist-locks.</t>
+          <t>Unveiled at Eurosatory 2026, the Containerized Missile Launcher (CML) packs up to 18 FV-014 loitering munitions into a 20-foot ISO container with internal battery reserves, an optional generator, and a low-power sleep mode for extended covert standby. The FV-014 itself has a 100 km range, 70 minutes of endurance, and a 4-5 kg HEDP warhead able to penetrate over 600 mm of armor, flown man-in-the-loop but capable of coordinated swarm salvos of 18 munitions from a single operator. The CML plugs into Rheinmetall's Battlesuite C4I architecture, and in April 2026 the Bundeswehr awarded Rheinmetall a multi-billion-euro framework contract with an initial 300 million euro production order.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -990,94 +980,94 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>An ecosystem/family of modules rather than a single weapon; entry covers the CUBE concept broadly.</t>
+          <t>Bundeswehr framework contract announced the same year as unveiling; drones use man-in-the-loop EO guidance, not full autonomy, despite the launcher's autonomous standby features.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>images/sh-defence-cube.jpg</t>
+          <t>images/rheinmetall-cml-fv014.jpg</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>SH Defence</t>
+          <t>Rheinmetall / Army Recognition</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>https://shdefence.com/</t>
+          <t>https://www.rheinmetall.com/en/products/weapon-stations/containerized-missile-launcher</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>https://shdefence.com/wp-content/uploads/2021/08/SH-Defence_The-Cube%E2%84%A2-Solutions_Collection_Low.pdf</t>
+          <t>https://thedefensewatch.com/military-ordnance/rheinmetall-cml-fv014-loitering-munition-eurosatory-2026/</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>The Cube Solutions — SH Defence</t>
+          <t>Rheinmetall Unveils CML Multi-Launcher To Expand FV-014 Loitering Munition Strike Capability — The Defense Watch</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>https://www.edge-defence.com/shdefencecube</t>
+          <t>https://www.rheinmetall.com/en/media/news-watch/news/2026/06/2026-06-15-world-premiere-at-eurosatory-rheinmetall-presents-cml-multi-launcher-for-fv-014-loitering-munition</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>The Cube — EDGE Defence Ltd</t>
+          <t>Containerised Missile Launcher makes its debut at Eurosatory — Rheinmetall</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rafael-c-dome</t>
+          <t>hanwha-striker-musv</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rafael C-DOME Mission Module</t>
+          <t>Hanwha Striker MUSV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Containerized Iron Dome for ships</t>
+          <t>Striker-S</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rafael Advanced Defense Systems</t>
+          <t>Hanwha Systems</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2021-01-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Deployment on Israeli Navy Sa'ar 6-class corvettes</t>
+          <t>Unveiled at Eurosatory 2026</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Autonomous vehicle</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1087,64 +1077,64 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Rafael modularized its combat-proven Iron Dome into the C-DOME Mission Module, a multi-round Vertical Launch Unit using the Tamir interceptor packaged in a standard footprint that requires no deck penetration, for offshore patrol vessels and corvettes lacking organic air defense. It networks with a ship's existing search radar through an open-architecture Combat Management System to intercept saturation attacks from rockets, cruise missiles, and UAVs, and is deployed on the Israeli Navy's Sa'ar 6-class corvettes.</t>
+          <t>South Korea's Hanwha Systems introduced the Striker-S at Eurosatory 2026, a 35-meter low-observable-hull Medium Uncrewed Surface Vessel (MUSV) with a mission deck for a 10-ton containerized payload module. Hanwha pairs it with a containerized launcher for the Chunmoo missile family, specifically the CTM-ASBM (Chunmoo Tactical Missile - Anti-Ship Ballistic Missile), a GPS/INS- and imaging-infrared-guided 280mm missile that lets the autonomous vessel act as a remote missile carrier extending a task group's strike radius by up to 160 km.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Actively fielded, unlike several other entries in this catalog that remain prototypes.</t>
+          <t>Newly unveiled at Eurosatory 2026; fielding/testing status not yet established.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>images/rafael-c-dome.jpg</t>
+          <t>images/hanwha-striker-musv.jpg</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>IDF Spokesperson (CC BY-SA 3.0) / Wikimedia Commons</t>
+          <t>Hanwha Systems / Army Recognition</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Sa%27ar-6-class-corvette-0023.jpg</t>
+          <t>https://www.navalnews.com/naval-news/2026/06/hanwha-unveils-striker-musv-family-at-eurosatory-2026/</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>https://www.rafael.co.il/system/c-dome-2/</t>
+          <t>https://www.navalnews.com/naval-news/2026/06/hanwha-unveils-striker-musv-family-at-eurosatory-2026/</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>C-DOME: Maritime Application of the Combat-Proven Iron Dome — Rafael</t>
+          <t>Hanwha Unveils Striker MUSV Family at Eurosatory 2026 — Naval News</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mk70-pds</t>
+          <t>lockheed-grizzly</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mk 70 Payload Delivery System</t>
+          <t>Lockheed Martin GRIZZLY</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mk 70 Mod 1 PDS; containerised Mk 41 VLS</t>
+          <t>Containerized Hellfire/JAGM Launcher</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1159,22 +1149,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>September 2021</t>
+          <t>June 2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Unveiled Sept 2021 via SM-6 launch from USV Ranger</t>
+          <t>Live-fire validation at Yuma Proving Ground</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Strike missile</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1184,7 +1174,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>The Mk 70 PDS packs four strike-length Mk 41 vertical launch cells into a 40-ft (12 m) ISO-container footprint that erects to fire SM-6 and Tomahawk missiles at maritime and land targets out to roughly 450 km and 1,600 km. First shown in September 2021 when an SM-6 was fired from the unmanned surface vessel USV Ranger, it has since been integrated onto Freedom-class Littoral Combat Ships. Unlike Club-K it makes no attempt at concealment — the container is a modular launcher, not a disguise.</t>
+          <t>GRIZZLY is a 10-ft containerized launcher built on the proven M299 launcher architecture, capable of firing up to eight AGM-114 Hellfire or Joint Air-to-Ground Missiles (JAGM); its roof hinges open for vertical or angled launch. In live-fire tests at Yuma Proving Ground in June 2026, GRIZZLY successfully intercepted Group 3 attack drones using radar cues from Fortem Technologies R-40 radars and Lockheed's Sanctum battle-management software. It gives expeditionary forces a rapidly deployable counter-UAS and anti-armor capability in a single box.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1194,94 +1184,94 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>A separate claim that the Mk 70 first fired at sea from USS Savannah (LCS 28) in 2023 was refuted; its first at-sea firing was from USV Ranger in 2021.</t>
+          <t>Dual-role system: demonstrated primarily as counter-UAS in its highlighted 2026 test, though the M299/Hellfire/JAGM armament is originally an anti-armor weapon.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>images/mk70-pds.jpg</t>
+          <t>images/lockheed-grizzly.jpg</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>U.S. Navy / The War Zone</t>
+          <t>U.S. Army</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>public-domain-gov</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2023/09/u-s-navy-and-army-mk-70-pds-stretch-their-wings/</t>
+          <t>https://www.army.mil/article/293025/</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2023/09/u-s-navy-and-army-mk-70-pds-stretch-their-wings/</t>
+          <t>https://www.army.mil/article/293025/u_s_army_yuma_proving_ground_tests_containerized_missile_launcher</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>U.S. Navy And Army Mk 70 PDS Stretch Their Wings — Naval News</t>
+          <t>U.S. Army Yuma Proving Ground tests containerized missile launcher — Army.mil</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/event-news/sna-2025/2025/01/u-s-navy-brings-offensive-capability-to-lcs-with-mk-70-pds/</t>
+          <t>https://www.twz.com/air/hellfire-missile-launcher-tucked-inside-a-container-rolled-out-by-lockheed</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>U.S. Navy Brings Offensive Capability To LCS With Mk 70 PDS — Naval News</t>
+          <t>Hellfire Missile Launcher Tucked Inside A Container Rolled Out By Lockheed — The War Zone</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>edge-hunter-skyknight</t>
+          <t>containerized-helios</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EDGE HUNTER 10 &amp; SkyKnight Containerized Systems</t>
+          <t>Containerised HELIOS Laser</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HALCON HUNTER 10; SkyKnight Multi-Launcher Unit</t>
+          <t>Mk 5 Mod 0 HELIOS; Containerized Maritime High Energy Laser Weapon System</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EDGE Group (HALCON subsidiary)</t>
+          <t>Lockheed Martin (for U.S. Navy)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2026 (draft FY2027 NDAA)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Unveiling (UMEX 2022) and subsequent SkyKnight containerization</t>
+          <t>Congressional funding push, draft FY2027 NDAA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Modular system</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1291,211 +1281,211 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>UAE's EDGE Group, through its HALCON subsidiary, developed the HUNTER 10, a container-launched fixed-wing loitering munition with a 50 kg maximum take-off weight, 10 kg payload, 33 m/s cruising speed, and 100 km range; a smaller Hunter SP variant has been integrated into dual 7-tube containerized pods on Milrem Robotics' THeMIS unmanned ground vehicle. Separately, EDGE has containerized its SkyKnight missile as a 20-ft Multi-Launcher Unit holding up to 60 missiles for Counter Rocket, Artillery, and Mortar (C-RAM) defense, firing at five rounds per second. The two products represent EDGE's parallel push into container-packaged offensive loitering munitions and defensive C-RAM.</t>
+          <t>HELIOS (High-Energy Laser with Integrated Optical-dazzler and Surveillance) is a 60 kW-class Lockheed Martin laser, designated Mk 5 Mod 0 and already deployed on the destroyer USS Preble. In 2026 an early draft of the FY2027 National Defense Authorization Act moved to authorise $5 million for a containerised HELIOS plus $2.5 million for a separate 'Containerized Maritime High Energy Laser Weapon System.' The push would repackage the shipboard laser into a deployable container for wider basing.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Two distinct EDGE Group products bundled into one catalog entry: HUNTER 10 (offensive loitering munition) and SkyKnight (defensive C-RAM missile container).</t>
+          <t>A draft authorisation, not enacted law and not yet built.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>images/edge-hunter-skyknight.jpg</t>
+          <t>images/containerized-helios.jpg</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>EDGE Group / Army Recognition</t>
+          <t>U.S. DoD DOT&amp;E report</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>public-domain-gov</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://edgegroup.ae/solutions/hunter-10</t>
+          <t>https://www.twz.com/news-features/containerized-variant-of-navys-drone-swatting-helios-laser-being-pushed-by-congress</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>https://edgegroup.ae/solutions/hunter-10</t>
+          <t>https://www.twz.com/news-features/containerized-variant-of-navys-drone-swatting-helios-laser-being-pushed-by-congress</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>HUNTER 10 Long-Range Multi Role Loitering Munition — EDGE Group</t>
+          <t>Containerized Variant Of Navy's Drone-Swatting HELIOS Laser Being Pushed By Congress — The War Zone</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bit-swarm-truck</t>
+          <t>iai-diamond</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Beijing Institute of Technology (BIT) Containerized Swarm Launcher Truck</t>
+          <t>IAI DIAMOND Distributed Warfare System</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chinese disguised loitering-munition truck</t>
+          <t>DIAMOND, Distributed Warfare Solution</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Beijing Institute of Technology (BIT), part of a consortium of 70+ Chinese research entities</t>
+          <t>Israel Aerospace Industries</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Late 2022</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Revealed by Chinese state media (CCTV)</t>
+          <t>Official unveiling</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Covert / disguised</t>
+          <t>Modular system</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Concealed cargo</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Chinese state broadcaster CCTV revealed in late 2022 a vehicle-mounted swarm launcher disguised as an ordinary light tactical truck, able to rapidly deploy up to 18 loitering munitions with pop-out wings and V-shaped tails resembling the U.S. Switchblade or Israeli Mini Harpy. It is one module within a broader 'containerized weapon module suite' developed by over 70 Chinese research entities, spanning at least 10 modules covering drones, air defense, anti-ship strike, and electronic warfare. The truck is designed for network-enabled saturation strikes against personnel, light armor, and radar sites.</t>
+          <t>A distributed-warfare architecture using container-footprint payload modules for ships and other platforms, able to host loitering munitions, Blue Spear, LORA, Barak MX and counter-UAS payloads in reconfigurable packages.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Details rely on a single state-media reveal; the broader 10-module 'containerized weapon suite' program is only partially disclosed.</t>
+          <t>From ChatGPT deep-research set. Architecture/family rather than a fixed single-munition launcher.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>images/bit-swarm-truck.jpg</t>
+          <t>images/iai-diamond.jpg</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>The War Zone (Zhuhai Air Show)</t>
+          <t>IAI (Israel Aerospace Industries), via Naval News</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://www.twz.com/drone-swarm-launcher-truck-displayed-at-chinas-big-arms-expo</t>
+          <t>https://www.navalnews.com/naval-news/2026/05/iai-unveils-diamond-new-distributed-warfare-solution-that-expands-the-power-of-modern-frigates/</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>https://www.twz.com/drone-swarm-launcher-truck-displayed-at-chinas-big-arms-expo</t>
+          <t>https://www.iai.co.il/press/iai-unveils-diamond</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Drone Swarm Launcher Truck Displayed At China's Big Arms Expo — The War Zone</t>
+          <t>IAI Unveils DIAMOND: New Distributed Warfare Solution - IAI</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>https://asiatimes.com/2026/07/chinas-truck-drone-launcher-hides-airpower-in-civilian-traffic/</t>
+          <t>https://www.iai.co.il/product/diamond</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>China's truck drone launcher hides airpower in civilian traffic — Asia Times</t>
+          <t>DIAMOND - IAI</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>patria-nemo-container</t>
+          <t>dzyne-blitzbox</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Patria NEMO Container</t>
+          <t>DZYNE BlitzBox</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patria NEMO (NEw MOrtar) containerized turret</t>
+          <t>BlitzBox, Blitz drone container launcher</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Patria</t>
+          <t>DZYNE Technologies</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Product literature/introduction; live-fire demonstrated June 2026</t>
+          <t>Unveiled at SOF Week</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Artillery / coastal</t>
+          <t>Loitering munition</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Concealed cargo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Patria integrated its 120 mm NEMO remote-controlled mortar turret into a standard 20-ft ISO container as a fully independent firing unit with its own power generation, NBC filtration, air conditioning, and ballistic protection. A semi-automatic autoloader sustains 6 rounds per minute (three rounds in 12 seconds in a burst), and the fire-control network supports Multiple Rounds Simultaneous Impact (MRSI) missions of up to six mortar bombs landing on one target at once. The container can be moved by standard military trucks or mounted on fast naval patrol vessels for coastal defense.</t>
+          <t>An ordinary-looking shipping container hiding a launch system for DZYNE's Blitz Group-1 expendable swarming drones; a 10-ft container holds 16 drones on 4 rail launchers, a 40-ft container up to 100.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1505,89 +1495,89 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Document cites a June 2026 test alongside earlier 2023 product literature; treated here as an established, available product.</t>
+          <t>TWZ direct interview with DZYNE program manager.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>images/patria-nemo-container.jpg</t>
+          <t>images/dzyne-blitzbox.jpg</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>S. Kiyotani / European Security &amp; Defence</t>
+          <t>DZYNE Technologies</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
+          <t>https://dzyne.com/wp-content/uploads/2026/03/Blitz%20ISO%20container%20launcher-edited-2048x1342.png</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>https://www.patriagroup.com/products-and-services/defence-and-weapon-systems/armament/patria-nemo-container</t>
+          <t>https://www.twz.com/</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Patria NEMO Container — Patria</t>
+          <t>BlitzBox Packs 100 Weaponized Drones Into A Container - TWZ</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>https://www.patriagroup.com/download/patria-nemo-container-a4210x297mm-08-2023-final-webpdf</t>
+          <t>https://www.slashgear.com/</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Patria NEMO Container — 120 mm mortar system (product sheet)</t>
+          <t>A Container Full Of 100 Deadly Drones - SlashGear</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kongsberg-nsm-cds</t>
+          <t>anduril-slb-500m</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kongsberg Naval Strike Missile (NSM) Coastal Defence System</t>
+          <t>Anduril Surface-Launched Barracuda-500M</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NSM CDS</t>
+          <t>SLB-500M, Surface-Launched Barracuda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kongsberg Defence &amp; Aerospace</t>
+          <t>Anduril Industries</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Multi-nation adoption reports (Poland, Romania, Australia, USMC NMESIS)</t>
+          <t>Production agreement announcement</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1602,7 +1592,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Kongsberg adapted its stealthy, sea-skimming Naval Strike Missile (NSM), which has a range exceeding 200 km, a Microturbo TRI-40 turbojet, and an imaging-infrared seeker with autonomous target recognition, into a modular, truck- or flatbed-transportable Coastal Defence System. A Fire Control Center built on the NASAMS architecture can network up to four FCCs to coordinate engagement of up to 48 simultaneous targets across land and sea. The containerized CDS has been adopted by Poland, Romania, Australia, and the U.S. Marine Corps (via the NMESIS program), and an unidentified NSM launcher has reportedly been observed operating in Ukraine.</t>
+          <t>A surface-launched Barracuda-500M variant paired with a standard 20-ft ISO launcher that can carry up to 16 rounds, for dispersed land and maritime strike; announced under the US Low-Cost Containerized Munitions effort.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1612,94 +1602,94 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Ukraine sighting described in the source as an 'unidentified' NSM launcher, not officially confirmed.</t>
+          <t>From ChatGPT deep-research set; corroborated by Anduril and Naval News.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>images/kongsberg-nsm-cds.jpg</t>
+          <t>images/anduril-slb-500m.jpg</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Wikimedia Commons</t>
+          <t>Anduril Industries, via The Defense Post</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Naval_Strike_Missile_(NSM).jpg</t>
+          <t>https://thedefensepost.com/2026/05/14/anduril-us-barracuda-500m-production/</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Naval_Strike_Missile</t>
+          <t>https://www.anduril.com/news/anduril-department-of-war-sign-production-agreement-for-surface-launched-barracuda-500m</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Naval Strike Missile — Wikipedia</t>
+          <t>Anduril-DoW Production Agreement for SLB-500M - Anduril</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>https://www.kongsberg.com/what-we-do/defence-and-security/integrated-air-and-missile-defence/coastal-defence-system/</t>
+          <t>https://www.navalnews.com/naval-news/2026/05/massive-u-s-missile-order-may-expand-american-anti-ship-arsenal/</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Naval Strike Missile (NSM) Coastal Defence System — Kongsberg</t>
+          <t>Massive US Missile Order May Expand Anti-Ship Arsenal - Naval News</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>typhon-mrc</t>
+          <t>speartooth-luuv</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Typhon / Mid-Range Capability (MRC)</t>
+          <t>C2 Robotics Speartooth LUUV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Strategic Mid-Range Fires; land-based Mk 41 container launcher</t>
+          <t>Speartooth, C2 Robotics long-range LUUV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>C2 Robotics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27 June 2023</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>First Tomahawk launch and first-unit operational declaration 27 Jun 2023</t>
+          <t>First unit delivered to US Navy</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Strike missile</t>
+          <t>Autonomous vehicle</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1709,7 +1699,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Typhon is the U.S. Army's land-based sibling of the Mk 70, mounting four strike-length Mk 41 cells in a 40-ft ISO-container footprint on a trailer-borne transporter-erector-launcher that raises to fire SM-6 and Tomahawk. The first battery was declared operational with the 1st Multi-Domain Task Force on 27 June 2023, and the system deployed to the Philippines in April 2024, drawing sharp reactions from China. It gives ground forces a mobile intermediate-range strike capability packaged as a shipping container.</t>
+          <t>A long-range (2,000 km), 2,000m-depth large uncrewed undersea vehicle purpose-built to ship inside and deploy from a standard container via ramp or austere coastal infrastructure, without dedicated submarine support; ISR, mine warfare and strike delivery.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1719,124 +1709,124 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>'Containerised' here denotes the container form-factor that erects to fire, not cargo-disguise concealment.</t>
+          <t>Follows a 2025 NUWC Newport order for three long-range LUUVs.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>images/typhon-mrc.jpg</t>
+          <t>images/speartooth-luuv.jpg</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>U.S. Army / Wikimedia Commons</t>
+          <t>C2 Robotics Pty Ltd</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>public-domain-gov</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Typhon_Mid-Range_Capability_(MRC)_missile_system_firing_SM-6.jpg</t>
+          <t>https://c2robotics.com.au/products/speartooth/</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Typhon_missile_system</t>
+          <t>https://www.armyrecognition.com/news/navy-news/2026/us-navy-receives-first-australian-speartooth-luuv-drone-for-autonomous-underwater-strikes</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Typhon missile system — Wikipedia</t>
+          <t>US Navy receives first Australian Speartooth LUUV - Army Recognition</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2023/09/u-s-navy-and-army-mk-70-pds-stretch-their-wings/</t>
+          <t>https://www.navaltoday.com/2026/05/05/australian-firm-commissions-first-us-export-luuv/</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>U.S. Navy And Army Mk 70 PDS Stretch Their Wings — Naval News</t>
+          <t>Australian firm commissions first US export LUUV - Naval Today</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dprk-disguised-mlrs</t>
+          <t>sinarit-submarine</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>North Korean Disguised MLRS</t>
+          <t>Sinarit Autonomous Submarine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Civilian-truck-disguised 122mm MLRS</t>
+          <t>Datum Submarine Technologies Sinarit UUV</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>North Korean state defense industry</t>
+          <t>Datum Submarine Technologies</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>North Korea (DPRK)</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>September 2023</t>
+          <t>May 2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Unveiled at military parade</t>
+          <t>Unveiled at SAHA Expo, Istanbul</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Covert / disguised</t>
+          <t>Autonomous vehicle</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Concealed cargo</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>North Korea unveiled a fleet of Multiple Launch Rocket Systems disguised as ordinary civilian box trucks and yellow hard-hat dump trucks at a September 2023 military parade, with sliding roofs that open to reveal 12-tube 122mm rocket launchers. In 2026, intelligence reports and open-source video reportedly confirmed these disguised MLRS trucks operating in Russia's Kursk region, demonstrating their utility in heavily surveilled combat zones where distinguishing civilian from military traffic is critical to survival.</t>
+          <t>Turkish firm Datum Submarine Technologies unveiled the Sinarit at the SAHA Expo in Istanbul in May 2026: an 11.5-meter, 19.8-ton uncrewed autonomous diesel-electric submarine explicitly designed to fit inside a standard shipping container, allowing transport by commercial truck or Airbus A400M cargo aircraft. Operating to 100-meter depths, it can autonomously launch its own containerized payloads while submerged, including Roketsan Atmaca anti-ship missiles (250 km range, active RF seeker), Orka lightweight torpedoes, and swarms of FPV attack drones that breach the surface to strike before the submarine withdraws undetected.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Kursk deployment reports rely on open-source and intelligence claims rather than official confirmation.</t>
+          <t>Newly unveiled prototype; sourced to a single outlet (Autonocion) in the document.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>images/dprk-disguised-mlrs.webp</t>
+          <t>images/sinarit-submarine.jpg</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>The War Zone / KCNA</t>
+          <t>Datum Submarine Technologies / Naval News</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1846,181 +1836,181 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://www.twz.com/north-korea-debuts-rocket-launchers-that-appear-as-civilian-trucks</t>
+          <t>https://www.navalnews.com/naval-news/2026/05/datum-introduces-strike-capable-sinarit-xluuv/</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://www.twz.com/land/north-korean-rocket-launcher-disguised-as-civilian-truck-may-just-have-appeared-in-kursk</t>
+          <t>https://www.autonocion.com/us/drone-submarine-turkey/</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Artillery Rocket Launcher Disguised As Civilian Truck May Have Just Appeared In Russia — The War Zone</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>https://www.twz.com/north-korea-debuts-rocket-launchers-that-appear-as-civilian-trucks</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>North Korea Debuts Rocket Launchers That Appear As Civilian Trucks — The War Zone</t>
+          <t>Turkey just unveiled a 19.8-ton drone submarine built to launch FPV drone swarms, anti-ship missiles, torpedoes and mines while submerged — Autonocion.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iai-acdc</t>
+          <t>blacksea-chaser-usv</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IAI All-Capabilities Defence Container (ACDC)</t>
+          <t>BlackSea Technologies Chaser USV</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ACDC</t>
+          <t>Chaser, GARC Block II</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Israel Aerospace Industries (IAI)</t>
+          <t>BlackSea Technologies</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>April 2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Product marketing/announcement</t>
+          <t>Unveiled at Sea-Air-Space 2026</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Modular system</t>
+          <t>Autonomous vehicle</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>IAI markets the All-Capabilities Defence Container (ACDC), a modular self-defense package housing four Mini Harpy and eight Rotem L loitering munitions alongside its own operations room and an integrated mast carrying radar, communications, and optronic sights. It is designed to bolt onto weakly armed vessels to give them an immediate self-defense and limited-strike capability without a major refit.</t>
+          <t>A modular unmanned surface vessel engineered to fit inside and deploy from a standard 20-ft ISO container per a US Navy transportability requirement; carries JAGM launchers and EO/radar sensors.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Described in marketing/analyst literature; fielding status on any specific vessel is not established in the source.</t>
+          <t>Built on ~5,000 operational hours of the earlier GARC design; unveiled alongside the larger Comet USV.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>images/iai-acdc.jpg</t>
+          <t>images/blacksea-chaser-usv.jpg</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>IAI (DIAMOND) / Breaking Defense</t>
+          <t>BlackSea Technologies</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://breakingdefense.com/2026/05/iais-new-diamond-naval-offering-envisions-flexible-drones-missiles-for-small-vessels/</t>
+          <t>https://www.blacksea.tech/chaser</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
+          <t>https://www.navalnews.com/naval-news/2026/05/video-new-comet-and-chaser-usv-by-blacksea-technologies/</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
+          <t>New Comet and Chaser USV by BlackSea Technologies - Naval News</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>https://www.blacksea.tech/chaser</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Chaser - BlackSea Technologies</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>shahid-mahdavi</t>
+          <t>bluewhale-uuv</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IRIS Shahid Mahdavi Containerized Ballistic Missile Ship</t>
+          <t>IAI/tkMS BlueWhale UUV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>L110-3; converted container ship Sarvin</t>
+          <t>BlueWhale AUV/XLUUV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Islamic Revolutionary Guard Corps Navy (IRGCN); hull built in South Korea</t>
+          <t>Israel Aerospace Industries / thyssenkrupp Marine Systems</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Israel / Germany</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>February 2024</t>
+          <t>February 2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>First containerized ballistic missile launch from deck (ship commissioned March 2023)</t>
+          <t>Delivered to German Navy at Eckernforde</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Naval arsenal</t>
+          <t>Autonomous vehicle</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Converted from the 36,000-ton South Korean-built Panamax container ship Sarvin, the IRIS Shahid Mahdavi was commissioned by the IRGC Navy in March 2023 with a 150-metre flat deck for helicopters, UAV launches (including Shahed-136s), and containerized missile strikes, defended by four Nawab short-range VLS air-defense missiles and a 3D phased-array radar. In February 2024 the IRGCN test-fired long-range solid-fueled ballistic missiles — variously identified as Fateh-110, Zolfaghar, or Dezful variants — directly from standard shipping containers on its deck, with reported ranges of 500-1,700 km. The conversion turns an innocuous cargo hull into a mobile strategic strike asset capable of reaching the Indian Ocean, the Gulf of Aden, or targets across the Middle East.</t>
+          <t>A 10.9m, 5.5-tonne autonomous underwater vehicle for ASW support, minehunting and covert ISR, engineered to be transported inside a standard 40-ft shipping container for deployment by land, air or sea; 10-30 day endurance to 300m depth.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2030,17 +2020,17 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Exact missile type used in the Feb 2024 test is disputed among sources (Fateh-110/Zolfaghar/Dezful variants all cited).</t>
+          <t>Delivered under Germany's Kurs Marine 2035+ program after a 2-week German Navy trial.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>images/shahid-mahdavi.jpg</t>
+          <t>images/bluewhale-uuv.jpg</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Iranian govt / Wikimedia Commons</t>
+          <t>Swadim / Wikimedia Commons (CC0)</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2050,74 +2040,74 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Commissioning_ceremony_of_IRGC_naval_vessels_in_March_2023_(06).jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:BlueWhale.jpg</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/IRIS_Shahid_Mahdavi</t>
+          <t>https://www.tkmsgroup.com/news/article/autonomous-underwater-vehicle-bluewhale-handed-over-to-german-navy-delivery-by-tkms-and-israel-aerospace-industries-as-part-of-the-kurs-marine-2035-program</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>IRIS Shahid Mahdavi — Wikipedia</t>
+          <t>BlueWhale AUV handed over to German Navy - TKMS Group</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>https://www.rusi.org/explore-our-research/publications/commentary/irans-modern-q-ship-threat-new-quarters</t>
+          <t>https://www.armyrecognition.com/news/navy-news/2026/germanys-new-bluewhale-autonomous-underwater-vehicle-is-transforming-baltic-maritime-surveillance</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Iran's Modern Q-Ship: A Threat from New Quarters — RUSI</t>
+          <t>Germany's BlueWhale AUV - Army Recognition</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hero-120-126cell</t>
+          <t>iron-beam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UVision Hero-120 126-Cell Multi-Launcher</t>
+          <t>Iron Beam</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rheinmetall/UVision 126-cell containerized launcher</t>
+          <t>Magen Or, Light Shield, Iron Beam 450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rheinmetall and UVision</t>
+          <t>Rafael Advanced Defense Systems (Elbit laser source)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Israel / Germany</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27 June 2024</t>
+          <t>December 2025</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Product reveal reported by TWZ/UAS Vision</t>
+          <t>First operational unit delivered to IDF</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Loitering munition</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2127,104 +2117,104 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Rheinmetall and its strategic partner UVision built a modified shipping container holding 126 launch cells for the Hero-120 loitering munition, arranged as three 42-cell arrays for massed swarm-saturation attacks. The Hero-120 itself has a 60 km range, 60-minute endurance, and a gimbaled EO/IR seeker for anti-armor strikes with under 1 meter CEP. Deployable on uncrewed surface vessels, civilian trucks, or static forward operating bases, the MOSA-compliant launcher lets a small force project sea-denial or area-control over a wide zone.</t>
+          <t>100kW-class laser (ten fused 10kW fiber lasers) with a dome turret; beam-generation and cooling equipment described as housed in two 40-ft container-like modules, generally stationary but relocatable.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Marketed as also compatible with the larger Hero-400 munition for deeper-strike missions.</t>
+          <t>The 'two 40-ft container modules' phrasing recurs in secondary sources but primary ISO-container wording not verified.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>images/hero-120-126cell.webp</t>
+          <t>images/iron-beam.jpg</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Rheinmetall / The War Zone</t>
+          <t>Rafael Advanced Defense Systems (via Wikimedia Commons)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://www.twz.com/news-features/shipping-container-launcher-packing-126-kamikaze-drones-hits-the-market</t>
+          <t>https://commons.wikimedia.org/wiki/File:Iron_beam_01.jpg</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>https://www.twz.com/news-features/shipping-container-launcher-packing-126-kamikaze-drones-hits-the-market</t>
+          <t>https://en.wikipedia.org/wiki/Iron_Beam</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Shipping Container Launcher Packing 126 Kamikaze Drones Hits The Market — The War Zone</t>
+          <t>Iron Beam - Wikipedia</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>https://www.uasvision.com/2024/06/27/shipping-container-launcher-packing-126-kamikaze-drones/</t>
+          <t>https://www.armyrecognition.com/news/army-news/2025/rafael-delivers-israels-first-operational-iron-beam-laser-shield-to-revolutionize-air-defense-era</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Shipping Container Launcher Packing 126 Kamikaze Drones — UAS Vision</t>
+          <t>Rafael Delivers First Operational Iron Beam - Army Recognition</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>socom-pfal</t>
+          <t>kawasaki-hel</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SOCOM Palletized Field Artillery Launcher (PFAL)</t>
+          <t>Kawasaki 100kW Laser C-UAS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PFAL</t>
+          <t>KHI Electric-Drive High-Power Laser System</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>U.S. Special Operations Command (SOCOM); contractor undisclosed</t>
+          <t>Kawasaki Heavy Industries (KHI)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>December 2025</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Identified at Fort Bragg</t>
+          <t>Installed aboard JMSDF test ship JS Asuka</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Artillery / coastal</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2234,27 +2224,27 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>The Palletized Field Artillery Launcher (PFAL) is a prototype erectable launcher housed in a standard container footprint, identified at Fort Bragg in 2025, capable of firing the same Multiple Launch Rocket System Family of Munitions (MFOM) used by the HIMARS system. It lets SOCOM and conventional ground units distribute long-range precision fires from civilian-pattern Palletized Load System (PLS) trucks or maritime vessels, hiding 'boxes of rockets' in plain sight and complicating adversary targeting.</t>
+          <t>100kW-class laser (ten fused 10kW fiber lasers) for counter-UAS, packaged into two 40-ft ISO container modules with a domed turret, installed on JS Asuka's deck for maritime trials.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Status is prototype; identified via open-source sighting rather than an official unveiling.</t>
+          <t>Prototype delivered to Japan MoD Feb 2023.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>images/socom-pfal.jpg</t>
+          <t>images/kawasaki-hel.jpg</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>The War Zone (Fort Bragg)</t>
+          <t>Koji Miyake / Shephard Media</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2264,94 +2254,104 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>https://www.twz.com/land/mysterious-guided-rocket-launcher-disguised-in-a-shipping-container-at-fort-bragg-identified</t>
+          <t>https://www.shephardmedia.com/news/landwarfareintl/kawasaki-develops-c-uas-laser-system-for-japanese-military/</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>https://www.twz.com/land/mysterious-guided-rocket-launcher-disguised-in-a-shipping-container-at-fort-bragg-identified</t>
+          <t>https://www.navalnews.com/naval-news/2025/12/high-energy-laser-system-spotted-aboard-jmsdf-test-ship/</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Mysterious Guided Rocket Launcher Disguised In A Shipping Container At Fort Bragg Identified — The War Zone</t>
+          <t>High-Energy Laser Aboard JMSDF Test Ship - Naval News</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>https://www.janes.com/osint-insights/defence-news/industry/dsei-japan-2023-kawasaki-heavy-industries-unveils-high-energy-laser-c-uas</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>KHI unveils high-energy laser C-UAS - Janes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>invariant-cws-a</t>
+          <t>zhong-da-79</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Invariant CWS-A (Containerized Weapon System - APKWS)</t>
+          <t>Chinese Container-Ship Missile Battery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Killer Weapons Container</t>
+          <t>Zhong Da 79 'arsenal ship'</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Invariant Corporation</t>
+          <t>Chinese state / commercial shipbuilding (operator undisclosed)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>December 2025</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Product announcement</t>
+          <t>Photographed at a Shanghai shipyard, Dec 2025</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Naval arsenal</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Invariant's Containerized Weapon System - APKWS (CWS-A) pairs a 4-pack launcher for APKWS 2.75-inch laser-guided rockets with the L3 Wescam MX-10 RSTA-D sensor suite and radar, claiming better than a 90% kill ratio against Class 2 and 3 UAS threats. The 'Killer Weapons Container' can be reconfigured with Javelin anti-tank missiles or heavy machine guns (M2, M134), managed through an integrated fire-control system and a Threat Illumination Verification System (TIVS).</t>
+          <t>A roughly 97 m merchant vessel, Zhong Da 79, was photographed at a Shanghai shipyard on the Huangpu River in December 2025 carrying deck-mounted containerised vertical launch cells — estimates range from 48 (Naval News) to 60 (The War Zone) tubes — plus a phased-array radar and a CIWS dome. Analysts suggest a possible fit of CJ-10 land-attack, YJ-18 anti-ship, or YJ-21 anti-ship ballistic missiles. It is the clearest modern example of a military-civil-fusion 'arsenal ship' built on a container-ship hull.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Sourced to a single manufacturer product page; independent fielding or test details are not given in the document.</t>
+          <t>Cell count is unsettled (48 vs 60 for the same vessel); operational-vs-mockup status unconfirmed; missile fit is analyst speculation.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>images/invariant-cws-a.jpg</t>
+          <t>images/zhong-da-79.jpg</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>The War Zone</t>
+          <t>The War Zone / social media</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2361,39 +2361,49 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>https://www.invariant-corp.com/cws-a/</t>
+          <t>https://www.twz.com/sea/chinese-cargo-ship-packed-full-of-modular-missile-launchers-emerges</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://www.invariant-corp.com/cws-a/</t>
+          <t>https://www.navalnews.com/naval-news/2025/12/container-ship-turned-missile-battery-spotted-in-china/</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CWS-A — Invariant Corp.</t>
+          <t>Container Ship Turned Missile Battery Spotted In China — Naval News</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>https://www.twz.com/sea/chinese-cargo-ship-packed-full-of-modular-missile-launchers-emerges</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Chinese Cargo Ship Packed Full Of Modular Missile Launchers Emerges — The War Zone</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>uk-gravehawk</t>
+          <t>xv-excalibur</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UK Gravehawk</t>
+          <t>XV Excalibur XLUUV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Team Kindred containerized C-UAS launcher</t>
+          <t>Project Cetus XLUUV, Excalibur</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BAE Systems and UK Ministry of Defence (Team Kindred), funded jointly with Denmark</t>
+          <t>MSubs Ltd / UK Submarine Delivery Agency</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2403,22 +2413,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Early 2025</t>
+          <t>December 2025</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fielded for Ukraine</t>
+          <t>Handed over to Royal Navy</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Autonomous vehicle</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2428,7 +2438,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Developed over 18 months by Team Kindred — a UK MoD and BAE Systems collaboration funded jointly by the UK and Denmark — Gravehawk mounts a twin-arm launcher for Soviet-designed R-73 infrared-guided missiles and an electro-optical targeting camera inside a 20-ft shipping container, fielded for Ukraine's armed forces in early 2025. Purpose-built to intercept Shahed-type loitering munitions, the container can be mounted on commercial hook-loading trucks for rapid shoot-and-scoot operations. A related UK-Estonian venture, Babcock and Frankenburg Technologies, announced a joint low-cost containerized anti-drone launcher in early 2026.</t>
+          <t>A 12m, ~19-25 tonne extra-large uncrewed underwater vehicle technology testbed, sized to be transported worldwide inside a standard shipping container; controlled submerged from a remote centre in Australia during Talisman Sabre 2025.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2438,104 +2448,104 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Babcock/Frankenburg anti-drone launcher (announced early 2026) is a related but separate program, folded into this entry's notes rather than given its own entry.</t>
+          <t>Culmination of Project Cetus; payload bay can carry mines, smaller UUVs, sensors.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>images/uk-gravehawk.jpg</t>
+          <t>images/xv-excalibur.jpg</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>UK Defence Equipment &amp; Support / Army Technology</t>
+          <t>Royal Navy / UK MOD (OGL v3.0)</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>https://www.army-technology.com/news/revealed-first-images-of-ukraines-gravehawk/</t>
+          <t>https://commons.wikimedia.org/wiki/File:Cetus-at-an-angle-front.jpg</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Gravehawk</t>
+          <t>https://www.navalnews.com/naval-news/2026/01/autonomous-submarine-xv-excalibur-handed-to-royal-navy/</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Gravehawk — Wikipedia</t>
+          <t>Autonomous submarine XV Excalibur handed to Royal Navy - Naval News</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>https://resiliencemedia.co/babcock-and-frankenburg-will-build-a-containerized-launch-system-for-anti-drone-missiles/</t>
+          <t>https://www.naval-technology.com/news/royal-navy-name-project-cetus-xluuv-excalibur/</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Babcock and Frankenburg will build a containerized launch system for anti-drone missiles — Resilience Media</t>
+          <t>Royal Navy name Project Cetus XLUUV Excalibur - Naval Technology</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rnln-mss</t>
+          <t>vampire-casket</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Royal Netherlands Navy Multifunctional Support Ships (MSS)</t>
+          <t>L3Harris VAMPIRE CASKET</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RNLN MSS containerized Barak ER</t>
+          <t>VAMPIRE CASKET, Containerized VAMPIRE counter-drone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Royal Netherlands Navy (RNLN), with IAI-supplied weapons</t>
+          <t>L3Harris Technologies</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>October 2025</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Program/design details reported</t>
+          <t>Shown in L3Harris roadmap imagery</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Naval arsenal</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>The Royal Netherlands Navy is outfitting new Multifunctional Support Ships, escorts for the De Zeven Provincien-class air-defense frigates, with a 28 x 8.5 m aft deck accommodating four 20-ft ISO containers. The primary payload is containerized IAI Barak ER surface-to-air missiles, capable of defeating cruise and short-range ballistic missiles at ranges up to 150 km, supplemented by Harop loitering munitions for land-attack roles, with the frigates providing targeting data and command and control — effectively making the MSS a distributed magazine for the fleet.</t>
+          <t>A standard-container mounting of L3Harris's VAMPIRE counter-drone system, combining its sensor-and-launcher architecture with kinetic effectors including laser-guided 70mm rockets.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2545,94 +2555,94 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Program is still in development; specifics sourced to a single analyst article.</t>
+          <t>From ChatGPT deep-research set. Depicted as a proposed family variant; dimensions/procurement/fielding limited.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>images/rnln-mss.jpg</t>
+          <t>images/vampire-casket.jpg</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Royal Netherlands Navy / The War Zone</t>
+          <t>L3Harris (via The War Zone)</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
+          <t>https://www.twz.com/air/entire-family-of-vampire-counter-drone-systems-unveiled</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
+          <t>https://www.twz.com/air/entire-family-of-vampire-counter-drone-systems-unveiled</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
+          <t>Entire Family Of VAMPIRE Counter-Drone Systems Unveiled - TWZ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>operation-spiderweb</t>
+          <t>aerovironment-locust-phel</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operation Spiderweb</t>
+          <t>AeroVironment LOCUST P-HEL</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SBU container-hidden drone strike</t>
+          <t>Palletized High Energy Laser</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Security Service of Ukraine (SBU)</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1 June 2025</t>
+          <t>October 2025</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Executed 1 Jun 2025</t>
+          <t>Live-fire test aboard USS George H.W. Bush</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Covert / disguised</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Concealed cargo</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>In the most consequential real-world use of the concealed-container concept, Ukraine's SBU hid around 117 FPV quadcopter drones inside wooden cabin-style containers on flatbed trucks driven deep into Russia by unwitting drivers. On 1 June 2025 the roofs were raised by remote control and the drones swarmed out to strike Russian strategic-bomber bases, damaging Tu-95, Tu-22M3, Tu-160 and A-50 aircraft. It proved that the Club-K idea works — with cheap drones instead of cruise missiles.</t>
+          <t>In October 2025 the U.S. Navy lashed AeroVironment's Palletized High Energy Laser (P-HEL) — built around the 20-26 kW-class LOCUST laser — to the flight deck of the aircraft carrier USS George H.W. Bush, using Fortem radars and Lockheed's Sanctum battle-management software to track and destroy multiple target drones. The test demonstrated that a palletized/containerized directed-energy weapon can draw on a host ship's organic power to provide functionally unlimited magazine depth against drone swarms without any permanent shipboard integration.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2642,84 +2652,94 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Structures were wooden mobile-cabin boxes rather than ISO containers; 'loitering munitions' is a loose label for the FPV quadcopters used.</t>
+          <t>Distinct from the higher-power Lockheed HELIOS; LOCUST is the lower-power (20-26 kW) AeroVironment system.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>images/operation-spiderweb.jpg</t>
+          <t>images/aerovironment-locust-phel.jpg</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>SBU / Wikimedia Commons</t>
+          <t>U.S. Navy / DVIDS</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>public-domain-gov</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:2025-06-01_DroneAttack_SBU_(Drones_in_containers).jpg</t>
+          <t>https://www.twz.com/news-features/navy-fires-dronefrying-locust-laser-from-supercarrier-uss-george-h-w-bush</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Operation_Spiderweb</t>
+          <t>https://www.twz.com/news-features/navy-fires-dronefrying-locust-laser-from-supercarrier-uss-george-h-w-bush</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Operation Spiderweb — Wikipedia</t>
+          <t>Navy Fires Drone-Frying LOCUST Laser From Supercarrier USS George H.W. Bush — The War Zone</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>https://www.avinc.com/avinc_product_family/locust/</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Locust — AeroVironment</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>aerovironment-locust-phel</t>
+          <t>cm-300la</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AeroVironment LOCUST P-HEL</t>
+          <t>Iran CM-300LA Land-Attack Container Launcher</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palletized High Energy Laser</t>
+          <t>CM-300LA, Container Missile-300 Land Attack</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Iranian defence industry (AIO/Shahid Bagheri lineage)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>October 2025</t>
+          <t>September 2025</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Live-fire test aboard USS George H.W. Bush</t>
+          <t>Shown at PARTNER 2025 exhibition (Belgrade)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2729,114 +2749,114 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>In October 2025 the U.S. Navy lashed AeroVironment's Palletized High Energy Laser (P-HEL) — built around the 20-26 kW-class LOCUST laser — to the flight deck of the aircraft carrier USS George H.W. Bush, using Fortem radars and Lockheed's Sanctum battle-management software to track and destroy multiple target drones. The test demonstrated that a palletized/containerized directed-energy weapon can draw on a host ship's organic power to provide functionally unlimited magazine depth against drone swarms without any permanent shipboard integration.</t>
+          <t>A three-round canister built to mimic a standard 20-ft ISO container on a civilian-style 6x6 truck, firing a subsonic (~300 km) sea-skimming land-attack cruise missile; onboard power, auto-leveling and shoot-and-scoot salvo capability.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Distinct from the higher-power Lockheed HELIOS; LOCUST is the lower-power (20-26 kW) AeroVironment system.</t>
+          <t>Reported by three trade outlets from the same unveiling; no TWZ/Naval News/Janes coverage yet.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>images/aerovironment-locust-phel.jpg</t>
+          <t>images/cm-300la.jpg</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>U.S. Navy / DVIDS</t>
+          <t>Army Recognition</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>public-domain-gov</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://www.twz.com/news-features/navy-fires-dronefrying-locust-laser-from-supercarrier-uss-george-h-w-bush</t>
+          <t>https://www.armyrecognition.com/news/army-news/2025/iran-presents-cm-300la-land-attack-container-launcher-firing-three-cruise-missiles-in-minutes</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>https://www.twz.com/news-features/navy-fires-dronefrying-locust-laser-from-supercarrier-uss-george-h-w-bush</t>
+          <t>https://www.armyrecognition.com/news/army-news/2025/iran-presents-cm-300la-land-attack-container-launcher-firing-three-cruise-missiles-in-minutes</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Navy Fires Drone-Frying LOCUST Laser From Supercarrier USS George H.W. Bush — The War Zone</t>
+          <t>Iran Presents CM-300LA Land-Attack Container Launcher - Army Recognition</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>https://www.avinc.com/avinc_product_family/locust/</t>
+          <t>https://milivox.media/iran-cm300la-cruise-missile-container-launcher/</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Locust — AeroVironment</t>
+          <t>Iran Unveils CM-300LA Containerized Cruise Missile Launcher - Milivox</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zhong-da-79</t>
+          <t>saab-rbs15-cdms</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chinese Container-Ship Missile Battery</t>
+          <t>Saab Coastal Defence Missile System (RBS15 CDMS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Zhong Da 79 'arsenal ship'</t>
+          <t>Saab CDMS, RBS15 containerized coastal launcher</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Chinese state / commercial shipbuilding (operator undisclosed)</t>
+          <t>Saab</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>December 2025</t>
+          <t>September 2025</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Photographed at a Shanghai shipyard, Dec 2025</t>
+          <t>Publicly unveiled; on order for Swedish Armed Forces</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Naval arsenal</t>
+          <t>Artillery / coastal</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A roughly 97 m merchant vessel, Zhong Da 79, was photographed at a Shanghai shipyard on the Huangpu River in December 2025 carrying deck-mounted containerised vertical launch cells — estimates range from 48 (Naval News) to 60 (The War Zone) tubes — plus a phased-array radar and a CIWS dome. Analysts suggest a possible fit of CJ-10 land-attack, YJ-18 anti-ship, or YJ-21 anti-ship ballistic missiles. It is the clearest modern example of a military-civil-fusion 'arsenal ship' built on a container-ship hull.</t>
+          <t>A truck-carried launcher matching the footprint of a 20-ft ISO container, holding four RBS15 Mk3/Mk4 anti-ship missiles (&gt;300 km) with a shoot-and-scoot relocation under 120 seconds.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2846,17 +2866,17 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Cell count is unsettled (48 vs 60 for the same vessel); operational-vs-mockup status unconfirmed; missile fit is analyst speculation.</t>
+          <t>RBS15 fielded across Sweden, Finland, Germany, Poland, Bulgaria, Croatia.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>images/zhong-da-79.jpg</t>
+          <t>images/saab-rbs15-cdms.jpg</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>The War Zone / social media</t>
+          <t>Army Recognition Group</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2866,49 +2886,49 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://www.twz.com/sea/chinese-cargo-ship-packed-full-of-modular-missile-launchers-emerges</t>
+          <t>https://www.armyrecognition.com/news/navy-news/2025/saabs-new-coastal-defense-system-built-on-rbs15-missile-targets-growing-maritime-threats</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2025/12/container-ship-turned-missile-battery-spotted-in-china/</t>
+          <t>https://www.saab.com/newsroom/stories/2025/september/a-powerful-new-deterrent-to-seaborne-threats</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Container Ship Turned Missile Battery Spotted In China — Naval News</t>
+          <t>A powerful new deterrent to seaborne threats - Saab</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>https://www.twz.com/sea/chinese-cargo-ship-packed-full-of-modular-missile-launchers-emerges</t>
+          <t>https://www.armyrecognition.com/news/navy-news/2025/saabs-new-coastal-defense-system-built-on-rbs15-missile-targets-growing-maritime-threats</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Chinese Cargo Ship Packed Full Of Modular Missile Launchers Emerges — The War Zone</t>
+          <t>Saab's New Coastal Defense System - Army Recognition</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>sinarit-submarine</t>
+          <t>roketsan-eren</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sinarit Autonomous Submarine</t>
+          <t>Roketsan EREN Containerized Loitering Munition Launcher</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Datum Submarine Technologies Sinarit UUV</t>
+          <t>EREN Container Launch System, Roketsan EREN ground launcher</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Datum Submarine Technologies</t>
+          <t>Roketsan</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2918,22 +2938,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>July 2025</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Unveiled at SAHA Expo, Istanbul</t>
+          <t>Unveiled at IDEF 2025 (Istanbul)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Autonomous vehicle</t>
+          <t>Loitering munition</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2943,27 +2963,27 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Turkish firm Datum Submarine Technologies unveiled the Sinarit at the SAHA Expo in Istanbul in May 2026: an 11.5-meter, 19.8-ton uncrewed autonomous diesel-electric submarine explicitly designed to fit inside a standard shipping container, allowing transport by commercial truck or Airbus A400M cargo aircraft. Operating to 100-meter depths, it can autonomously launch its own containerized payloads while submerged, including Roketsan Atmaca anti-ship missiles (250 km range, active RF seeker), Orka lightweight torpedoes, and swarms of FPV attack drones that breach the surface to strike before the submarine withdraws undetected.</t>
+          <t>A truck-mounted launcher disguised as a civilian freight container, concealing up to 12 EREN jet-powered dual-role (anti-air/anti-ground) loitering munitions (35kg, &gt;100 km); serial production planned for 2026.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Newly unveiled prototype; sourced to a single outlet (Autonocion) in the document.</t>
+          <t>Multiple independent outlets confirm the container disguise and IDEF 2025 debut.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>images/sinarit-submarine.jpg</t>
+          <t>images/roketsan-eren.jpg</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Datum Submarine Technologies / Naval News</t>
+          <t>Army Recognition Group</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2973,64 +2993,74 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2026/05/datum-introduces-strike-capable-sinarit-xluuv/</t>
+          <t>https://armyrecognition.com/news/army-news/2025/roketsan-debuts-containerized-eren-loitering-munition-launcher-at-idef-2025-for-covert-deep-strikes</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://www.autonocion.com/us/drone-submarine-turkey/</t>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/defense-news-army-2025/roketsan-debuts-containerized-eren-loitering-munition-launcher-at-idef-2025-for-covert-deep-strikes</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Turkey just unveiled a 19.8-ton drone submarine built to launch FPV drone swarms, anti-ship missiles, torpedoes and mines while submerged — Autonocion.com</t>
+          <t>Roketsan Debuts Containerized EREN Launcher at IDEF 2025 - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>https://united24media.com/latest-news/inspired-by-ukraines-operation-spiderweb-turkey-unveils-hidden-drone-launcher-for-deep-strikes-10361</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Turkey Unveils Hidden Drone Launcher for Deep Strikes - United24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>containerized-helios</t>
+          <t>roketsan-kara-atmaca</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Containerised HELIOS Laser</t>
+          <t>Roketsan Kara Atmaca Container Launcher</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mk 5 Mod 0 HELIOS; Containerized Maritime High Energy Laser Weapon System</t>
+          <t>Kara Atmaca, ATMACA-UM Container Launch System</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lockheed Martin (for U.S. Navy)</t>
+          <t>Roketsan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026 (draft FY2027 NDAA)</t>
+          <t>July 2025</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Congressional funding push, draft FY2027 NDAA</t>
+          <t>Unveiled at IDEF 2025 (Istanbul)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3040,7 +3070,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>HELIOS (High-Energy Laser with Integrated Optical-dazzler and Surveillance) is a 60 kW-class Lockheed Martin laser, designated Mk 5 Mod 0 and already deployed on the destroyer USS Preble. In 2026 an early draft of the FY2027 National Defense Authorization Act moved to authorise $5 million for a containerised HELIOS plus $2.5 million for a separate 'Containerized Maritime High Energy Laser Weapon System.' The push would repackage the shipboard laser into a deployable container for wider basing.</t>
+          <t>A launcher disguised as an ordinary 20/40-ft commercial container, firing up to six Kara Atmaca land-attack/anti-ship cruise missiles (~250-280 km, 220kg warhead), movable by truck, rail or civilian cargo vessel.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3050,59 +3080,69 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A draft authorisation, not enacted law and not yet built.</t>
+          <t>Roketsan states it is fully operational; multiple independent outlets confirm the container form factor.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>images/containerized-helios.jpg</t>
+          <t>images/roketsan-kara-atmaca.jpg</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>U.S. DoD DOT&amp;E report</t>
+          <t>Army Recognition Group</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>public-domain-gov</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://www.twz.com/news-features/containerized-variant-of-navys-drone-swatting-helios-laser-being-pushed-by-congress</t>
+          <t>https://www.armyrecognition.com/news/army-news/2025/tuerkiye-debuts-kara-atmaca-container-launcher-at-idef-2025-for-covert-and-mobile-land-based-strike-roles</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>https://www.twz.com/news-features/containerized-variant-of-navys-drone-swatting-helios-laser-being-pushed-by-congress</t>
+          <t>https://www.armyrecognition.com/news/army-news/2025/tuerkiye-debuts-kara-atmaca-container-launcher-at-idef-2025-for-covert-and-mobile-land-based-strike-roles</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Containerized Variant Of Navy's Drone-Swatting HELIOS Laser Being Pushed By Congress — The War Zone</t>
+          <t>Turkiye Debuts Kara Atmaca Container Launcher at IDEF 2025 - Army Recognition</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>https://interestingengineering.com/military/shipping-containers-into-surprise-missile-launchers</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Turkey turns cargo container into missile-in-a-box - Interesting Engineering</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>lockheed-grizzly</t>
+          <t>socom-pfal</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lockheed Martin GRIZZLY</t>
+          <t>SOCOM Palletized Field Artillery Launcher (PFAL)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Containerized Hellfire/JAGM Launcher</t>
+          <t>PFAL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>U.S. Special Operations Command (SOCOM); contractor undisclosed</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3112,22 +3152,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>July 2025</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Live-fire validation at Yuma Proving Ground</t>
+          <t>SOCOM prototype identified at Fort Bragg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Artillery / coastal</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3137,201 +3177,191 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>GRIZZLY is a 10-ft containerized launcher built on the proven M299 launcher architecture, capable of firing up to eight AGM-114 Hellfire or Joint Air-to-Ground Missiles (JAGM); its roof hinges open for vertical or angled launch. In live-fire tests at Yuma Proving Ground in June 2026, GRIZZLY successfully intercepted Group 3 attack drones using radar cues from Fortem Technologies R-40 radars and Lockheed's Sanctum battle-management software. It gives expeditionary forces a rapidly deployable counter-UAS and anti-armor capability in a single box.</t>
+          <t>The Palletized Field Artillery Launcher (PFAL) is a prototype container-form launcher platform owned by U.S. Special Operations Command, publicly identified at Fort Bragg in July 2025. The Army has stressed it is not MLRS and is not fielded to the Army. The prototype fires the current MLRS Family of Munitions (MFOM) — 227mm guided rockets and the ATACMS short-range ballistic missile — but not the newer Precision Strike Missile (PrSM). MFOM munitions come in standardised pods (six rockets, a single ATACMS, or two PrSMs each), and the PFAL launcher accommodates two pods at once, letting SOCOM distribute long-range precision fires from a container-sized platform that hides in plain sight.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Dual-role system: demonstrated primarily as counter-UAS in its highlighted 2026 test, though the M299/Hellfire/JAGM armament is originally an anti-armor weapon.</t>
+          <t>Status is prototype; identified via open-source sighting rather than an official unveiling.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>images/lockheed-grizzly.jpg</t>
+          <t>images/socom-pfal.jpg</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>U.S. Army</t>
+          <t>The War Zone (Fort Bragg)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>public-domain-gov</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://www.army.mil/article/293025/</t>
+          <t>https://www.twz.com/wp-content/uploads/2025/07/pfal-container-launcher-fort-bragg.jpg</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://www.army.mil/article/293025/u_s_army_yuma_proving_ground_tests_containerized_missile_launcher</t>
+          <t>https://www.twz.com/land/mysterious-guided-rocket-launcher-disguised-in-a-shipping-container-at-fort-bragg-identified</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>U.S. Army Yuma Proving Ground tests containerized missile launcher — Army.mil</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>https://www.twz.com/air/hellfire-missile-launcher-tucked-inside-a-container-rolled-out-by-lockheed</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Hellfire Missile Launcher Tucked Inside A Container Rolled Out By Lockheed — The War Zone</t>
+          <t>Mysterious Guided Rocket Launcher Disguised In A Shipping Container At Fort Bragg Identified — The War Zone</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hanwha-striker-musv</t>
+          <t>operation-spiderweb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hanwha Striker MUSV</t>
+          <t>Operation Spiderweb</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Striker-S</t>
+          <t>SBU container-hidden drone strike</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hanwha Systems</t>
+          <t>Security Service of Ukraine (SBU)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>1 June 2025</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Unveiled at Eurosatory 2026</t>
+          <t>Executed 1 Jun 2025</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Autonomous vehicle</t>
+          <t>Covert / disguised</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Concealed cargo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>South Korea's Hanwha Systems introduced the Striker-S at Eurosatory 2026, a 35-meter low-observable-hull Medium Uncrewed Surface Vessel (MUSV) with a mission deck for a 10-ton containerized payload module. Hanwha pairs it with a containerized launcher for the Chunmoo missile family, specifically the CTM-ASBM (Chunmoo Tactical Missile - Anti-Ship Ballistic Missile), a GPS/INS- and imaging-infrared-guided 280mm missile that lets the autonomous vessel act as a remote missile carrier extending a task group's strike radius by up to 160 km.</t>
+          <t>In the most consequential real-world use of the concealed-container concept, Ukraine's SBU hid around 117 FPV quadcopter drones inside wooden cabin-style containers on flatbed trucks driven deep into Russia by unwitting drivers. On 1 June 2025 the roofs were raised by remote control and the drones swarmed out to strike Russian strategic-bomber bases, damaging Tu-95, Tu-22M3, Tu-160 and A-50 aircraft. It proved that the Club-K idea works — with cheap drones instead of cruise missiles.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Newly unveiled at Eurosatory 2026; fielding/testing status not yet established.</t>
+          <t>Structures were wooden mobile-cabin boxes rather than ISO containers; 'loitering munitions' is a loose label for the FPV quadcopters used.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>images/hanwha-striker-musv.jpg</t>
+          <t>images/operation-spiderweb.jpg</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Hanwha Systems / Army Recognition</t>
+          <t>SBU / Wikimedia Commons</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2026/06/hanwha-unveils-striker-musv-family-at-eurosatory-2026/</t>
+          <t>https://commons.wikimedia.org/wiki/File:2025-06-01_DroneAttack_SBU_(Drones_in_containers).jpg</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2026/06/hanwha-unveils-striker-musv-family-at-eurosatory-2026/</t>
+          <t>https://en.wikipedia.org/wiki/Operation_Spiderweb</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Hanwha Unveils Striker MUSV Family at Eurosatory 2026 — Naval News</t>
+          <t>Operation Spiderweb — Wikipedia</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rheinmetall-cml-fv014</t>
+          <t>elbit-seagull-usv</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rheinmetall Containerized Missile Launcher (CML) / FV-014</t>
+          <t>Elbit Seagull USV</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CML; FV-014 loitering munition launcher</t>
+          <t>Seagull MCM/ASW USV, Seagull Mk3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rheinmetall</t>
+          <t>Elbit Systems</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15 June 2026</t>
+          <t>February 2025</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>World premiere at Eurosatory 2026</t>
+          <t>4th-gen Seagull showcased at NAVDEX 2025</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Loitering munition</t>
+          <t>Autonomous vehicle</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3341,7 +3371,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Unveiled at Eurosatory 2026, the Containerized Missile Launcher (CML) packs up to 18 FV-014 loitering munitions into a 20-foot ISO container with internal battery reserves, an optional generator, and a low-power sleep mode for extended covert standby. The FV-014 itself has a 100 km range, 70 minutes of endurance, and a 4-5 kg HEDP warhead able to penetrate over 600 mm of armor, flown man-in-the-loop but capable of coordinated swarm salvos of 18 munitions from a single operator. The CML plugs into Rheinmetall's Battlesuite C4I architecture, and in April 2026 the Bundeswehr awarded Rheinmetall a multi-billion-euro framework contract with an initial 300 million euro production order.</t>
+          <t>A 12m multi-mission unmanned surface vessel (MCM/ASW/EW) that ships and deploys from a standard 40-ft ISO container; the planned 20m Mk3 adds deck space for a standardised 20-ft ISO container payload.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3351,94 +3381,94 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Bundeswehr framework contract announced the same year as unveiling; drones use man-in-the-loop EO guidance, not full autonomy, despite the launcher's autonomous standby features.</t>
+          <t>100% success in Royal Navy WISEX mine-hunting trials.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>images/rheinmetall-cml-fv014.jpg</t>
+          <t>images/elbit-seagull-usv.jpg</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Rheinmetall / Army Recognition</t>
+          <t>Elbit Systems</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://www.rheinmetall.com/en/products/weapon-stations/containerized-missile-launcher</t>
+          <t>https://www.elbitsystems.com/unmanned/maritime/unmanned-surface-vessel/seagull-usv</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://thedefensewatch.com/military-ordnance/rheinmetall-cml-fv014-loitering-munition-eurosatory-2026/</t>
+          <t>https://www.elbitsystems.com/unmanned/maritime/unmanned-surface-vessel/seagull-usv</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Rheinmetall Unveils CML Multi-Launcher To Expand FV-014 Loitering Munition Strike Capability — The Defense Watch</t>
+          <t>Seagull USV - Elbit Systems</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>https://www.rheinmetall.com/en/media/news-watch/news/2026/06/2026-06-15-world-premiere-at-eurosatory-rheinmetall-presents-cml-multi-launcher-for-fv-014-loitering-munition</t>
+          <t>https://www.janes.com/osint-insights/defence-news/sea/navdex-2025-elbit-system-showcases-fourth-generation-seagull-usv</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Containerised Missile Launcher makes its debut at Eurosatory — Rheinmetall</t>
+          <t>NAVDEX 2025: 4th-gen Seagull USV - Janes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>csdcs</t>
+          <t>northrop-ares</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CSDCS Container-Type Sea Defense Combat System</t>
+          <t>Northrop Grumman AReS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CSDCS, containerized coastal defense system, China's Club-K</t>
+          <t>AReS, Advanced Reactive Strike, containerized ground-launched AARGM-ER</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CASIC (China Aerospace Science and Industry Corp)</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2022-11-08</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>November 2022</t>
+          <t>January 2025</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Unveiled at Airshow China (Zhuhai)</t>
+          <t>Unveiled at Surface Navy Association Symposium</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Missile launcher</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3448,27 +3478,27 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A self-contained combat system built into a 20/40-ft container (~13m x 2.3m x 2.5m) with operator station, power and a quadruple launcher firing YJ-12E supersonic or YJ-18E subsonic anti-ship cruise missiles from ships, trucks or trains; China's openly-marketed Club-K analogue with broader missile compatibility.</t>
+          <t>A 20/40-ft ISO container concealing a four-cell vertical launcher for ground-launched AARGM-ER anti-radiation missiles (~150 km), aimed at rapidly deployable suppression of enemy radar and air-defense sites.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Distinct from the Zhong Da 79 arsenal-ship entry already in the list; this is the standalone containerized launcher product.</t>
+          <t>Northrop and Hanwha signed an MOA (Apr 2026) to co-develop an AReS rocket booster.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>images/csdcs.jpg</t>
+          <t>images/northrop-ares.jpg</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Fan Wei / Global Times</t>
+          <t>Army Recognition Group</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3478,94 +3508,84 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://www.globaltimes.cn/page/202211/1279349.shtml</t>
+          <t>https://www.armyrecognition.com/news/army-news/2025/new-northrop-grumman-ares-missile-launcher-enables-fast-deployment-against-enemy-radar</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>https://www.globaltimes.cn/page/202211/1279349.shtml</t>
+          <t>https://www.armyrecognition.com/news/army-news/2025/new-northrop-grumman-ares-missile-launcher-enables-fast-deployment-against-enemy-radar</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>China debuts container-type missile launch system - Global Times</t>
+          <t>New Northrop Grumman AReS missile launcher - Army Recognition</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>https://en.defence-ua.com/news/in_2022_china_unveiled_its_copy_of_russias_club_k_missile_system_now_it_threatens_us_navy-14827.html</t>
+          <t>https://www.fw-mag.com/shownews/351/sna-2025-sees-northrop-grumman-push-ares-a-containerized-ground-launched-aargm-er</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>China unveiled its copy of Russia's Club-K - Defense Express</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>https://www.vermilionchina.com/p/36-chinas-container-launched-cruise</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>China's Container-launched Cruise Missiles - Vermilion China</t>
+          <t>SNA 2025: Northrop Grumman push AReS - FW-MAG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yj-18c</t>
+          <t>invariant-cws-a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YJ-18C Container-Launched Cruise Missile</t>
+          <t>Invariant CWS-A (Containerized Weapon System - APKWS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YJ-18C, container-launched YJ-18 land-attack variant</t>
+          <t>Killer Weapons Container</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CASC (China Aerospace Science and Technology Corp)</t>
+          <t>Invariant Corporation</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2019-03-01</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>March 2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>US intelligence-sourced reporting of container-launched variant</t>
+          <t>Product announcement</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Covert strike</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Concealed cargo</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Reported land-attack variant of the YJ-18 cruise missile (&gt;1,000 km, low-RCS) designed to fire from launchers built to look like standard ISO shipping containers on merchant-ship decks or trucks; conceptually a Chinese Club-K.</t>
+          <t>Invariant's Containerized Weapon System - APKWS (CWS-A) pairs a 4-pack launcher for APKWS 2.75-inch laser-guided rockets with the L3 Wescam MX-10 RSTA-D sensor suite and radar, claiming better than a 90% kill ratio against Class 2 and 3 UAS threats. The 'Killer Weapons Container' can be reconfigured with Javelin anti-tank missiles or heavy machine guns (M2, M134), managed through an integrated fire-control system and a Threat Illumination Verification System (TIVS).</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3575,17 +3595,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Traces to a single 2019 US-intel report; missile never officially shown separately from the container concept.</t>
+          <t>Sourced to a single manufacturer product page; independent fielding or test details are not given in the document.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>images/yj-18c.jpg</t>
+          <t>images/invariant-cws-a.jpg</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>CCTV News via Global Times</t>
+          <t>The War Zone</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3595,79 +3615,59 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://www.globaltimes.cn/page/202509/1342523.shtml</t>
+          <t>https://www.invariant-corp.com/cws-a/</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://freebeacon.com/national-security/china-building-long-range-cruise-missile-launched-from-ship-container/</t>
+          <t>https://www.invariant-corp.com/cws-a/</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>China Building Cruise Missile Launched from Ship Container - Free Beacon</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>https://www.armyrecognition.com/archives/archives-naval-defense/naval-defense-2019/china-is-building-long-range-cruise-missiles-launched-from-ship-containers</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>China building long-range cruise missiles from ship containers - Army Recognition</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>https://www.scmp.com/news/china/military/article/3341929/will-new-chinas-yj-18c-missile-be-logistics-killer-us-navy</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Will China's YJ-18C missile be a logistics killer - SCMP</t>
+          <t>CWS-A — Invariant Corp.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ivan-papanin-kalibr-k</t>
+          <t>rnln-mss</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Project 23550 Ivan Papanin Kalibr-K Container Module</t>
+          <t>Royal Netherlands Navy Multifunctional Support Ships (MSS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ivan Papanin containerized Kalibr, Project 23550 combat icebreaker</t>
+          <t>RNLN MSS containerized Barak ER</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Admiralty Shipyards / Morinformsystem-Agat lineage</t>
+          <t>Royal Netherlands Navy (RNLN), with IAI-supplied weapons</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>October 2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Naval News detailed the containerized-bay design; lead ship commissioned Sept 2025</t>
+          <t>Program/design details reported</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Purpose-built Arctic combat icebreaker/patrol ship with an open stern flex-bay designed to accept containerized Kalibr-K cruise-missile or Kh-35 anti-ship modules (up to 8 missiles); Russia's first near-operational Club-K-style warship fit.</t>
+          <t>The Royal Netherlands Navy is outfitting new Multifunctional Support Ships, escorts for the De Zeven Provincien-class air-defense frigates, with a 28 x 8.5 m aft deck accommodating four 20-ft ISO containers. The primary payload is containerized IAI Barak ER surface-to-air missiles, capable of defeating cruise and short-range ballistic missiles at ranges up to 150 km, supplemented by Harop loitering munitions for land-attack roles, with the frigates providing targeting data and command and control — effectively making the MSS a distributed magazine for the fleet.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3692,94 +3692,84 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Missile module reportedly not yet installed at commissioning (only the 76mm gun fitted); deck pre-wired for retrofit.</t>
+          <t>Program is still in development; specifics sourced to a single analyst article.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>images/ivan-papanin-kalibr-k.jpg</t>
+          <t>images/rnln-mss.jpg</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Alekc2m / Wikimedia Commons</t>
+          <t>Royal Netherlands Navy / The War Zone</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:%D0%9B%D0%B5%D0%B4%D0%BE%D0%BA%D0%BE%D0%BB_%22%D0%98%D0%B2%D0%B0%D0%BD_%D0%9F%D0%B0%D0%BD%D0%B0%D0%BD%D0%B8%D0%BD%22_01.jpg</t>
+          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2021/10/russia-arctic-patrol-ship-cruise-missiles/</t>
+          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Russia's Arctic Patrol Ships to Feature Cruise Missiles - Naval News</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>https://www.armyrecognition.com/news/navy-news/2024/russian-navys-new-ivan-papanin-project-23550-combat-icebreaker-begins-sea-trials-with-kalibr-missiles</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Ivan Papanin begins sea trials with Kalibr - Army Recognition</t>
+          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cm-300la</t>
+          <t>uk-gravehawk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Iran CM-300LA Land-Attack Container Launcher</t>
+          <t>UK Gravehawk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CM-300LA, Container Missile-300 Land Attack</t>
+          <t>Team Kindred containerized C-UAS launcher</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Iranian defence industry (AIO/Shahid Bagheri lineage)</t>
+          <t>BAE Systems and UK Ministry of Defence (Team Kindred), funded jointly with Denmark</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>September 2025</t>
+          <t>Early 2025</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Shown at PARTNER 2025 exhibition (Belgrade)</t>
+          <t>Fielded for Ukraine</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Covert strike</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3789,27 +3779,27 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A three-round canister built to mimic a standard 20-ft ISO container on a civilian-style 6x6 truck, firing a subsonic (~300 km) sea-skimming land-attack cruise missile; onboard power, auto-leveling and shoot-and-scoot salvo capability.</t>
+          <t>Developed over 18 months by Team Kindred — a UK MoD and BAE Systems collaboration funded jointly by the UK and Denmark — Gravehawk mounts a twin-arm launcher for Soviet-designed R-73 infrared-guided missiles and an electro-optical targeting camera inside a 20-ft shipping container, fielded for Ukraine's armed forces in early 2025. Purpose-built to intercept Shahed-type loitering munitions, the container can be mounted on commercial hook-loading trucks for rapid shoot-and-scoot operations. A related UK-Estonian venture, Babcock and Frankenburg Technologies, announced a joint low-cost containerized anti-drone launcher in early 2026.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Reported by three trade outlets from the same unveiling; no TWZ/Naval News/Janes coverage yet.</t>
+          <t>Babcock/Frankenburg anti-drone launcher (announced early 2026) is a related but separate program, folded into this entry's notes rather than given its own entry.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>images/cm-300la.jpg</t>
+          <t>images/uk-gravehawk.jpg</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Army Recognition</t>
+          <t>UK Defence Equipment &amp; Support / Army Technology</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3819,74 +3809,74 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/iran-presents-cm-300la-land-attack-container-launcher-firing-three-cruise-missiles-in-minutes</t>
+          <t>https://www.army-technology.com/news/revealed-first-images-of-ukraines-gravehawk/</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/iran-presents-cm-300la-land-attack-container-launcher-firing-three-cruise-missiles-in-minutes</t>
+          <t>https://en.wikipedia.org/wiki/Gravehawk</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Iran Presents CM-300LA Land-Attack Container Launcher - Army Recognition</t>
+          <t>Gravehawk — Wikipedia</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>https://milivox.media/iran-cm300la-cruise-missile-container-launcher/</t>
+          <t>https://resiliencemedia.co/babcock-and-frankenburg-will-build-a-containerized-launch-system-for-anti-drone-missiles/</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Iran Unveils CM-300LA Containerized Cruise Missile Launcher - Milivox</t>
+          <t>Babcock and Frankenburg will build a containerized launch system for anti-drone missiles — Resilience Media</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>shahed-136-container-launcher</t>
+          <t>cheongwang-skylight</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Iran Shahed-136 Tilting Container Drone Launcher</t>
+          <t>Cheongwang (Skylight) Laser</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shahed-136 catapult-container system, Great Prophet 17 launcher</t>
+          <t>Cheongwang, Skylight, Block-I laser air-defense</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HESA / IRGC Aerospace Force</t>
+          <t>Hanwha Aerospace with ADD</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2021-12-24</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>December 2021</t>
+          <t>December 2024</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Unveiled during Great Prophet 17 exercise</t>
+          <t>Initial operational fielding (Seoul area and frontline)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Loitering munition</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3896,7 +3886,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A tilting truck-mounted container-like box holding up to five Shahed-136 loitering munitions, each rocket-boosted into flight; container form factor allows palletizing onto rail cars, ships or other vehicles.</t>
+          <t>World's first laser weapon to reach operational military deployment; a 20kW fiber laser fully housed in a container-sized unit (~9m x 3m x 3m) with integrated radar mast, for point air-defense against small drones over Seoul.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3906,288 +3896,308 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Well corroborated; distinct from later no-container pickup-truck launch method.</t>
+          <t>Army Recognition explicitly calls it container-sized.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>images/shahed-136-container-launcher.jpg</t>
+          <t>images/cheongwang-skylight.jpg</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Amin Ahouei / Tasnim News Agency, via Wikimedia Commons</t>
+          <t>Army Recognition</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Sacred_Defence_Week_parade,_2023,_in_Tehran_(113).jpg</t>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/south-korea-commissions-cheongwang-its-most-modern-laser-system-to-counter-aerial-threats</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>https://iranprimer.usip.org/blog/2021/dec/28/irgc-tests-ballistic-missiles-drones-war-game</t>
+          <t>https://armyrecognition.com/news/army-news/army-news-2024/south-korea-commissions-cheongwang-its-most-modern-laser-system-to-counter-aerial-threats</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>IRGC Tests Ballistic Missiles, Drones in War Game - USIP</t>
+          <t>South Korea Commissions Cheongwang Laser - Army Recognition</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>https://militarnyi.com/en/news/shahed-loitering-munition-received-the-capability-to-be-launched-from-a-vehicle/</t>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/south-korea-deploys-skylight-laser-weapon-to-protect-seoul-capital-and-frontline-areas-from-north-korean-drones</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Shahed launched from a vehicle - Militarnyi</t>
+          <t>South Korea deploys Skylight laser - Army Recognition</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>shahid-roudaki</t>
+          <t>hero-120-126cell</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Iran Shahid Roudaki Twin Container Anti-Ship Launchers</t>
+          <t>UVision Hero-120 126-Cell Multi-Launcher</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shahid Roudaki forward-base ship container launchers, Qader/Ghadir deck launchers</t>
+          <t>Rheinmetall/UVision 126-cell containerized launcher</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>IRGC Navy (converted from merchant Galaxy F)</t>
+          <t>Rheinmetall and UVision</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Israel / Germany</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2020-11-19</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>November 2020</t>
+          <t>27 June 2024</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Commissioning ceremony reveal</t>
+          <t>Product reveal reported by TWZ/UAS Vision</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Naval arsenal</t>
+          <t>Loitering munition</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Four twin box/container-style launchers (eight Qader/Ghadir anti-ship cruise missiles) bolted to the forward deck of a converted forward-base ship, alongside road-mobile radar.</t>
+          <t>Rheinmetall and its strategic partner UVision built a modified shipping container holding 126 launch cells for the Hero-120 loitering munition, arranged as three 42-cell arrays for massed swarm-saturation attacks. The Hero-120 itself has a 60 km range, 60-minute endurance, and a gimbaled EO/IR seeker for anti-armor strikes with under 1 meter CEP. Deployable on uncrewed surface vessels, civilian trucks, or static forward operating bases, the MOSA-compliant launcher lets a small force project sea-denial or area-control over a wide zone.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>H.I. Sutton flagged some displayed equipment may have been staged for the ceremony rather than integrated.</t>
+          <t>Marketed as also compatible with the larger Hero-400 munition for deeper-strike missions.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>images/shahid-roudaki.jpg</t>
+          <t>images/hero-120-126cell.webp</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Tasnim News Agency, via Wikimedia Commons</t>
+          <t>Rheinmetall / The War Zone</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:IRIS_Shahid_Roudaki.jpg</t>
+          <t>https://www.twz.com/news-features/shipping-container-launcher-packing-126-kamikaze-drones-hits-the-market</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://www.hisutton.com/Iranian-IRGC-Forward-Base-Shahid-Roudaki.html</t>
+          <t>https://www.twz.com/news-features/shipping-container-launcher-packing-126-kamikaze-drones-hits-the-market</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Iranian IRGC Forward Base Shahid Roudaki - Covert Shores</t>
+          <t>Shipping Container Launcher Packing 126 Kamikaze Drones Hits The Market — The War Zone</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>https://news.usni.org/2020/11/19/video-iran-inducts-new-special-operations-ship</t>
+          <t>https://www.uasvision.com/2024/06/27/shipping-container-launcher-packing-126-kamikaze-drones/</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Iran Inducts New Special Operations Ship - USNI</t>
+          <t>Shipping Container Launcher Packing 126 Kamikaze Drones — UAS Vision</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>hezbollah-container-launcher</t>
+          <t>iris-t-slm-container</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hezbollah Container-Concealed Launcher Trucks</t>
+          <t>Diehl IRIS-T SLM Containerized Fire Unit</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hezbollah closed-container hydraulic launcher, Paveh-351 container truck</t>
+          <t>IRIS-T SLM, IRIS-T SL container launcher/radar/TOC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hezbollah (Iranian-supplied)</t>
+          <t>Diehl Defence</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Documented doctrine; Nov 2022 Israeli strike on a Paveh container truck</t>
+          <t>First fire unit delivered to German Armed Forces</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Covert / disguised</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Concealed cargo</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Hezbollah mounts Iranian-supplied rockets/cruise missiles on civilian trucks within closed containers that open hydraulically to erect and fire, dispersed in populated areas for survivability.</t>
+          <t>IRIS-T SLM fire units (launcher, TRML-4D radar and IBMS tactical operations centre) are each built on standardised 20-ft ISO container frames for road/rail/sea/air transport; unmanned launchers reach readiness in 10 minutes.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Described launch method/doctrine (Alma Research) rather than one photographed named system; secondary confirmation thinner.</t>
+          <t>Widely fielded to Ukraine and the Bundeswehr; container-frame design confirmed by multiple sources.</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>images/iris-t-slm-container.jpg</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Boevaya mashina / Wikimedia Commons</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>wikimedia</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:IRIS-T_SLM_launcher_at_ILA-2024.JPG</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://israel-alma.org/hezbollahs-heavy-rocket-array-medium-range-up-to-200-km-and-its-ballistic-missile-array-constitute-strategic-capabilities-of-the-organization/</t>
+          <t>https://defence-industry.eu/diehl-defence-delivers-first-unit-of-iris-t-slm-system-to-german-armed-forces/</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Hezbollah's heavy rocket array - Alma Research</t>
+          <t>Diehl delivers first IRIS-T SLM unit to German Armed Forces - Defence Industry Europe</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>https://israel-alma.org/iranian-paveh-cruise-missile-351-supplied-to-lebanese-hezbollah/</t>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/diehl-defence-delivers-first-iris-t-slm-air-defense-system-to-german-army</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Iranian Paveh Cruise Missile supplied to Hezbollah - Alma Research</t>
+          <t>Diehl delivers first IRIS-T SLM to German Army - Army Recognition</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>hwasal-2-container</t>
+          <t>boeing-clws</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>North Korea Hwasal-2 Container Cruise-Missile Launcher</t>
+          <t>Boeing Compact Laser Weapon System (containerized)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hwasal-2 angled container launcher, Amnok-class corvette cruise-missile box</t>
+          <t>CLWS, Boeing containerized laser weapon</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>North Korean state defence industry</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>North Korea (DPRK)</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>August 2023</t>
+          <t>June 2024</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Naval version revealed on Amnok-class corvette; ground debut Oct 2021</t>
+          <t>Demonstrated in containerized config at Canada's IDEaS C-UAS Sandbox</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Strike missile</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4197,7 +4207,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Nuclear-capable land-attack cruise missile (~1,500-2,000 km) launched from an angled, box-like container rather than a VLS; seen in a 5-tube road-mobile launcher and an 8-tube aft-deck fit on the Amnok-class corvette.</t>
+          <t>A fixed containerized configuration of Boeing's 5kW-class Compact Laser Weapon System, paired with radar cueing to detect, track and defeat FPV drones, mortar rounds and a five-UAS swarm at 200m-2.5km in Canadian trials.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4207,196 +4217,196 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Ambiguity over whether 'container' means a true ISO box or an inclined canister bank.</t>
+          <t>Tested alongside a Polaris RZR-mounted CLWS unit; hosted by DRDC at CFB Suffield.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>images/hwasal-2-container.jpg</t>
+          <t>images/boeing-clws.jpg</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>KCNA via Army Recognition</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/north-korea-announces-successful-test-of-strategic-cruise-missile-hwasal-2</t>
+          <t>https://www.boeing.com/features/2024/10/boeing-compact-lasers-down-group-3-drones-for-first-time</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Hwasal-2</t>
+          <t>https://www.boeing.com/features/2024/06/boeings-compact-lasers-shine-at-counter-drone-competition</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Hwasal-2 - Wikipedia</t>
+          <t>Boeing's compact lasers at counter-drone competition - Boeing</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2023/08/north-korea-new-cruise-missile-amnok-class-corvette/</t>
+          <t>https://www.unmannedairspace.info/counter-uas-systems-and-policies/boeings-compact-laser-weapon-system-features-in-canadas-ideas-c-uas-trials/</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>North Korea reveals cruise missile-armed corvette - Naval News</t>
+          <t>Boeing CLWS in Canada's IDEaS C-UAS trials - Unmanned Airspace</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dprk-harop-launcher</t>
+          <t>shahid-mahdavi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>North Korea Harop-Type Loitering Munition Container Launcher</t>
+          <t>IRIS Shahid Mahdavi Containerized Ballistic Missile Ship</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DPRK Harop-clone container launcher, six-cell suicide-drone box</t>
+          <t>L110-3; converted container ship Sarvin</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>North Korean state defence industry</t>
+          <t>Islamic Revolutionary Guard Corps Navy (IRGCN); hull built in South Korea</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>North Korea (DPRK)</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>October 2025</t>
+          <t>February 2024</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Displayed at Pyongyang parade (80th WPK anniversary)</t>
+          <t>First containerized ballistic missile launch from deck (ship commissioned March 2023)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Loitering munition</t>
+          <t>Naval arsenal</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A 6x6 armored truck carrying two rows of three container-style launch cells for Harop-style kamikaze drones, marking a shift from 2024's bare-airframe reveal to fieldable launch hardware.</t>
+          <t>Converted from the 36,000-ton South Korean-built Panamax container ship Sarvin, the IRIS Shahid Mahdavi was commissioned by the IRGC Navy in March 2023 with a 150-metre flat deck for helicopters, UAV launches (including Shahed-136s), and containerized missile strikes, defended by four Nawab short-range VLS air-defense missiles and a 3D phased-array radar. In February 2024 the IRGCN test-fired long-range solid-fueled ballistic missiles — variously identified as Fateh-110, Zolfaghar, or Dezful variants — directly from standard shipping containers on its deck, with reported ranges of 500-1,700 km. The conversion turns an innocuous cargo hull into a mobile strategic strike asset capable of reaching the Indian Ocean, the Gulf of Aden, or targets across the Middle East.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Single-source detailed reporting; technical detail relies on analyst inference.</t>
+          <t>Exact missile type used in the Feb 2024 test is disputed among sources (Fateh-110/Zolfaghar/Dezful variants all cited).</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>images/dprk-harop-launcher.jpg</t>
+          <t>images/shahid-mahdavi.jpg</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>KCNA via Army Recognition</t>
+          <t>Iranian govt / Wikimedia Commons</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/north-korea-rolls-out-harop-type-loitering-munition-launcher-in-pyongyang-parade</t>
+          <t>https://commons.wikimedia.org/wiki/File:Commissioning_ceremony_of_IRGC_naval_vessels_in_March_2023_(06).jpg</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/north-korea-rolls-out-harop-type-loitering-munition-launcher-in-pyongyang-parade</t>
+          <t>https://en.wikipedia.org/wiki/IRIS_Shahid_Mahdavi</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>North Korea rolls out Harop-type loitering munition launcher - Army Recognition</t>
+          <t>IRIS Shahid Mahdavi — Wikipedia</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>https://militarnyi.com/en/news/north-korea-presents-launcher-for-copies-of-israeli-harop-kamikaze-drones/</t>
+          <t>https://www.rusi.org/explore-our-research/publications/commentary/irans-modern-q-ship-threat-new-quarters</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>North Korea Presents Launcher for Harop Copies - Militarnyi</t>
+          <t>Iran's Modern Q-Ship: A Threat from New Quarters — RUSI</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>thor-hpm</t>
+          <t>dragonfire</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>THOR</t>
+          <t>DragonFire</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tactical High-power Operational Responder</t>
+          <t>DragonFire laser directed-energy weapon</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Air Force Research Laboratory (AFRL)</t>
+          <t>MBDA UK / Leonardo UK / QinetiQ / Dstl</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>January 2024</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Development and swarm-defeat testing at Kirtland AFB</t>
+          <t>First UK high-power live firing vs aerial targets (Hebrides Range)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4411,7 +4421,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>High-power microwave counter-swarm weapon stored in a standard 20-ft ISO container, C-130 transportable, set up in hours for airbase point defense against drone swarms.</t>
+          <t>50kW-class laser weapon whose land-trial unit is described as roughly the size of a TEU shipping container; £316m production contract (Nov 2025) to arm Royal Navy Type 45 destroyers by 2027.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4421,114 +4431,104 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Follow-on is Mjolnir (Leidos).</t>
+          <t>Shipboard-fitted version's exact housing less certain than the land-test container configuration.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>images/thor-hpm.jpg</t>
+          <t>images/dragonfire.jpg</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>AFRL Directed Energy Directorate</t>
+          <t>UK Ministry of Defence / Crown Copyright (OGL v3.0)</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>public-domain-gov</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://afresearchlab.com/counter-swarm-high-power-weapon/</t>
+          <t>https://commons.wikimedia.org/wiki/File:Dragonfire_laser_system_test_firing.webp</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>https://www.twz.com/thor-microwave-anti-drone-system-downs-swarms-in-test</t>
+          <t>https://www.naval-technology.com/news/dragonfire-uk-royal-navy-to-get-ships-with-laser-beams-by-2027/</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>THOR Microwave Anti-Drone System Downs Swarms - TWZ</t>
+          <t>DragonFire: Royal Navy laser by 2027 - Naval Technology</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>https://www.airandspaceforces.com/air-forces-thor-drone-swarm-demo/</t>
+          <t>https://breakingdefense.com/2024/01/in-first-uk-test-fires-13-per-strike-dragonfire-laser-weapon-against-aerial-targets/</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>THOR Hammers Drone Swarm - Air &amp; Space Forces Magazine</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>https://en.wikipedia.org/wiki/THOR_(weapon)</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>THOR (weapon) - Wikipedia</t>
+          <t>UK test fires DragonFire laser - Breaking Defense</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mjolnir-hpm</t>
+          <t>iai-acdc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mjolnir</t>
+          <t>IAI All-Capabilities Defence Container (ACDC)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>THOR follow-on high-power microwave</t>
+          <t>ACDC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Leidos / Air Force Research Laboratory</t>
+          <t>Israel Aerospace Industries (IAI)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Development contract award</t>
+          <t>Product marketing/announcement</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Modular system</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Next-generation high-power microwave counter-swarm weapon derived from THOR, packaged in a transportable ISO container.</t>
+          <t>IAI markets the All-Capabilities Defence Container (ACDC), a modular self-defense package housing four Mini Harpy and eight Rotem L loitering munitions alongside its own operations room and an integrated mast carrying radar, communications, and optronic sights. It is designed to bolt onto weakly armed vessels to give them an immediate self-defense and limited-strike capability without a major refit.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4538,84 +4538,94 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Container form-factor inherited from THOR.</t>
+          <t>Described in marketing/analyst literature; fielding status on any specific vessel is not established in the source.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>images/iai-acdc.jpg</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>IAI (DIAMOND) / Breaking Defense</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>news</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://breakingdefense.com/2026/05/iais-new-diamond-naval-offering-envisions-flexible-drones-missiles-for-small-vessels/</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://afresearchlab.com/technology/directed-energy/</t>
+          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>AFRL Directed Energy</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>https://www.leidos.com/insights/leidos-awarded-contract-develop-next-generation-high-power-microwave-weapon</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Leidos next-gen HPM weapon - Leidos</t>
+          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>epirus-leonidas</t>
+          <t>dprk-disguised-mlrs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Epirus Leonidas (IFPC-HPM)</t>
+          <t>North Korean Disguised MLRS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Leonidas, IFPC-HPM, Indirect Fire Protection Capability-High Power Microwave</t>
+          <t>Civilian-truck-disguised 122mm MLRS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Epirus Inc.</t>
+          <t>North Korean state defense industry</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>North Korea (DPRK)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>January 2023</t>
+          <t>September 2023</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>US Army selection ($66.1M); prototypes delivered 2023-2024</t>
+          <t>Unveiled at military parade</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Covert / disguised</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Concealed cargo</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Solid-state GaN high-power microwave system that disables drone swarms; the base/IFPC-HPM unit fits inside a standard 20-ft container. Live-fire demo Aug 2025 downed 61 drones.</t>
+          <t>North Korea unveiled a fleet of Multiple Launch Rocket Systems disguised as ordinary civilian box trucks and yellow hard-hat dump trucks at a September 2023 military parade, with sliding roofs that open to reveal 12-tube 122mm rocket launchers. In 2026, intelligence reports and open-source video reportedly confirmed these disguised MLRS trucks operating in Russia's Kursk region, demonstrating their utility in heavily surveilled combat zones where distinguishing civilian from military traffic is critical to survival.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4625,69 +4635,69 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Only the base/IFPC-HPM version is containerized; Mobile/Pod/Expeditionary variants are not.</t>
+          <t>Kursk deployment reports rely on open-source and intelligence claims rather than official confirmation.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>images/epirus-leonidas.jpg</t>
+          <t>images/dprk-disguised-mlrs.webp</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Epirus, Inc.</t>
+          <t>The War Zone / KCNA</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>https://www.epirusinc.com/press-releases/epirus-general-dynamics-land-systems-unveil-integrated-counter-electronics-system-stryker-leonidas</t>
+          <t>https://www.twz.com/north-korea-debuts-rocket-launchers-that-appear-as-civilian-trucks</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://breakingdefense.com/2025/02/high-power-microwave-force-field-knocks-drone-swarms-from-sky/</t>
+          <t>https://www.twz.com/land/north-korean-rocket-launcher-disguised-as-civilian-truck-may-just-have-appeared-in-kursk</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>HPM force field knocks drone swarms from sky - Breaking Defense</t>
+          <t>Artillery Rocket Launcher Disguised As Civilian Truck May Have Just Appeared In Russia — The War Zone</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>https://www.defensedaily.com/ifpc-hpm-prototype-deliveries-complete-epirus-eyes-engineering-tests-ahead-of-potential-deployment/army/</t>
+          <t>https://www.twz.com/north-korea-debuts-rocket-launchers-that-appear-as-civilian-trucks</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>IFPC-HPM Prototype Deliveries Complete - Defense Daily</t>
+          <t>North Korea Debuts Rocket Launchers That Appear As Civilian Trucks — The War Zone</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>liteye-c-auds</t>
+          <t>typhon-mrc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Liteye C-AUDS</t>
+          <t>Typhon / Mid-Range Capability (MRC)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C-AUDS, Containerized Anti-UAS Defense System</t>
+          <t>Strategic Mid-Range Fires; land-based Mk 41 container launcher</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Liteye Systems (integrating UK AUDS tech)</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4697,22 +4707,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2018-09-05</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>September 2018</t>
+          <t>27 June 2023</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>USAF follow-on contract; production units delivered Dec 2018</t>
+          <t>First Tomahawk launch and first-unit operational declaration 27 Jun 2023</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4722,7 +4732,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Integrates AUDS radar (Blighter), EO/IR tracker (Chess Dynamics) and RF-jamming effector (optional kinetic add-on) into a self-contained 20-ft ISO container for base and critical-infrastructure defense.</t>
+          <t>Typhon is the U.S. Army's land-based sibling of the Mk 70, mounting four strike-length Mk 41 cells in a 40-ft ISO-container footprint on a trailer-borne transporter-erector-launcher that raises to fire SM-6 and Tomahawk. The first battery was declared operational with the 1st Multi-Domain Task Force on 27 June 2023, and the system deployed to the Philippines in April 2024, drawing sharp reactions from China. It gives ground forces a mobile intermediate-range strike capability packaged as a shipping container.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4732,124 +4742,124 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Base AUDS is vehicle/trailer-mounted; only the C-AUDS repackaging is a true container.</t>
+          <t>'Containerised' here denotes the container form-factor that erects to fire, not cargo-disguise concealment.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>images/liteye-c-auds.jpg</t>
+          <t>images/typhon-mrc.jpg</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Liteye Systems, Inc.</t>
+          <t>U.S. Army / Wikimedia Commons</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>public-domain-gov</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://www.globenewswire.com/news-release/2020/07/16/2063226/0/en/Liteye-C-AUDS-Chosen-to-Defend-Critical-Infrastructure-by-the-US-Government.html</t>
+          <t>https://commons.wikimedia.org/wiki/File:Typhon_Mid-Range_Capability_(MRC)_missile_system_firing_SM-6.jpg</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>https://equipment.adsinc.com/</t>
+          <t>https://en.wikipedia.org/wiki/Typhon_missile_system</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Liteye C-AUDS product page - ADS</t>
+          <t>Typhon missile system — Wikipedia</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>https://www.unmannedairspace.info/</t>
+          <t>https://www.navalnews.com/naval-news/2023/09/u-s-navy-and-army-mk-70-pds-stretch-their-wings/</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Blighter to supply C-UAS radar to Liteye - Unmanned Airspace</t>
+          <t>U.S. Navy And Army Mk 70 PDS Stretch Their Wings — Naval News</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>dzyne-blitzbox</t>
+          <t>edge-skyshield</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DZYNE BlitzBox</t>
+          <t>EDGE SKYSHIELD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BlitzBox, Blitz drone container launcher</t>
+          <t>SKYSHIELD, SKYSHIELD-TM C-UAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DZYNE Technologies</t>
+          <t>SIGN4L (EDGE Group)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2023-02-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>February 2023</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Unveiled at SOF Week</t>
+          <t>Unveiled at IDEX 2023</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Loitering munition</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Concealed cargo</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>An ordinary-looking shipping container hiding a launch system for DZYNE's Blitz Group-1 expendable swarming drones; a 10-ft container holds 16 drones on 4 rail launchers, a 40-ft container up to 100.</t>
+          <t>A multi-layered C-UAS solution (3D radar, EO/IR, RF direction-finders, jammers) networked into a unified C2 system, housed in a shock-proof, sealed container/cabinet for fixed or rapidly-deployable use; UAE MoD contract announced ~2024.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>TWZ direct interview with DZYNE program manager.</t>
+          <t>Sources describe a compact shock-proof container/cabinet rather than confirmed full ISO dimensions.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>images/dzyne-blitzbox.jpg</t>
+          <t>images/edge-skyshield.jpg</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>DZYNE Technologies (via The War Zone)</t>
+          <t>EDGE Group (via The Defense Post)</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4859,69 +4869,69 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://www.twz.com/news-features/blitzbox-packs-100-weaponized-drones-into-an-unassuming-container</t>
+          <t>https://thedefensepost.com/2023/02/22/edge-skyshield-counter-drone/</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>https://www.twz.com/</t>
+          <t>https://www.armyrecognition.com/</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>BlitzBox Packs 100 Weaponized Drones Into A Container - TWZ</t>
+          <t>IDEX 2023: EDGE launches SKYSHIELD C-UAS - Army Recognition</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>https://www.slashgear.com/</t>
+          <t>https://www.sign4l.ae/</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>A Container Full Of 100 Deadly Drones - SlashGear</t>
+          <t>SKYSHIELD Counter-UAS - SIGN4L</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>dragonfire</t>
+          <t>epirus-leonidas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DragonFire</t>
+          <t>Epirus Leonidas (IFPC-HPM)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DragonFire laser directed-energy weapon</t>
+          <t>Leonidas, IFPC-HPM, Indirect Fire Protection Capability-High Power Microwave</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MBDA UK / Leonardo UK / QinetiQ / Dstl</t>
+          <t>Epirus Inc.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>January 2024</t>
+          <t>January 2023</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>First UK high-power live firing vs aerial targets (Hebrides Range)</t>
+          <t>US Army selection ($66.1M); prototypes delivered 2023-2024</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4936,7 +4946,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>50kW-class laser weapon whose land-trial unit is described as roughly the size of a TEU shipping container; £316m production contract (Nov 2025) to arm Royal Navy Type 45 destroyers by 2027.</t>
+          <t>Solid-state GaN high-power microwave system that disables drone swarms; the base/IFPC-HPM unit fits inside a standard 20-ft container. Live-fire demo Aug 2025 downed 61 drones.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4946,94 +4956,94 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Shipboard-fitted version's exact housing less certain than the land-test container configuration.</t>
+          <t>Only the base/IFPC-HPM version is containerized; Mobile/Pod/Expeditionary variants are not.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>images/dragonfire.jpg</t>
+          <t>images/epirus-leonidas.jpg</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>UK Ministry of Defence / Crown Copyright (OGL v3.0)</t>
+          <t>Epirus, Inc.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Dragonfire_laser_system_test_firing.webp</t>
+          <t>https://www.epirusinc.com/press-releases/epirus-general-dynamics-land-systems-unveil-integrated-counter-electronics-system-stryker-leonidas</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>https://www.naval-technology.com/news/dragonfire-uk-royal-navy-to-get-ships-with-laser-beams-by-2027/</t>
+          <t>https://breakingdefense.com/2025/02/high-power-microwave-force-field-knocks-drone-swarms-from-sky/</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>DragonFire: Royal Navy laser by 2027 - Naval Technology</t>
+          <t>HPM force field knocks drone swarms from sky - Breaking Defense</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>https://breakingdefense.com/2024/01/in-first-uk-test-fires-13-per-strike-dragonfire-laser-weapon-against-aerial-targets/</t>
+          <t>https://www.defensedaily.com/ifpc-hpm-prototype-deliveries-complete-epirus-eyes-engineering-tests-ahead-of-potential-deployment/army/</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>UK test fires DragonFire laser - Breaking Defense</t>
+          <t>IFPC-HPM Prototype Deliveries Complete - Defense Daily</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>rheinmetall-mbda-lwd</t>
+          <t>kongsberg-nsm-cds</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rheinmetall/MBDA Laser Weapon Demonstrator</t>
+          <t>Kongsberg Naval Strike Missile (NSM) Coastal Defence System</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LWD, 20kW naval laser demonstrator</t>
+          <t>NSM CDS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Rheinmetall + MBDA Deutschland</t>
+          <t>Kongsberg Defence &amp; Aerospace</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>October 2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Installed on frigate Sachsen; sea trials 2022-2023</t>
+          <t>Multi-nation adoption reports (Poland, Romania, Australia, USMC NMESIS)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5043,7 +5053,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>20kW-scalable laser demonstrator with turret and support equipment housed in a standard 20-ft container, craned onto the frigate Sachsen for a year of at-sea firing trials against drones and small boats.</t>
+          <t>Kongsberg adapted its stealthy, sea-skimming Naval Strike Missile (NSM), which has a range exceeding 200 km, a Microturbo TRI-40 turbojet, and an imaging-infrared seeker with autonomous target recognition, into a modular, truck- or flatbed-transportable Coastal Defence System. A Fire Control Center built on the NASAMS architecture can network up to four FCCs to coordinate engagement of up to 48 simultaneous targets across land and sea. The containerized CDS has been adopted by Poland, Romania, Australia, and the U.S. Marine Corps (via the NMESIS program), and an unidentified NSM launcher has reportedly been observed operating in Ukraine.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -5053,94 +5063,94 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>In-service target ~2029.</t>
+          <t>Ukraine sighting described in the source as an 'unidentified' NSM launcher, not officially confirmed.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>images/rheinmetall-mbda-lwd.jpg</t>
+          <t>images/kongsberg-nsm-cds.jpg</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Rheinmetall (via Naval News)</t>
+          <t>Wikimedia Commons</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2025/10/rheinmetall-and-mbda-german-laser-weapon-system-close-to-market-readiness/</t>
+          <t>https://commons.wikimedia.org/wiki/File:Naval_Strike_Missile_(NSM).jpg</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2025/10/rheinmetall-and-mbda-german-laser-weapon-system-close-to-market-readiness/</t>
+          <t>https://en.wikipedia.org/wiki/Naval_Strike_Missile</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>German laser weapon close to market readiness - Naval News</t>
+          <t>Naval Strike Missile — Wikipedia</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>https://www.edrmagazine.eu/mbda-deutschland-provided-new-details-on-the-laser-weapon-demonstrator</t>
+          <t>https://www.kongsberg.com/what-we-do/defence-and-security/integrated-air-and-missile-defence/coastal-defence-system/</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>MBDA Laser Weapon Demonstrator details - EDR Magazine</t>
+          <t>Naval Strike Missile (NSM) Coastal Defence System — Kongsberg</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iron-beam</t>
+          <t>patria-nemo-container</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Iron Beam</t>
+          <t>Patria NEMO Container</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Magen Or, Light Shield, Iron Beam 450</t>
+          <t>Patria NEMO (NEw MOrtar) containerized turret</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Rafael Advanced Defense Systems (Elbit laser source)</t>
+          <t>Patria</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>December 2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>First operational unit delivered to IDF</t>
+          <t>Product literature/introduction; live-fire demonstrated June 2026</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Artillery / coastal</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5150,79 +5160,79 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>100kW-class laser (ten fused 10kW fiber lasers) with a dome turret; beam-generation and cooling equipment described as housed in two 40-ft container-like modules, generally stationary but relocatable.</t>
+          <t>Patria integrated its 120 mm NEMO remote-controlled mortar turret into a standard 20-ft ISO container as a fully independent firing unit with its own power generation, NBC filtration, air conditioning, and ballistic protection. A semi-automatic autoloader sustains 6 rounds per minute (three rounds in 12 seconds in a burst), and the fire-control network supports Multiple Rounds Simultaneous Impact (MRSI) missions of up to six mortar bombs landing on one target at once. The container can be moved by standard military trucks or mounted on fast naval patrol vessels for coastal defense.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>The 'two 40-ft container modules' phrasing recurs in secondary sources but primary ISO-container wording not verified.</t>
+          <t>Document cites a June 2026 test alongside earlier 2023 product literature; treated here as an established, available product.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>images/iron-beam.jpg</t>
+          <t>images/patria-nemo-container.jpg</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Rafael Advanced Defense Systems (via Wikimedia Commons)</t>
+          <t>S. Kiyotani / European Security &amp; Defence</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Iron_beam_01.jpg</t>
+          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Iron_Beam</t>
+          <t>https://www.patriagroup.com/products-and-services/defence-and-weapon-systems/armament/patria-nemo-container</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Iron Beam - Wikipedia</t>
+          <t>Patria NEMO Container — Patria</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/rafael-delivers-israels-first-operational-iron-beam-laser-shield-to-revolutionize-air-defense-era</t>
+          <t>https://www.patriagroup.com/download/patria-nemo-container-a4210x297mm-08-2023-final-webpdf</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Rafael Delivers First Operational Iron Beam - Army Recognition</t>
+          <t>Patria NEMO Container — 120 mm mortar system (product sheet)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>silent-hunter</t>
+          <t>csdcs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Silent Hunter</t>
+          <t>CSDCS Container-Type Sea Defense Combat System</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shen Nu, Silent Hunter laser air-defence</t>
+          <t>CSDCS, containerized coastal defense system, China's Club-K</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Poly Technologies</t>
+          <t>CASIC (China Aerospace Science and Industry Corp)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5232,22 +5242,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2017-02-01</t>
+          <t>2022-11-08</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>February 2017</t>
+          <t>November 2022</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Unveiled at IDEX 2017; Saudi operational use vs Houthi drones</t>
+          <t>Unveiled at Airshow China (Zhuhai)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5257,27 +5267,27 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>30-100kW-class anti-drone fiber laser; the mobile version is described as installed in a container towed by a 6x6 truck. Exported to the UAE/Saudi Arabia.</t>
+          <t>A self-contained combat system built into a 20/40-ft container (~13m x 2.3m x 2.5m) with operator station, power and a quadruple launcher firing YJ-12E supersonic or YJ-18E subsonic anti-ship cruise missiles from ships, trucks or trains; China's openly-marketed Club-K analogue with broader missile compatibility.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Some sources describe it as separate truck-sized power and equipment units rather than a clear ISO box.</t>
+          <t>Distinct from the Zhong Da 79 arsenal-ship entry already in the list; this is the standalone containerized launcher product.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>images/silent-hunter.jpg</t>
+          <t>images/csdcs.jpg</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Army Recognition</t>
+          <t>Fan Wei / Global Times</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5287,104 +5297,114 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/dsa-2024-chinese-company-poly-technologies-showcases-silent-hunter-laser-defense-system</t>
+          <t>https://www.globaltimes.cn/page/202211/1279349.shtml</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Silent_Hunter_(laser_weapon)</t>
+          <t>https://www.globaltimes.cn/page/202211/1279349.shtml</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Silent Hunter (laser weapon) - Wikipedia</t>
+          <t>China debuts container-type missile launch system - Global Times</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>https://armyrecognition.com/news/army-news/army-news-2024/dsa-2024-chinese-company-poly-technologies-showcases-silent-hunter-laser-defense-system</t>
+          <t>https://en.defence-ua.com/news/in_2022_china_unveiled_its_copy_of_russias_club_k_missile_system_now_it_threatens_us_navy-14827.html</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Poly Technologies showcases Silent Hunter - Army Recognition</t>
+          <t>China unveiled its copy of Russia's Club-K - Defense Express</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://www.vermilionchina.com/p/36-chinas-container-launched-cruise</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>China's Container-launched Cruise Missiles - Vermilion China</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cheongwang-skylight</t>
+          <t>bit-swarm-truck</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cheongwang (Skylight) Laser</t>
+          <t>Beijing Institute of Technology (BIT) Containerized Swarm Launcher Truck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cheongwang, Skylight, Block-I laser air-defense</t>
+          <t>Chinese disguised loitering-munition truck</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hanwha Aerospace with ADD</t>
+          <t>Beijing Institute of Technology (BIT), part of a consortium of 70+ Chinese research entities</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>December 2024</t>
+          <t>Late 2022</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Initial operational fielding (Seoul area and frontline)</t>
+          <t>Revealed by Chinese state media (CCTV)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Covert / disguised</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Concealed cargo</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>World's first laser weapon to reach operational military deployment; a 20kW fiber laser fully housed in a container-sized unit (~9m x 3m x 3m) with integrated radar mast, for point air-defense against small drones over Seoul.</t>
+          <t>Chinese state broadcaster CCTV revealed in late 2022 a vehicle-mounted swarm launcher disguised as an ordinary light tactical truck, able to rapidly deploy up to 18 loitering munitions with pop-out wings and V-shaped tails resembling the U.S. Switchblade or Israeli Mini Harpy. It is one module within a broader 'containerized weapon module suite' developed by over 70 Chinese research entities, spanning at least 10 modules covering drones, air defense, anti-ship strike, and electronic warfare. The truck is designed for network-enabled saturation strikes against personnel, light armor, and radar sites.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Army Recognition explicitly calls it container-sized.</t>
+          <t>Details rely on a single state-media reveal; the broader 10-module 'containerized weapon suite' program is only partially disclosed.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>images/cheongwang-skylight.jpg</t>
+          <t>images/bit-swarm-truck.jpg</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Army Recognition</t>
+          <t>The War Zone (Zhuhai Air Show)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5394,84 +5414,84 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/south-korea-commissions-cheongwang-its-most-modern-laser-system-to-counter-aerial-threats</t>
+          <t>https://www.twz.com/drone-swarm-launcher-truck-displayed-at-chinas-big-arms-expo</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>https://armyrecognition.com/news/army-news/army-news-2024/south-korea-commissions-cheongwang-its-most-modern-laser-system-to-counter-aerial-threats</t>
+          <t>https://www.twz.com/drone-swarm-launcher-truck-displayed-at-chinas-big-arms-expo</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>South Korea Commissions Cheongwang Laser - Army Recognition</t>
+          <t>Drone Swarm Launcher Truck Displayed At China's Big Arms Expo — The War Zone</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/south-korea-deploys-skylight-laser-weapon-to-protect-seoul-capital-and-frontline-areas-from-north-korean-drones</t>
+          <t>https://asiatimes.com/2026/07/chinas-truck-drone-launcher-hides-airpower-in-civilian-traffic/</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>South Korea deploys Skylight laser - Army Recognition</t>
+          <t>China's truck drone launcher hides airpower in civilian traffic — Asia Times</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kawasaki-hel</t>
+          <t>rafael-c-dome</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kawasaki 100kW Laser C-UAS</t>
+          <t>Rafael C-DOME Mission Module</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KHI Electric-Drive High-Power Laser System</t>
+          <t>Containerized Iron Dome for ships</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kawasaki Heavy Industries (KHI)</t>
+          <t>Rafael Advanced Defense Systems</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>December 2025</t>
+          <t>November 2022</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Installed aboard JMSDF test ship JS Asuka</t>
+          <t>Final operationalization aboard Israeli Navy Sa'ar 6-class corvettes</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>100kW-class laser (ten fused 10kW fiber lasers) for counter-UAS, packaged into two 40-ft ISO container modules with a domed turret, installed on JS Asuka's deck for maritime trials.</t>
+          <t>Rafael modularized its combat-proven Iron Dome into the C-DOME Mission Module, a multi-round Vertical Launch Unit using the Tamir interceptor packaged in a standard footprint that requires no deck penetration, for offshore patrol vessels and corvettes lacking organic air defense. It networks with a ship's existing search radar through an open-architecture Combat Management System to intercept saturation attacks from rockets, cruise missiles, and UAVs, and is deployed on the Israeli Navy's Sa'ar 6-class corvettes.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5481,94 +5501,84 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Prototype delivered to Japan MoD Feb 2023.</t>
+          <t>Actively fielded, unlike several other entries in this catalog that remain prototypes.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>images/kawasaki-hel.jpg</t>
+          <t>images/rafael-c-dome.jpg</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Koji Miyake / Shephard Media</t>
+          <t>Rafael (via EDR Magazine)</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://www.shephardmedia.com/news/landwarfareintl/kawasaki-develops-c-uas-laser-system-for-japanese-military/</t>
+          <t>https://www.edrmagazine.eu/wp-content/uploads/2023/05/CRafael-C-Dome-Mission-Modue_03.jpg</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2025/12/high-energy-laser-system-spotted-aboard-jmsdf-test-ship/</t>
+          <t>https://www.rafael.co.il/system/c-dome-2/</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>High-Energy Laser Aboard JMSDF Test Ship - Naval News</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>https://www.janes.com/osint-insights/defence-news/industry/dsei-japan-2023-kawasaki-heavy-industries-unveils-high-energy-laser-c-uas</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>KHI unveils high-energy laser C-UAS - Janes</t>
+          <t>C-DOME: Maritime Application of the Combat-Proven Iron Dome — Rafael</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>edge-skyshield</t>
+          <t>rheinmetall-mbda-lwd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EDGE SKYSHIELD</t>
+          <t>Rheinmetall/MBDA Laser Weapon Demonstrator</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SKYSHIELD, SKYSHIELD-TM C-UAS</t>
+          <t>LWD, 20kW naval laser demonstrator</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SIGN4L (EDGE Group)</t>
+          <t>Rheinmetall + MBDA Deutschland</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2023-02-20</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>February 2023</t>
+          <t>October 2022</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Unveiled at IDEX 2023</t>
+          <t>Installed on frigate Sachsen; sea trials 2022-2023</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5578,27 +5588,27 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A multi-layered C-UAS solution (3D radar, EO/IR, RF direction-finders, jammers) networked into a unified C2 system, housed in a shock-proof, sealed container/cabinet for fixed or rapidly-deployable use; UAE MoD contract announced ~2024.</t>
+          <t>20kW-scalable laser demonstrator with turret and support equipment housed in a standard 20-ft container, craned onto the frigate Sachsen for a year of at-sea firing trials against drones and small boats.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Sources describe a compact shock-proof container/cabinet rather than confirmed full ISO dimensions.</t>
+          <t>In-service target ~2029.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>images/edge-skyshield.jpg</t>
+          <t>images/rheinmetall-mbda-lwd.jpg</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>EDGE Group (via The Defense Post)</t>
+          <t>Rheinmetall (via Naval News)</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5608,69 +5618,69 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://thedefensepost.com/2023/02/22/edge-skyshield-counter-drone/</t>
+          <t>https://www.navalnews.com/naval-news/2025/10/rheinmetall-and-mbda-german-laser-weapon-system-close-to-market-readiness/</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/</t>
+          <t>https://www.navalnews.com/naval-news/2025/10/rheinmetall-and-mbda-german-laser-weapon-system-close-to-market-readiness/</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>IDEX 2023: EDGE launches SKYSHIELD C-UAS - Army Recognition</t>
+          <t>German laser weapon close to market readiness - Naval News</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>https://www.sign4l.ae/</t>
+          <t>https://www.edrmagazine.eu/mbda-deutschland-provided-new-details-on-the-laser-weapon-demonstrator</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SKYSHIELD Counter-UAS - SIGN4L</t>
+          <t>MBDA Laser Weapon Demonstrator details - EDR Magazine</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>knds-drone-container</t>
+          <t>elbit-skystriker-container</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KNDS Containerized Drone Launcher</t>
+          <t>Elbit SkyStriker Containerized Launcher</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KNDS drone launch container, Helsing HX-2 / Tytan TI-1 METIS container</t>
+          <t>SkyStriker container launch configuration</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KNDS (France/Germany) with Helsing and Tytan</t>
+          <t>Elbit Systems</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>France / Germany</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Demonstrator unveiled at Eurosatory 2026</t>
+          <t>Container launch configuration publicized (approximate)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5685,7 +5695,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A self-contained 20-ft ISO container with independent power, environmental control and networking, housing dozens to 100+ effectors combining Helsing HX-2 strike drones and Tytan TI-1 METIS hard-kill interceptor drones; pitched as a response to Ukraine's Operation Spiderweb.</t>
+          <t>Electrically powered canister-launched loitering munition (up to 100 km, 10kg warhead); Elbit markets a container launch configuration packing 6 SkyStriker rounds per container for land or naval deployment.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5695,94 +5705,94 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Mock-up demonstrator/concept, not yet fielded; dual strike + interceptor role.</t>
+          <t>Container figure from Elbit product literature rather than a dedicated show unveiling; reveal date approximate.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>images/knds-drone-container.jpg</t>
+          <t>images/elbit-skystriker-container.jpg</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>KNDS Group</t>
+          <t>Boevaya mashina / Wikimedia Commons</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://knds.com/en/press-releases/bolstering-mission-solution-portfolio-knds-showcases-first-drone-launch-container-prototype-at-eurosatory-2026-1</t>
+          <t>https://commons.wikimedia.org/wiki/File:Elbit_Systems_SkyStriker_SIAF-2022.jpg</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/</t>
+          <t>https://www.elbitsystems.com/sites/default/files/2025-02/skystriker.pdf</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>KNDS unveils containerized drone launcher concept - Army Recognition</t>
+          <t>Elbit SkyStriker datasheet</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>https://www.euro-sd.com/</t>
+          <t>https://www.battlepolicy.com/skystriker/</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>KNDS showcases C-UAV capabilities at Eurosatory 2026 - ESD</t>
+          <t>SkyStriker Israel's electric loitering munition - Battle Policy</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>destinus-hornet-b1</t>
+          <t>edge-hunter-skyknight</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Destinus Hornet Block 1 Containerized Interceptor</t>
+          <t>EDGE HUNTER 10 &amp; SkyKnight Containerized Systems</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hornet B1, Destinus containerized interceptor drone launcher</t>
+          <t>HALCON HUNTER 10; SkyKnight Multi-Launcher Unit</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Destinus</t>
+          <t>EDGE Group (HALCON subsidiary)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Switzerland (tested by Spain)</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Test-fired aboard frigate Santa Maria and in land container config</t>
+          <t>Unveiling (UMEX 2022) and subsequent SkyKnight containerization</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Modular system</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5792,104 +5802,94 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Canister-launched hard-kill interceptor drone engaging subsonic UAVs/swarms, fired from a modular containerized launch unit demonstrated on both a ship's deck and a land container configuration.</t>
+          <t>UAE's EDGE Group, through its HALCON subsidiary, developed the HUNTER 10, a container-launched fixed-wing loitering munition with a 50 kg maximum take-off weight, 10 kg payload, 33 m/s cruising speed, and 100 km range; a smaller Hunter SP variant has been integrated into dual 7-tube containerized pods on Milrem Robotics' THeMIS unmanned ground vehicle. Separately, EDGE has containerized its SkyKnight missile as a 20-ft Multi-Launcher Unit holding up to 60 missiles for Counter Rocket, Artillery, and Mortar (C-RAM) defense, firing at five rounds per second. The two products represent EDGE's parallel push into container-packaged offensive loitering munitions and defensive C-RAM.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Clearest verified containerized interceptor-drone launcher found.</t>
+          <t>Two distinct EDGE Group products bundled into one catalog entry: HUNTER 10 (offensive loitering munition) and SkyKnight (defensive C-RAM missile container).</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>images/destinus-hornet-b1.jpg</t>
+          <t>images/edge-hunter-skyknight.jpg</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Artvill / Wikimedia Commons</t>
+          <t>EDGE Group / Army Recognition</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Destinus_Hornet_au_Salon_du_Bourget_2025_1.jpg</t>
+          <t>https://edgegroup.ae/solutions/hunter-10</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/</t>
+          <t>https://edgegroup.ae/solutions/hunter-10</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Spanish Navy Tests Hornet Block 1 from Santa Maria Frigate - Naval News</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>https://thedefensepost.com/</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Spanish Army Tests Destinus Hornet B1 in Container Launch Config - The Defense Post</t>
+          <t>HUNTER 10 Long-Range Multi Role Loitering Munition — EDGE Group</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>roketsan-kara-atmaca</t>
+          <t>shahed-136-container-launcher</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Roketsan Kara Atmaca Container Launcher</t>
+          <t>Iran Shahed-136 Tilting Container Drone Launcher</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kara Atmaca, ATMACA-UM Container Launch System</t>
+          <t>Shahed-136 catapult-container system, Great Prophet 17 launcher</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Roketsan</t>
+          <t>HESA / IRGC Aerospace Force</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2021-12-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>July 2025</t>
+          <t>December 2021</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Unveiled at IDEF 2025 (Istanbul)</t>
+          <t>Unveiled during Great Prophet 17 exercise</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Covert strike</t>
+          <t>Loitering munition</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A launcher disguised as an ordinary 20/40-ft commercial container, firing up to six Kara Atmaca land-attack/anti-ship cruise missiles (~250-280 km, 220kg warhead), movable by truck, rail or civilian cargo vessel.</t>
+          <t>A tilting truck-mounted container-like box holding up to five Shahed-136 loitering munitions, each rocket-boosted into flight; container form factor allows palletizing onto rail cars, ships or other vehicles.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5909,124 +5909,124 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Roketsan states it is fully operational; multiple independent outlets confirm the container form factor.</t>
+          <t>Well corroborated; distinct from later no-container pickup-truck launch method.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>images/roketsan-kara-atmaca.jpg</t>
+          <t>images/shahed-136-container-launcher.jpg</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Army Recognition Group</t>
+          <t>Amin Ahouei / Tasnim News Agency, via Wikimedia Commons</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/tuerkiye-debuts-kara-atmaca-container-launcher-at-idef-2025-for-covert-and-mobile-land-based-strike-roles</t>
+          <t>https://commons.wikimedia.org/wiki/File:Sacred_Defence_Week_parade,_2023,_in_Tehran_(113).jpg</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/tuerkiye-debuts-kara-atmaca-container-launcher-at-idef-2025-for-covert-and-mobile-land-based-strike-roles</t>
+          <t>https://iranprimer.usip.org/blog/2021/dec/28/irgc-tests-ballistic-missiles-drones-war-game</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Turkiye Debuts Kara Atmaca Container Launcher at IDEF 2025 - Army Recognition</t>
+          <t>IRGC Tests Ballistic Missiles, Drones in War Game - USIP</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/military/shipping-containers-into-surprise-missile-launchers</t>
+          <t>https://militarnyi.com/en/news/shahed-loitering-munition-received-the-capability-to-be-launched-from-a-vehicle/</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Turkey turns cargo container into missile-in-a-box - Interesting Engineering</t>
+          <t>Shahed launched from a vehicle - Militarnyi</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>roketsan-eren</t>
+          <t>ivan-papanin-kalibr-k</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Roketsan EREN Containerized Loitering Munition Launcher</t>
+          <t>Project 23550 Ivan Papanin Kalibr-K Container Module</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>EREN Container Launch System, Roketsan EREN ground launcher</t>
+          <t>Ivan Papanin containerized Kalibr, Project 23550 combat icebreaker</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Roketsan</t>
+          <t>Admiralty Shipyards / Morinformsystem-Agat lineage</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>July 2025</t>
+          <t>October 2021</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Unveiled at IDEF 2025 (Istanbul)</t>
+          <t>Naval News detailed the containerized-bay design; lead ship commissioned Sept 2025</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Loitering munition</t>
+          <t>Naval arsenal</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A truck-mounted launcher disguised as a civilian freight container, concealing up to 12 EREN jet-powered dual-role (anti-air/anti-ground) loitering munitions (35kg, &gt;100 km); serial production planned for 2026.</t>
+          <t>Purpose-built Arctic combat icebreaker/patrol ship with an open stern flex-bay designed to accept containerized Kalibr-K cruise-missile or Kh-35 anti-ship modules (up to 8 missiles); Russia's first near-operational Club-K-style warship fit.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Multiple independent outlets confirm the container disguise and IDEF 2025 debut.</t>
+          <t>Missile module reportedly not yet installed at commissioning (only the 76mm gun fitted); deck pre-wired for retrofit.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>images/roketsan-eren.jpg</t>
+          <t>images/ivan-papanin-kalibr-k.jpg</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Army Recognition Group</t>
+          <t>Naval News</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6036,74 +6036,76 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://armyrecognition.com/news/army-news/2025/roketsan-debuts-containerized-eren-loitering-munition-launcher-at-idef-2025-for-covert-deep-strikes</t>
+          <t>https://www.navalnews.com/wp-content/uploads/2020/08/Project_23550_Club-K_Containers_2-1024x679.jpg</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/archives/archives-land-defense/defense-news-army-2025/roketsan-debuts-containerized-eren-loitering-munition-launcher-at-idef-2025-for-covert-deep-strikes</t>
+          <t>https://www.navalnews.com/naval-news/2021/10/russia-arctic-patrol-ship-cruise-missiles/</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Roketsan Debuts Containerized EREN Launcher at IDEF 2025 - Army Recognition</t>
+          <t>Russia's Arctic Patrol Ships to Feature Cruise Missiles - Naval News</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>https://united24media.com/latest-news/inspired-by-ukraines-operation-spiderweb-turkey-unveils-hidden-drone-launcher-for-deep-strikes-10361</t>
+          <t>https://www.armyrecognition.com/news/navy-news/2024/russian-navys-new-ivan-papanin-project-23550-combat-icebreaker-begins-sea-trials-with-kalibr-missiles</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Turkey Unveils Hidden Drone Launcher for Deep Strikes - United24</t>
-        </is>
-      </c>
+          <t>Ivan Papanin begins sea trials with Kalibr - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>elbit-skystriker-container</t>
+          <t>navypods-strike</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Elbit SkyStriker Containerized Launcher</t>
+          <t>Royal Navy NavyPODS (Strike POD)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SkyStriker container launch configuration</t>
+          <t>PODS, Persistent Operational Deployment System, Strike POD</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Elbit Systems</t>
+          <t>G3 Systems / QinetiQ for Royal Navy</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>September 2021</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Container launch configuration publicized (approximate)</t>
+          <t>Concept unveiled at DSEI 2021</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Loitering munition</t>
+          <t>Modular system</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6113,7 +6115,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Electrically powered canister-launched loitering munition (up to 100 km, 10kg warhead); Elbit markets a container launch configuration packing 6 SkyStriker rounds per container for land or naval deployment.</t>
+          <t>A 20-ft ISO container-footprint modular payload system for RN vessels; the Strike POD variant hosts launchers for armed UAVs or loitering munitions plus a mission-planning area, part of an 18+ POD family.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6123,308 +6125,308 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Container figure from Elbit product literature rather than a dedicated show unveiling; reveal date approximate.</t>
+          <t>Armed Strike POD remains a low-TRL demonstrator; G3 Systems selected as preferred supplier Nov 2025.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>images/elbit-skystriker-container.jpg</t>
+          <t>images/navypods-strike.jpg</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Boevaya mashina / Wikimedia Commons</t>
+          <t>FDS/Simon Bradley, via Naval News</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Elbit_Systems_SkyStriker_SIAF-2022.jpg</t>
+          <t>https://www.navalnews.com/naval-news/2026/05/royal-navy-achieves-milestone-with-first-sea-trials-of-navypods/</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>https://www.elbitsystems.com/sites/default/files/2025-02/skystriker.pdf</t>
+          <t>https://www.navylookout.com/thinking-inside-the-box-the-royal-navys-containerised-capability-concept/</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Elbit SkyStriker datasheet</t>
+          <t>Royal Navy's containerised capability concept - Navy Lookout</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>https://www.battlepolicy.com/skystriker/</t>
+          <t>https://www.navalnews.com/naval-news/2025/11/g3-systems-selected-as-the-preferred-supplier-to-upgrade-navypods-capability/</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SkyStriker Israel's electric loitering munition - Battle Policy</t>
+          <t>G3 Systems preferred supplier for NavyPODS - Naval News</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>elbit-trigon</t>
+          <t>mk70-pds</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Elbit TRIGON Sea-to-Shore Weapon System</t>
+          <t>Mk 70 Payload Delivery System</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TRIGON naval rocket and missile launcher</t>
+          <t>Mk 70 Mod 1 PDS; containerised Mk 41 VLS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Elbit Systems</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>September 2021</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Earliest trade-press coverage (approximate)</t>
+          <t>Unveiled Sept 2021 via SM-6 launch from USV Ranger</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Naval arsenal</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Modular deck launcher</t>
+          <t>Container form-factor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A fixed-elevation deck-mounted launcher carrying two pods of four EXTRA guided rockets (150 km) each, installable permanently or as an add-on mission module above or below deck on small-to-medium naval craft.</t>
+          <t>The Mk 70 PDS packs four strike-length Mk 41 vertical launch cells into a 40-ft (12 m) ISO-container footprint that erects to fire SM-6 and Tomahawk missiles at maritime and land targets out to roughly 450 km and 1,600 km. First shown in September 2021 when an SM-6 was fired from the unmanned surface vessel USV Ranger, it has since been integrated onto Freedom-class Littoral Combat Ships. Unlike Club-K it makes no attempt at concealment — the container is a modular launcher, not a disguise.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Elbit describes it as a bolt-on deck mission module rather than an explicit ISO container; container claim less firmly documented.</t>
+          <t>A separate claim that the Mk 70 first fired at sea from USS Savannah (LCS 28) in 2023 was refuted; its first at-sea firing was from USV Ranger in 2021.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>images/elbit-trigon.jpg</t>
+          <t>images/mk70-pds.jpg</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Elbit Systems</t>
+          <t>U.S. Navy / The War Zone</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://elbitsystems.com/product/trigon/</t>
+          <t>https://www.twz.com/wp-content/uploads/2022/09/14/navy-truck-missile-launcher-europe.jpg</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>https://elbitsystems.com/product/trigon/</t>
+          <t>https://www.navalnews.com/naval-news/2023/09/u-s-navy-and-army-mk-70-pds-stretch-their-wings/</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>TRIGON Sea-to-Shore Weapon System - Elbit</t>
+          <t>U.S. Navy And Army Mk 70 PDS Stretch Their Wings — Naval News</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>https://www.asianmilitaryreview.com/2017/06/imi-systems-solutions-extend-modern-naval-capabilities/</t>
+          <t>https://www.navalnews.com/event-news/sna-2025/2025/01/u-s-navy-brings-offensive-capability-to-lcs-with-mk-70-pds/</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>IMI Systems naval solutions - Asian Military Review</t>
+          <t>U.S. Navy Brings Offensive Capability To LCS With Mk 70 PDS — Naval News</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>northrop-ares</t>
+          <t>sh-defence-cube</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Northrop Grumman AReS</t>
+          <t>SH Defence CUBE System</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AReS, Advanced Reactive Strike, containerized ground-launched AARGM-ER</t>
+          <t>The Cube</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>SH Defence</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>January 2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Unveiled at Surface Navy Association Symposium</t>
+          <t>Product/brochure introduction</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Strike missile</t>
+          <t>Modular system</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A 20/40-ft ISO container concealing a four-cell vertical launcher for ground-launched AARGM-ER anti-radiation missiles (~150 km), aimed at rapidly deployable suppression of enemy radar and air-defense sites.</t>
+          <t>Denmark's SH Defence built the CUBE System, a maritime modularity ecosystem using 20-ft and 40-ft container dimensions fully compliant with NATO STANAG and DNV GL ST-0378, letting a naval vessel switch between mission profiles — anti-surface warfare, mine-laying, search and rescue — in under four hours. The catalog includes specialized modules such as UAV side-launch-and-recovery systems, top-launch UAV swarm modules, towed-array ASW sonars, and modular missile launchers, moved between a ship's internal mission bay and flight deck via automated 'Skidding Systems' and twist-locks.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Northrop and Hanwha signed an MOA (Apr 2026) to co-develop an AReS rocket booster.</t>
+          <t>An ecosystem/family of modules rather than a single weapon; entry covers the CUBE concept broadly.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>images/northrop-ares.jpg</t>
+          <t>images/sh-defence-cube.jpg</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Army Recognition Group</t>
+          <t>SH Defence</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/new-northrop-grumman-ares-missile-launcher-enables-fast-deployment-against-enemy-radar</t>
+          <t>https://shdefence.com/</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2025/new-northrop-grumman-ares-missile-launcher-enables-fast-deployment-against-enemy-radar</t>
+          <t>https://shdefence.com/wp-content/uploads/2021/08/SH-Defence_The-Cube%E2%84%A2-Solutions_Collection_Low.pdf</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>New Northrop Grumman AReS missile launcher - Army Recognition</t>
+          <t>The Cube Solutions — SH Defence</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>https://www.fw-mag.com/shownews/351/sna-2025-sees-northrop-grumman-push-ares-a-containerized-ground-launched-aargm-er</t>
+          <t>https://www.edge-defence.com/shdefencecube</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SNA 2025: Northrop Grumman push AReS - FW-MAG</t>
+          <t>The Cube — EDGE Defence Ltd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ruta-block-3</t>
+          <t>thor-hpm</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rheinmetall Destinus Ruta Block 3</t>
+          <t>THOR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ruta Block 3, RUTA Block III deep-strike cruise missile</t>
+          <t>Tactical High-power Operational Responder</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Rheinmetall Destinus Strike Systems</t>
+          <t>Air Force Research Laboratory (AFRL)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Germany / Switzerland-Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>June 2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Unveiled at Eurosatory 2026</t>
+          <t>Development and swarm-defeat testing at Kirtland AFB</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Strike missile</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6434,79 +6436,89 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A strategic deep-strike cruise missile (&gt;2,000 km, 250 kg warhead) launched exclusively from standard ISO shipping containers on vehicle (Rheinmetall HX truck) or maritime platforms, reaching firing readiness in ~2 minutes.</t>
+          <t>High-power microwave counter-swarm weapon stored in a standard 20-ft ISO container, C-130 transportable, set up in hours for airbase point defense against drone swarms.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Flight testing not scheduled until 2027; 100% European value chain targeted.</t>
+          <t>Follow-on is Mjolnir (Leidos).</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>images/ruta-block-3.jpg</t>
+          <t>images/thor-hpm.jpg</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Destinus (via Defence Industry Europe)</t>
+          <t>U.S. Air Force / AFRL (via Breaking Defense)</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>public-domain-gov</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://defence-industry.eu/destinus-and-rheinmetall-advance-ruta-block-3-programme-for-european-long-range-strike-production/</t>
+          <t>https://breakingdefense.com/wp-content/uploads/sites/13/2020/07/THOR-AFRL-HPM-190924-F-F3456-1001-1024x768.jpeg</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>https://defence-industry.eu/rheinmetall-destinus-strike-systems-outlines-european-cruise-missile-priorities-with-ruta-block-3-and-initial-production/</t>
+          <t>https://www.twz.com/thor-microwave-anti-drone-system-downs-swarms-in-test</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Rheinmetall Destinus Ruta Block 3 priorities - Defence Industry Europe</t>
+          <t>THOR Microwave Anti-Drone System Downs Swarms - TWZ</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>https://www.army-technology.com/news/rheinmetall-destinus-cruise-missile/</t>
+          <t>https://www.airandspaceforces.com/air-forces-thor-drone-swarm-demo/</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Rheinmetall, Destinus 2,000km cruise missile - Army Technology</t>
+          <t>THOR Hammers Drone Swarm - Air &amp; Space Forces Magazine</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/THOR_(weapon)</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>THOR (weapon) - Wikipedia</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cm-401</t>
+          <t>yj-18c</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CM-401 Containerized Deck Launcher</t>
+          <t>YJ-18C Container-Launched Cruise Missile</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CM-401 anti-ship ballistic missile, CASIC CM-401 deck launcher</t>
+          <t>YJ-18C, container-launched YJ-18 land-attack variant</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CASIC (China Aerospace Science &amp; Industry Corp)</t>
+          <t>CASC (China Aerospace Science and Technology Corp)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6516,32 +6528,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2018-11-06</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>November 2018</t>
+          <t>March 2019</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Unveiled at Zhuhai Airshow China 2018</t>
+          <t>US intelligence-sourced reporting of container-launched variant</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Missile launcher</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Concealed cargo</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Supersonic (Mach 4-6) anti-ship ballistic missile offered in a container-form deck launcher for surface ships (as well as an 8x8 truck TEL); pitched from 2025 for export coastal-defence use.</t>
+          <t>Reported land-attack variant of the YJ-18 cruise missile (&gt;1,000 km, low-RCS) designed to fire from launchers built to look like standard ISO shipping containers on merchant-ship decks or trucks; conceptually a Chinese Club-K.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6551,17 +6563,17 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Rebranded in army livery for coastal-defence export at IndoDefence 2025.</t>
+          <t>Traces to a single 2019 US-intel report; missile never officially shown separately from the container concept.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>images/cm-401.jpg</t>
+          <t>images/yj-18c.jpg</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Army Recognition</t>
+          <t>CCTV News via Global Times</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6571,74 +6583,84 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/army-news/2018/airshow-china-2018-casic-unveils-new-cm-401-anti-ship-missile</t>
+          <t>https://www.globaltimes.cn/page/202509/1342523.shtml</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>https://www.twz.com/24699/china-reveals-short-range-anti-ship-ballistic-missile-designed-to-dodge-enemy-defenses</t>
+          <t>https://freebeacon.com/national-security/china-building-long-range-cruise-missile-launched-from-ship-container/</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>China Reveals Short-Range Anti-Ship Ballistic Missile - TWZ</t>
+          <t>China Building Cruise Missile Launched from Ship Container - Free Beacon</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>https://armyrecognition.com/news/army-news/2025/indodefence-2025-china-promotes-cm-401-anti-ship-missile-as-coastal-defense-for-foreign-customers</t>
+          <t>https://www.armyrecognition.com/archives/archives-naval-defense/naval-defense-2019/china-is-building-long-range-cruise-missiles-launched-from-ship-containers</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>IndoDefence 2025: China promotes CM-401 as coastal defense - Army Recognition</t>
+          <t>China building long-range cruise missiles from ship containers - Army Recognition</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>https://www.scmp.com/news/china/military/article/3341929/will-new-chinas-yj-18c-missile-be-logistics-killer-us-navy</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Will China's YJ-18C missile be a logistics killer - SCMP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>saab-rbs15-cdms</t>
+          <t>mbda-spimm</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Saab Coastal Defence Missile System (RBS15 CDMS)</t>
+          <t>MBDA SPIMM / DEFENDAIR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saab CDMS, RBS15 containerized coastal launcher</t>
+          <t>Self-Protection Integrated Mistral Module</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Saab</t>
+          <t>MBDA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Europe (France-led consortium)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>September 2025</t>
+          <t>February 2019</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Publicly unveiled; on order for Swedish Armed Forces</t>
+          <t>Unveiled at NAVDEX 2019</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Artillery / coastal</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6648,104 +6670,104 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A truck-carried launcher matching the footprint of a 20-ft ISO container, holding four RBS15 Mk3/Mk4 anti-ship missiles (&gt;300 km) with a shoot-and-scoot relocation under 120 seconds.</t>
+          <t>MBDA's Self-Protection Integrated Mistral Module (SPIMM), unveiled at NAVDEX 2019, packs a SIMBAD-RC automated turret with two ready-to-fire Mistral 3 infrared-guided surface-to-air missiles into an all-in-one 10-ft, 7-ton container, topped with an HGH Spynel 360-degree infrared panoramic sensor and housing a two-operator control station. Needing only a tie-in to the host ship's main power, it gives unarmed auxiliary ships or landing craft immediate point-defense against aircraft, drones, and fast inshore attack craft. MBDA is separately developing DEFENDAIR, a maintenance-free containerized counter-UAS missile system optimized against agile drone swarms.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>RBS15 fielded across Sweden, Finland, Germany, Poland, Bulgaria, Croatia.</t>
+          <t>DEFENDAIR is a related but distinct, less-mature MBDA program folded into this entry.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>images/saab-rbs15-cdms.jpg</t>
+          <t>images/mbda-spimm.jpg</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Army Recognition Group</t>
+          <t>MBDA Systems</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>manufacturer</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/navy-news/2025/saabs-new-coastal-defense-system-built-on-rbs15-missile-targets-growing-maritime-threats</t>
+          <t>https://www.twz.com/26599/this-containerized-missile-launcher-could-give-almost-any-ship-short-range-air-defenses</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>https://www.saab.com/newsroom/stories/2025/september/a-powerful-new-deterrent-to-seaborne-threats</t>
+          <t>https://www.twz.com/26599/this-containerized-missile-launcher-could-give-almost-any-ship-short-range-air-defenses</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>A powerful new deterrent to seaborne threats - Saab</t>
+          <t>This Containerized Missile Launcher Could Give Almost Any Ship Short-Range Air Defenses — The War Zone</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/navy-news/2025/saabs-new-coastal-defense-system-built-on-rbs15-missile-targets-growing-maritime-threats</t>
+          <t>https://www.edrmagazine.eu/navdex-2019-mbda-unveils-the-self-protection-integrated-mistral-module-spimm-for-surface-ship</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Saab's New Coastal Defense System - Army Recognition</t>
+          <t>NAVDEX 2019: MBDA unveils the Self-Protection Integrated Mistral Module (SPIMM) for surface ship — EDR Magazine</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>iris-t-slm-container</t>
+          <t>cm-401</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Diehl IRIS-T SLM Containerized Fire Unit</t>
+          <t>CM-401 Containerized Deck Launcher</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IRIS-T SLM, IRIS-T SL container launcher/radar/TOC</t>
+          <t>CM-401 anti-ship ballistic missile, CASIC CM-401 deck launcher</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Diehl Defence</t>
+          <t>CASIC (China Aerospace Science &amp; Industry Corp)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>November 2018</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>First fire unit delivered to German Armed Forces</t>
+          <t>Unveiled at Zhuhai Airshow China 2018</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Air defense / C-UAS</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6755,79 +6777,79 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>IRIS-T SLM fire units (launcher, TRML-4D radar and IBMS tactical operations centre) are each built on standardised 20-ft ISO container frames for road/rail/sea/air transport; unmanned launchers reach readiness in 10 minutes.</t>
+          <t>Supersonic (Mach 4-6) anti-ship ballistic missile offered in a container-form deck launcher for surface ships (as well as an 8x8 truck TEL); pitched from 2025 for export coastal-defence use.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Widely fielded to Ukraine and the Bundeswehr; container-frame design confirmed by multiple sources.</t>
+          <t>Rebranded in army livery for coastal-defence export at IndoDefence 2025.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>images/iris-t-slm-container.jpg</t>
+          <t>images/cm-401.jpg</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Boevaya mashina / Wikimedia Commons</t>
+          <t>Army Recognition</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:IRIS-T_SLM_launcher_at_ILA-2024.JPG</t>
+          <t>https://www.armyrecognition.com/news/army-news/2018/airshow-china-2018-casic-unveils-new-cm-401-anti-ship-missile</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>https://defence-industry.eu/diehl-defence-delivers-first-unit-of-iris-t-slm-system-to-german-armed-forces/</t>
+          <t>https://www.twz.com/24699/china-reveals-short-range-anti-ship-ballistic-missile-designed-to-dodge-enemy-defenses</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Diehl delivers first IRIS-T SLM unit to German Armed Forces - Defence Industry Europe</t>
+          <t>China Reveals Short-Range Anti-Ship Ballistic Missile - TWZ</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/diehl-defence-delivers-first-iris-t-slm-air-defense-system-to-german-army</t>
+          <t>https://armyrecognition.com/news/army-news/2025/indodefence-2025-china-promotes-cm-401-anti-ship-missile-as-coastal-defense-for-foreign-customers</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>Diehl delivers first IRIS-T SLM to German Army - Army Recognition</t>
+          <t>IndoDefence 2025: China promotes CM-401 as coastal defense - Army Recognition</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>boeing-clws</t>
+          <t>liteye-c-auds</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Boeing Compact Laser Weapon System (containerized)</t>
+          <t>Liteye C-AUDS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CLWS, Boeing containerized laser weapon</t>
+          <t>C-AUDS, Containerized Anti-UAS Defense System</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Liteye Systems (integrating UK AUDS tech)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6837,22 +6859,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2018-09-05</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>June 2024</t>
+          <t>September 2018</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Demonstrated in containerized config at Canada's IDEaS C-UAS Sandbox</t>
+          <t>USAF follow-on contract; production units delivered Dec 2018</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Directed energy</t>
+          <t>Air defense / C-UAS</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6862,27 +6884,27 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A fixed containerized configuration of Boeing's 5kW-class Compact Laser Weapon System, paired with radar cueing to detect, track and defeat FPV drones, mortar rounds and a five-UAS swarm at 200m-2.5km in Canadian trials.</t>
+          <t>Integrates AUDS radar (Blighter), EO/IR tracker (Chess Dynamics) and RF-jamming effector (optional kinetic add-on) into a self-contained 20-ft ISO container for base and critical-infrastructure defense.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tested alongside a Polaris RZR-mounted CLWS unit; hosted by DRDC at CFB Suffield.</t>
+          <t>Base AUDS is vehicle/trailer-mounted; only the C-AUDS repackaging is a true container.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>images/boeing-clws.jpg</t>
+          <t>images/liteye-c-auds.jpg</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Liteye Systems, Inc.</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6892,151 +6914,151 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://www.boeing.com/features/2024/10/boeing-compact-lasers-down-group-3-drones-for-first-time</t>
+          <t>https://www.globenewswire.com/news-release/2020/07/16/2063226/0/en/Liteye-C-AUDS-Chosen-to-Defend-Critical-Infrastructure-by-the-US-Government.html</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>https://www.boeing.com/features/2024/06/boeings-compact-lasers-shine-at-counter-drone-competition</t>
+          <t>https://equipment.adsinc.com/</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Boeing's compact lasers at counter-drone competition - Boeing</t>
+          <t>Liteye C-AUDS product page - ADS</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>https://www.unmannedairspace.info/counter-uas-systems-and-policies/boeings-compact-laser-weapon-system-features-in-canadas-ideas-c-uas-trials/</t>
+          <t>https://www.unmannedairspace.info/</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Boeing CLWS in Canada's IDEaS C-UAS trials - Unmanned Airspace</t>
+          <t>Blighter to supply C-UAS radar to Liteye - Unmanned Airspace</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>navypods-strike</t>
+          <t>iai-lora</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Royal Navy NavyPODS (Strike POD)</t>
+          <t>IAI LORA Containerised Ballistic Missile</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PODS, Persistent Operational Deployment System, Strike POD</t>
+          <t>Long-Range Artillery (LORA) naval / ship-deck launch</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>G3 Systems / QinetiQ for Royal Navy</t>
+          <t>Israel Aerospace Industries (IAI)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2017-06-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>September 2021</t>
+          <t>June 2017</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Concept unveiled at DSEI 2021</t>
+          <t>First ship-deck launch 20 Jun 2017; repeat Mediterranean test June 2020</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Modular system</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A 20-ft ISO container-footprint modular payload system for RN vessels; the Strike POD variant hosts launchers for armed UAVs or loitering munitions plus a mission-planning area, part of an 18+ POD family.</t>
+          <t>IAI test-launched its LORA quasi-ballistic missile from a container-dimensioned launcher placed on the deck of a civilian-type cargo ship on 20 June 2017, then repeated the feat in 2020 by striking two floating targets at roughly 90 km and 400 km. Because the sealed launch canister conforms to standard shipping-container dimensions, the system can be hidden among ordinary deck cargo. It demonstrated that a precision ballistic strike could be mounted from an unremarkable merchant hull.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Armed Strike POD remains a low-TRL demonstrator; G3 Systems selected as preferred supplier Nov 2025.</t>
+          <t>2017/2020 trials used the LORA launcher set on a deck and remote-fired; missiles ship in sealed ISO-conformant canisters.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>images/navypods-strike.jpg</t>
+          <t>images/iai-lora.jpg</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>FDS/Simon Bradley, via Naval News</t>
+          <t>Wikimedia Commons (Paris Air Show)</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2026/05/royal-navy-achieves-milestone-with-first-sea-trials-of-navypods/</t>
+          <t>https://commons.wikimedia.org/wiki/File:LORA_missile.JPG</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>https://www.navylookout.com/thinking-inside-the-box-the-royal-navys-containerised-capability-concept/</t>
+          <t>https://www.twz.com/11723/israel-just-launched-a-containerized-ballistic-missile-from-the-deck-of-a-ship</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Royal Navy's containerised capability concept - Navy Lookout</t>
+          <t>Israel Just Launched A Containerized Ballistic Missile From The Deck Of A Ship — The War Zone</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2025/11/g3-systems-selected-as-the-preferred-supplier-to-upgrade-navypods-capability/</t>
+          <t>https://en.wikipedia.org/wiki/LORA_(missile)</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>G3 Systems preferred supplier for NavyPODS - Naval News</t>
+          <t>LORA (missile) — Wikipedia</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>elbit-seagull-usv</t>
+          <t>elbit-trigon</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Elbit Seagull USV</t>
+          <t>Elbit TRIGON Sea-to-Shore Weapon System</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seagull MCM/ASW USV, Seagull Mk3</t>
+          <t>TRIGON naval rocket and missile launcher</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7051,47 +7073,47 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>February 2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4th-gen Seagull showcased at NAVDEX 2025</t>
+          <t>Earliest trade-press coverage (approximate)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Autonomous vehicle</t>
+          <t>Naval arsenal</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Modular deck launcher</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A 12m multi-mission unmanned surface vessel (MCM/ASW/EW) that ships and deploys from a standard 40-ft ISO container; the planned 20m Mk3 adds deck space for a standardised 20-ft ISO container payload.</t>
+          <t>A fixed-elevation deck-mounted launcher carrying two pods of four EXTRA guided rockets (150 km) each, installable permanently or as an add-on mission module above or below deck on small-to-medium naval craft.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>100% success in Royal Navy WISEX mine-hunting trials.</t>
+          <t>Elbit describes it as a bolt-on deck mission module rather than an explicit ISO container; container claim less firmly documented.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>images/elbit-seagull-usv.jpg</t>
+          <t>images/elbit-trigon.jpg</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -7106,74 +7128,74 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://www.elbitsystems.com/unmanned/maritime/unmanned-surface-vessel/seagull-usv</t>
+          <t>https://elbitsystems.com/product/trigon/</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>https://www.elbitsystems.com/unmanned/maritime/unmanned-surface-vessel/seagull-usv</t>
+          <t>https://elbitsystems.com/product/trigon/</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Seagull USV - Elbit Systems</t>
+          <t>TRIGON Sea-to-Shore Weapon System - Elbit</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>https://www.janes.com/osint-insights/defence-news/sea/navdex-2025-elbit-system-showcases-fourth-generation-seagull-usv</t>
+          <t>https://www.asianmilitaryreview.com/2017/06/imi-systems-solutions-extend-modern-naval-capabilities/</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>NAVDEX 2025: 4th-gen Seagull USV - Janes</t>
+          <t>IMI Systems naval solutions - Asian Military Review</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>blacksea-chaser-usv</t>
+          <t>silent-hunter</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BlackSea Technologies Chaser USV</t>
+          <t>Silent Hunter</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chaser, GARC Block II</t>
+          <t>Shen Nu, Silent Hunter laser air-defence</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BlackSea Technologies</t>
+          <t>Poly Technologies</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>February 2017</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Unveiled at Sea-Air-Space 2026</t>
+          <t>Unveiled at IDEX 2017; Saudi operational use vs Houthi drones</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Autonomous vehicle</t>
+          <t>Directed energy</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7183,114 +7205,114 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A modular unmanned surface vessel engineered to fit inside and deploy from a standard 20-ft ISO container per a US Navy transportability requirement; carries JAGM launchers and EO/radar sensors.</t>
+          <t>30-100kW-class anti-drone fiber laser; the mobile version is described as installed in a container towed by a 6x6 truck. Exported to the UAE/Saudi Arabia.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Built on ~5,000 operational hours of the earlier GARC design; unveiled alongside the larger Comet USV.</t>
+          <t>Some sources describe it as separate truck-sized power and equipment units rather than a clear ISO box.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>images/blacksea-chaser-usv.jpg</t>
+          <t>images/silent-hunter.jpg</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>BlackSea Technologies</t>
+          <t>Army Recognition</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://www.blacksea.tech/chaser</t>
+          <t>https://www.armyrecognition.com/archives/archives-land-defense/land-defense-2024/dsa-2024-chinese-company-poly-technologies-showcases-silent-hunter-laser-defense-system</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>https://www.navalnews.com/naval-news/2026/05/video-new-comet-and-chaser-usv-by-blacksea-technologies/</t>
+          <t>https://en.wikipedia.org/wiki/Silent_Hunter_(laser_weapon)</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>New Comet and Chaser USV by BlackSea Technologies - Naval News</t>
+          <t>Silent Hunter (laser weapon) - Wikipedia</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>https://www.blacksea.tech/chaser</t>
+          <t>https://armyrecognition.com/news/army-news/army-news-2024/dsa-2024-chinese-company-poly-technologies-showcases-silent-hunter-laser-defense-system</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Chaser - BlackSea Technologies</t>
+          <t>Poly Technologies showcases Silent Hunter - Army Recognition</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>speartooth-luuv</t>
+          <t>club-k</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C2 Robotics Speartooth LUUV</t>
+          <t>Club-K Container Missile System</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Speartooth, C2 Robotics long-range LUUV</t>
+          <t>Klab-K; 3M-54/Kh-35UE containerised launcher</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>C2 Robotics</t>
+          <t>Concern Morinformsystem-Agat (missiles by Novator Design Bureau)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2010-04-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>First unit delivered to US Navy</t>
+          <t>Unveiled 2010 (DSA Malaysia); live Kh-35UE test 22 Aug 2012</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Autonomous vehicle</t>
+          <t>Strike missile</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Container form-factor</t>
+          <t>Concealed cargo</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A long-range (2,000 km), 2,000m-depth large uncrewed undersea vehicle purpose-built to ship inside and deploy from a standard container via ramp or austere coastal infrastructure, without dedicated submarine support; ISR, mine warfare and strike delivery.</t>
+          <t>The archetype: a standard 20-ft or 40-ft ISO shipping container that conceals four cruise missiles from the Kalibr family (3M-54/3M-14) or Kh-35UE anti-ship missiles, letting any truck, rail car, or cargo ship become a covert missile battery disguised as ordinary freight. Marketed for export by Concern Morinformsystem-Agat, it triggered international alarm over the blurring of civilian and military shipping. A live-fire test of the Kh-35UE variant was reported on 22 August 2012.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7300,572 +7322,57 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Follows a 2025 NUWC Newport order for three long-range LUUVs.</t>
+          <t>Missiles designed by Novator; container system marketed by Morinformsystem-Agat. Widely regarded as the concept that launched the containerised-weapons debate.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>images/speartooth-luuv.jpg</t>
+          <t>images/club-k.jpg</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>C2 Robotics Pty Ltd</t>
+          <t>Wikimedia Commons</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>wikimedia</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://c2robotics.com.au/products/speartooth/</t>
+          <t>https://commons.wikimedia.org/wiki/File:Club-K.jpg</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>https://www.armyrecognition.com/news/navy-news/2026/us-navy-receives-first-australian-speartooth-luuv-drone-for-autonomous-underwater-strikes</t>
+          <t>https://en.wikipedia.org/wiki/Club-K_container_missile_system</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>US Navy receives first Australian Speartooth LUUV - Army Recognition</t>
+          <t>Club-K container missile system — Wikipedia</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>https://www.navaltoday.com/2026/05/05/australian-firm-commissions-first-us-export-luuv/</t>
+          <t>https://navyrecognition.com/index.php?id=592&amp;option=com_content&amp;view=article</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Australian firm commissions first US export LUUV - Naval Today</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>xv-excalibur</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>XV Excalibur XLUUV</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Project Cetus XLUUV, Excalibur</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>MSubs Ltd / UK Submarine Delivery Agency</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>December 2025</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Handed over to Royal Navy</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Autonomous vehicle</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Container form-factor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>A 12m, ~19-25 tonne extra-large uncrewed underwater vehicle technology testbed, sized to be transported worldwide inside a standard 40-ft shipping container; controlled submerged from a remote centre in Australia during Talisman Sabre 2025.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Culmination of Project Cetus; payload bay can carry mines, smaller UUVs, sensors.</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>images/xv-excalibur.jpg</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Royal Navy / UK MOD (OGL v3.0)</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>wikimedia</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Cetus-at-an-angle-front.jpg</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>https://www.navalnews.com/naval-news/2026/01/autonomous-submarine-xv-excalibur-handed-to-royal-navy/</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>Autonomous submarine XV Excalibur handed to Royal Navy - Naval News</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>https://www.naval-technology.com/news/royal-navy-name-project-cetus-xluuv-excalibur/</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Royal Navy name Project Cetus XLUUV Excalibur - Naval Technology</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>bluewhale-uuv</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>IAI/tkMS BlueWhale UUV</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>BlueWhale AUV/XLUUV</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Israel Aerospace Industries / thyssenkrupp Marine Systems</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Israel / Germany</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>February 2026</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Delivered to German Navy at Eckernforde</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Autonomous vehicle</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Container form-factor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>A 10.9m, 5.5-tonne autonomous underwater vehicle for ASW support, minehunting and covert ISR, engineered to be transported inside a standard 40-ft shipping container for deployment by land, air or sea; 10-30 day endurance to 300m depth.</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Delivered under Germany's Kurs Marine 2035+ program after a 2-week German Navy trial.</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>images/bluewhale-uuv.jpg</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>Swadim / Wikimedia Commons (CC0)</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>wikimedia</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:BlueWhale.jpg</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>https://www.tkmsgroup.com/news/article/autonomous-underwater-vehicle-bluewhale-handed-over-to-german-navy-delivery-by-tkms-and-israel-aerospace-industries-as-part-of-the-kurs-marine-2035-program</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>BlueWhale AUV handed over to German Navy - TKMS Group</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>https://www.armyrecognition.com/news/navy-news/2026/germanys-new-bluewhale-autonomous-underwater-vehicle-is-transforming-baltic-maritime-surveillance</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Germany's BlueWhale AUV - Army Recognition</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>anduril-slb-500m</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Anduril Surface-Launched Barracuda-500M</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>SLB-500M, Surface-Launched Barracuda</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Anduril Industries</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Production agreement announcement</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Strike missile</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Container form-factor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>A surface-launched Barracuda-500M variant paired with a standard 20-ft ISO launcher that can carry up to 16 rounds, for dispersed land and maritime strike; announced under the US Low-Cost Containerized Munitions effort.</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>From ChatGPT deep-research set; corroborated by Anduril and Naval News.</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>images/anduril-slb-500m.jpg</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Anduril Industries, via The Defense Post</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>https://thedefensepost.com/2026/05/14/anduril-us-barracuda-500m-production/</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>https://www.anduril.com/news/anduril-department-of-war-sign-production-agreement-for-surface-launched-barracuda-500m</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Anduril-DoW Production Agreement for SLB-500M - Anduril</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>https://www.navalnews.com/naval-news/2026/05/massive-u-s-missile-order-may-expand-american-anti-ship-arsenal/</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Massive US Missile Order May Expand Anti-Ship Arsenal - Naval News</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>iai-diamond</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>IAI DIAMOND Distributed Warfare System</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>DIAMOND, Distributed Warfare Solution</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Israel Aerospace Industries</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Official unveiling</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>Modular system</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Modular deck launcher</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>A distributed-warfare architecture using container-footprint payload modules for ships and other platforms, able to host loitering munitions, Blue Spear, LORA, Barak MX and counter-UAS payloads in reconfigurable packages.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>From ChatGPT deep-research set. Architecture/family rather than a fixed single-munition launcher.</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>images/iai-diamond.jpg</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>IAI (Israel Aerospace Industries), via Naval News</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>https://www.navalnews.com/naval-news/2026/05/iai-unveils-diamond-new-distributed-warfare-solution-that-expands-the-power-of-modern-frigates/</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>https://www.iai.co.il/press/iai-unveils-diamond</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>IAI Unveils DIAMOND: New Distributed Warfare Solution - IAI</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>https://www.iai.co.il/product/diamond</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>DIAMOND - IAI</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>vampire-casket</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>L3Harris VAMPIRE CASKET</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>VAMPIRE CASKET, Containerized VAMPIRE counter-drone</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>L3Harris Technologies</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>October 2025</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Shown in L3Harris roadmap imagery</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Air defense / C-UAS</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Container form-factor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>A standard-container mounting of L3Harris's VAMPIRE counter-drone system, combining its sensor-and-launcher architecture with kinetic effectors including laser-guided 70mm rockets.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>From ChatGPT deep-research set. Depicted as a proposed family variant; dimensions/procurement/fielding limited.</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>images/vampire-casket.jpg</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>L3Harris (via The War Zone)</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>https://www.twz.com/air/entire-family-of-vampire-counter-drone-systems-unveiled</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>https://www.twz.com/air/entire-family-of-vampire-counter-drone-systems-unveiled</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Entire Family Of VAMPIRE Counter-Drone Systems Unveiled - TWZ</t>
+          <t>Club-K Container Missile System — Navy Recognition</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>https://euro-sd.com/2025/05/articles/44048/if-it-floats-it-fights-containerised-naval-munitions/</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>If It Floats, It Fights: Containerised Naval Munitions — ESD</t>
         </is>
       </c>
     </row>

--- a/data/systems.xlsx
+++ b/data/systems.xlsx
@@ -669,17 +669,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Artvill / Wikimedia Commons</t>
+          <t>Destinus (via DroneFirms)</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>wikimedia</t>
+          <t>news</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Destinus_Hornet_au_Salon_du_Bourget_2025_1.jpg</t>
+          <t>https://media.dronefirms.com/articles/2026/img/destinus-hornet-block1-spanish-navy-frigate.jpg</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -6059,8 +6059,6 @@
           <t>Ivan Papanin begins sea trials with Kalibr - Army Recognition</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">

--- a/data/systems.xlsx
+++ b/data/systems.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="systems" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="systems" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -883,17 +883,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>KNDS Group</t>
+          <t>Army Recognition (@ArmyRecognition)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>manufacturer</t>
+          <t>editorial</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>https://knds.com/en/press-releases/bolstering-mission-solution-portfolio-knds-showcases-first-drone-launch-container-prototype-at-eurosatory-2026-1</t>
+          <t>https://x.com/ArmyRecognition/status/2067157227341811904</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
